--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:58</t>
+          <t>2026-05-31 17:53:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:00</t>
+          <t>2026-05-31 17:53:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81816</v>
+        <v>4.81765</v>
       </c>
       <c r="G3" t="n">
-        <v>12456</v>
+        <v>12465</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11584</v>
+        <v>11592</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:03</t>
+          <t>2026-05-31 17:53:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:05</t>
+          <t>2026-05-31 17:53:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53074</v>
+        <v>2.53174</v>
       </c>
       <c r="G5" t="n">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O5" t="n">
         <v>97</v>
@@ -802,10 +802,10 @@
         <v>97</v>
       </c>
       <c r="Q5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R5" t="n">
-        <v>1308</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:07</t>
+          <t>2026-05-31 17:53:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:09</t>
+          <t>2026-05-31 17:53:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.019</v>
+        <v>4.0201</v>
       </c>
       <c r="G7" t="n">
         <v>3631</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:11</t>
+          <t>2026-05-31 17:53:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -982,7 +982,7 @@
         <v>4.74974</v>
       </c>
       <c r="G8" t="n">
-        <v>13215</v>
+        <v>13223</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11894</v>
+        <v>11901</v>
       </c>
       <c r="O8" t="n">
         <v>529</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:14</t>
+          <t>2026-05-31 17:53:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61918</v>
+        <v>4.61972</v>
       </c>
       <c r="G9" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O9" t="n">
         <v>21</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:16</t>
+          <t>2026-05-31 17:53:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:18</t>
+          <t>2026-05-31 17:53:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:20</t>
+          <t>2026-05-31 17:53:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74338</v>
+        <v>4.74453</v>
       </c>
       <c r="G12" t="n">
-        <v>2872</v>
+        <v>2877</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2527</v>
+        <v>2532</v>
       </c>
       <c r="O12" t="n">
         <v>144</v>
       </c>
       <c r="P12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="n">
         <v>29</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:22</t>
+          <t>2026-05-31 17:53:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:25</t>
+          <t>2026-05-31 17:53:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:27</t>
+          <t>2026-05-31 17:53:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-30 17:55:29</t>
+          <t>2026-05-31 17:53:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75028</v>
+        <v>4.7504</v>
       </c>
       <c r="G16" t="n">
-        <v>31224</v>
+        <v>31231</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>28102</v>
+        <v>28108</v>
       </c>
       <c r="O16" t="n">
         <v>1249</v>
       </c>
       <c r="P16" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Q16" t="n">
         <v>312</v>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -496,27 +496,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>1_star_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2_star_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>3_star_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>4_star_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>5_star_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>4_star_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>3_star_count</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2_star_count</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>1_star_count</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:06</t>
+          <t>2026-06-01 17:43:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:08</t>
+          <t>2026-06-01 17:43:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81765</v>
+        <v>4.8174</v>
       </c>
       <c r="G3" t="n">
-        <v>12465</v>
+        <v>12470</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11592</v>
+        <v>374</v>
       </c>
       <c r="O3" t="n">
-        <v>249</v>
+        <v>125</v>
       </c>
       <c r="P3" t="n">
         <v>125</v>
       </c>
       <c r="Q3" t="n">
-        <v>125</v>
+        <v>249</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>11597</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:10</t>
+          <t>2026-06-01 17:43:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2960</v>
+        <v>955</v>
       </c>
       <c r="O4" t="n">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="P4" t="n">
         <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="R4" t="n">
-        <v>955</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:13</t>
+          <t>2026-06-01 17:43:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53174</v>
+        <v>2.5325</v>
       </c>
       <c r="G5" t="n">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>776</v>
+        <v>1312</v>
       </c>
       <c r="O5" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="P5" t="n">
         <v>97</v>
       </c>
       <c r="Q5" t="n">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="R5" t="n">
-        <v>1310</v>
+        <v>778</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:15</t>
+          <t>2026-06-01 17:43:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:17</t>
+          <t>2026-06-01 17:43:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0201</v>
+        <v>4.02037</v>
       </c>
       <c r="G7" t="n">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2324</v>
+        <v>581</v>
       </c>
       <c r="O7" t="n">
-        <v>399</v>
+        <v>145</v>
       </c>
       <c r="P7" t="n">
         <v>182</v>
       </c>
       <c r="Q7" t="n">
-        <v>145</v>
+        <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>581</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:19</t>
+          <t>2026-06-01 17:43:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74974</v>
+        <v>4.74941</v>
       </c>
       <c r="G8" t="n">
-        <v>13223</v>
+        <v>13233</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11901</v>
+        <v>529</v>
       </c>
       <c r="O8" t="n">
+        <v>132</v>
+      </c>
+      <c r="P8" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q8" t="n">
         <v>529</v>
       </c>
-      <c r="P8" t="n">
-        <v>264</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>132</v>
-      </c>
       <c r="R8" t="n">
-        <v>529</v>
+        <v>11910</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:22</t>
+          <t>2026-06-01 17:43:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>625</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>50</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:24</t>
+          <t>2026-06-01 17:43:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>652</v>
+        <v>224</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P10" t="n">
         <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>224</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:26</t>
+          <t>2026-06-01 17:43:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>13</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:28</t>
+          <t>2026-06-01 17:43:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74453</v>
+        <v>4.74478</v>
       </c>
       <c r="G12" t="n">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2532</v>
+        <v>86</v>
       </c>
       <c r="O12" t="n">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="P12" t="n">
         <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>86</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:31</t>
+          <t>2026-06-01 17:43:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>359</v>
+        <v>99</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
         <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>99</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:33</t>
+          <t>2026-06-01 17:43:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:35</t>
+          <t>2026-06-01 17:43:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:38</t>
+          <t>2026-06-01 17:43:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7504</v>
+        <v>4.75033</v>
       </c>
       <c r="G16" t="n">
-        <v>31231</v>
+        <v>31238</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>28108</v>
+        <v>1250</v>
       </c>
       <c r="O16" t="n">
-        <v>1249</v>
+        <v>312</v>
       </c>
       <c r="P16" t="n">
         <v>625</v>
       </c>
       <c r="Q16" t="n">
-        <v>312</v>
+        <v>1250</v>
       </c>
       <c r="R16" t="n">
-        <v>1249</v>
+        <v>28114</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:03</t>
+          <t>2026-06-01 20:49:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:05</t>
+          <t>2026-06-01 20:49:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:08</t>
+          <t>2026-06-01 20:49:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:11</t>
+          <t>2026-06-01 20:49:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:13</t>
+          <t>2026-06-01 20:49:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:15</t>
+          <t>2026-06-01 20:50:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:18</t>
+          <t>2026-06-01 20:50:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:20</t>
+          <t>2026-06-01 20:50:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:23</t>
+          <t>2026-06-01 20:50:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:27</t>
+          <t>2026-06-01 20:50:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:29</t>
+          <t>2026-06-01 20:50:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:32</t>
+          <t>2026-06-01 20:50:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:34</t>
+          <t>2026-06-01 20:50:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:37</t>
+          <t>2026-06-01 20:50:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-01 17:43:39</t>
+          <t>2026-06-01 20:50:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:49</t>
+          <t>2026-06-02 20:00:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:52</t>
+          <t>2026-06-02 20:00:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:54</t>
+          <t>2026-06-02 20:00:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:56</t>
+          <t>2026-06-02 20:00:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:59</t>
+          <t>2026-06-02 20:00:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:01</t>
+          <t>2026-06-02 20:00:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02037</v>
+        <v>4.02064</v>
       </c>
       <c r="G7" t="n">
-        <v>3632</v>
+        <v>3633</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:04</t>
+          <t>2026-06-02 20:00:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:06</t>
+          <t>2026-06-02 20:00:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61972</v>
+        <v>4.61991</v>
       </c>
       <c r="G9" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:08</t>
+          <t>2026-06-02 20:00:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:11</t>
+          <t>2026-06-02 20:00:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:13</t>
+          <t>2026-06-02 20:00:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74478</v>
+        <v>4.74486</v>
       </c>
       <c r="G12" t="n">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:15</t>
+          <t>2026-06-02 20:00:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:18</t>
+          <t>2026-06-02 20:00:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:20</t>
+          <t>2026-06-02 20:00:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-01 20:50:22</t>
+          <t>2026-06-02 20:00:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:01</t>
+          <t>2026-06-03 20:13:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:04</t>
+          <t>2026-06-03 20:13:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8174</v>
+        <v>4.81773</v>
       </c>
       <c r="G3" t="n">
-        <v>12470</v>
+        <v>12498</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O3" t="n">
         <v>125</v>
@@ -658,10 +658,10 @@
         <v>125</v>
       </c>
       <c r="Q3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R3" t="n">
-        <v>11597</v>
+        <v>11623</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:07</t>
+          <t>2026-06-03 20:13:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:09</t>
+          <t>2026-06-03 20:13:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5325</v>
+        <v>2.53125</v>
       </c>
       <c r="G5" t="n">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:12</t>
+          <t>2026-06-03 20:13:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:14</t>
+          <t>2026-06-03 20:13:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02064</v>
+        <v>4.02036</v>
       </c>
       <c r="G7" t="n">
-        <v>3633</v>
+        <v>3634</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>2325</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:17</t>
+          <t>2026-06-03 20:13:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74941</v>
+        <v>4.748</v>
       </c>
       <c r="G8" t="n">
-        <v>13233</v>
+        <v>13262</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O8" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
         <v>265</v>
       </c>
       <c r="Q8" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R8" t="n">
-        <v>11910</v>
+        <v>11936</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:19</t>
+          <t>2026-06-03 20:13:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:22</t>
+          <t>2026-06-03 20:13:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:25</t>
+          <t>2026-06-03 20:13:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>May 04, 2026</t>
+          <t>June 02, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:28</t>
+          <t>2026-06-03 20:13:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74486</v>
+        <v>4.74471</v>
       </c>
       <c r="G12" t="n">
-        <v>2877</v>
+        <v>2883</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2532</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:30</t>
+          <t>2026-06-03 20:13:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:33</t>
+          <t>2026-06-03 20:13:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:35</t>
+          <t>2026-06-03 20:13:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-02 20:00:37</t>
+          <t>2026-06-03 20:13:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75033</v>
+        <v>4.7502</v>
       </c>
       <c r="G16" t="n">
-        <v>31238</v>
+        <v>31265</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="O16" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P16" t="n">
         <v>625</v>
       </c>
       <c r="Q16" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="R16" t="n">
-        <v>28114</v>
+        <v>28138</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:14</t>
+          <t>2026-06-04 19:11:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:16</t>
+          <t>2026-06-04 19:11:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81773</v>
+        <v>4.81792</v>
       </c>
       <c r="G3" t="n">
-        <v>12498</v>
+        <v>12512</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>250</v>
       </c>
       <c r="R3" t="n">
-        <v>11623</v>
+        <v>11636</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:19</t>
+          <t>2026-06-04 19:11:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:21</t>
+          <t>2026-06-04 19:11:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53125</v>
+        <v>2.53262</v>
       </c>
       <c r="G5" t="n">
-        <v>2432</v>
+        <v>2437</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>97</v>
       </c>
       <c r="R5" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:24</t>
+          <t>2026-06-04 19:11:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:26</t>
+          <t>2026-06-04 19:11:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:29</t>
+          <t>2026-06-04 19:11:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.748</v>
+        <v>4.7484</v>
       </c>
       <c r="G8" t="n">
-        <v>13262</v>
+        <v>13271</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O8" t="n">
         <v>133</v>
@@ -1018,10 +1018,10 @@
         <v>265</v>
       </c>
       <c r="Q8" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R8" t="n">
-        <v>11936</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:31</t>
+          <t>2026-06-04 19:11:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:34</t>
+          <t>2026-06-04 19:11:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:36</t>
+          <t>2026-06-04 19:11:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>2.72414</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:39</t>
+          <t>2026-06-04 19:11:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74471</v>
+        <v>4.74697</v>
       </c>
       <c r="G12" t="n">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O12" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2537</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:42</t>
+          <t>2026-06-04 19:11:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:44</t>
+          <t>2026-06-04 19:11:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:47</t>
+          <t>2026-06-04 19:11:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:50</t>
+          <t>2026-06-04 19:11:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7502</v>
+        <v>4.75033</v>
       </c>
       <c r="G16" t="n">
-        <v>31265</v>
+        <v>31282</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>313</v>
       </c>
       <c r="P16" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Q16" t="n">
         <v>1251</v>
       </c>
       <c r="R16" t="n">
-        <v>28138</v>
+        <v>28154</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:01</t>
+          <t>2026-06-05 18:53:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:03</t>
+          <t>2026-06-05 18:53:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81792</v>
+        <v>4.81738</v>
       </c>
       <c r="G3" t="n">
-        <v>12512</v>
+        <v>12518</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O3" t="n">
         <v>125</v>
@@ -661,7 +661,7 @@
         <v>250</v>
       </c>
       <c r="R3" t="n">
-        <v>11636</v>
+        <v>11642</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:06</t>
+          <t>2026-06-05 18:54:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:08</t>
+          <t>2026-06-05 18:54:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:10</t>
+          <t>2026-06-05 18:54:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:13</t>
+          <t>2026-06-05 18:54:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02036</v>
+        <v>4.02062</v>
       </c>
       <c r="G7" t="n">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O7" t="n">
         <v>145</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:15</t>
+          <t>2026-06-05 18:54:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7484</v>
+        <v>4.74756</v>
       </c>
       <c r="G8" t="n">
-        <v>13271</v>
+        <v>13283</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>133</v>
       </c>
       <c r="P8" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="n">
         <v>531</v>
       </c>
       <c r="R8" t="n">
-        <v>11944</v>
+        <v>11955</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:17</t>
+          <t>2026-06-05 18:54:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:19</t>
+          <t>2026-06-05 18:54:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:22</t>
+          <t>2026-06-05 18:54:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72414</v>
+        <v>2.66667</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 02, 2026</t>
+          <t>June 05, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:24</t>
+          <t>2026-06-05 18:54:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74697</v>
+        <v>4.74714</v>
       </c>
       <c r="G12" t="n">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2568</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:26</t>
+          <t>2026-06-05 18:54:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:29</t>
+          <t>2026-06-05 18:54:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:31</t>
+          <t>2026-06-05 18:54:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-04 19:11:33</t>
+          <t>2026-06-05 18:54:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:57</t>
+          <t>2026-06-06 17:58:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:59</t>
+          <t>2026-06-06 17:58:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81738</v>
+        <v>4.81754</v>
       </c>
       <c r="G3" t="n">
-        <v>12518</v>
+        <v>12529</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:01</t>
+          <t>2026-06-06 17:58:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>955</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:04</t>
+          <t>2026-06-06 17:58:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53262</v>
+        <v>2.53074</v>
       </c>
       <c r="G5" t="n">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1316</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:06</t>
+          <t>2026-06-06 17:58:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:08</t>
+          <t>2026-06-06 17:58:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>582</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:11</t>
+          <t>2026-06-06 17:59:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74756</v>
+        <v>4.74733</v>
       </c>
       <c r="G8" t="n">
-        <v>13283</v>
+        <v>13290</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0.44</t>
+          <t>1.0.45</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1005,23 +1005,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>May 10, 2026</t>
+          <t>June 05, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>11955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:13</t>
+          <t>2026-06-06 17:59:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:15</t>
+          <t>2026-06-06 17:59:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:18</t>
+          <t>2026-06-06 17:59:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:20</t>
+          <t>2026-06-06 17:59:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74714</v>
+        <v>4.74732</v>
       </c>
       <c r="G12" t="n">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2569</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:22</t>
+          <t>2026-06-06 17:59:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01731</v>
+        <v>4.01919</v>
       </c>
       <c r="G13" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:25</t>
+          <t>2026-06-06 17:59:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:27</t>
+          <t>2026-06-06 17:59:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-05 18:54:30</t>
+          <t>2026-06-06 17:59:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75033</v>
+        <v>4.75028</v>
       </c>
       <c r="G16" t="n">
-        <v>31282</v>
+        <v>31296</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="O16" t="n">
         <v>313</v>
@@ -1594,10 +1594,10 @@
         <v>626</v>
       </c>
       <c r="Q16" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="R16" t="n">
-        <v>28154</v>
+        <v>28166</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:49</t>
+          <t>2026-06-07 17:57:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:51</t>
+          <t>2026-06-07 17:57:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81754</v>
+        <v>4.81759</v>
       </c>
       <c r="G3" t="n">
-        <v>12529</v>
+        <v>12533</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.42.1</t>
+          <t>4.43.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,23 +645,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>May 21, 2026</t>
+          <t>June 07, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11656</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:53</t>
+          <t>2026-06-07 17:58:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88377</v>
+        <v>3.88293</v>
       </c>
       <c r="G4" t="n">
         <v>4775</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:54</t>
+          <t>2026-06-07 17:58:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:56</t>
+          <t>2026-06-07 17:58:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:58</t>
+          <t>2026-06-07 17:58:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02062</v>
+        <v>4.0209</v>
       </c>
       <c r="G7" t="n">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:00</t>
+          <t>2026-06-07 17:58:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74733</v>
+        <v>4.74684</v>
       </c>
       <c r="G8" t="n">
-        <v>13290</v>
+        <v>13296</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>11833</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:02</t>
+          <t>2026-06-07 17:58:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:05</t>
+          <t>2026-06-07 17:58:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:07</t>
+          <t>2026-06-07 17:58:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:09</t>
+          <t>2026-06-07 17:58:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74732</v>
+        <v>4.7474</v>
       </c>
       <c r="G12" t="n">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>144</v>
       </c>
       <c r="R12" t="n">
-        <v>2571</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:11</t>
+          <t>2026-06-07 17:58:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:14</t>
+          <t>2026-06-07 17:58:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:16</t>
+          <t>2026-06-07 17:58:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-06 17:59:18</t>
+          <t>2026-06-07 17:58:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75028</v>
+        <v>4.75033</v>
       </c>
       <c r="G16" t="n">
-        <v>31296</v>
+        <v>31305</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>May 25, 2026</t>
+          <t>June 07, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1597,7 +1597,7 @@
         <v>1252</v>
       </c>
       <c r="R16" t="n">
-        <v>28166</v>
+        <v>28174</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:56</t>
+          <t>2026-06-08 19:12:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.64626</v>
+        <v>4.625</v>
       </c>
       <c r="G2" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:59</t>
+          <t>2026-06-08 19:12:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81759</v>
+        <v>4.81738</v>
       </c>
       <c r="G3" t="n">
-        <v>12533</v>
+        <v>12540</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>11656</v>
+        <v>11662</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:01</t>
+          <t>2026-06-08 19:12:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88293</v>
+        <v>3.88117</v>
       </c>
       <c r="G4" t="n">
-        <v>4775</v>
+        <v>4780</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.21.2</t>
+          <t>2.22.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -717,11 +717,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>March 18, 2026</t>
+          <t>June 08, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="O4" t="n">
         <v>239</v>
@@ -733,7 +733,7 @@
         <v>382</v>
       </c>
       <c r="R4" t="n">
-        <v>2960</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:03</t>
+          <t>2026-06-08 19:13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53074</v>
+        <v>2.52948</v>
       </c>
       <c r="G5" t="n">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="O5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
         <v>98</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:06</t>
+          <t>2026-06-08 19:13:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:08</t>
+          <t>2026-06-08 19:13:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0209</v>
+        <v>4.0206</v>
       </c>
       <c r="G7" t="n">
-        <v>3636</v>
+        <v>3639</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>582</v>
       </c>
       <c r="O7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P7" t="n">
         <v>182</v>
@@ -949,7 +949,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>2327</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:11</t>
+          <t>2026-06-08 19:13:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74684</v>
+        <v>4.74526</v>
       </c>
       <c r="G8" t="n">
-        <v>13296</v>
+        <v>13304</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>532</v>
       </c>
       <c r="R8" t="n">
-        <v>11833</v>
+        <v>11841</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:14</t>
+          <t>2026-06-08 19:13:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:16</t>
+          <t>2026-06-08 19:13:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.85953</v>
+        <v>3.85868</v>
       </c>
       <c r="G10" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:19</t>
+          <t>2026-06-08 19:13:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66667</v>
+        <v>2.74194</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:21</t>
+          <t>2026-06-08 19:13:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7474</v>
+        <v>4.74627</v>
       </c>
       <c r="G12" t="n">
-        <v>2890</v>
+        <v>2893</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2572</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:23</t>
+          <t>2026-06-08 19:13:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:25</t>
+          <t>2026-06-08 19:13:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:28</t>
+          <t>2026-06-08 19:13:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-07 17:58:30</t>
+          <t>2026-06-08 19:13:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75033</v>
+        <v>4.7504</v>
       </c>
       <c r="G16" t="n">
-        <v>31305</v>
+        <v>31310</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1252</v>
       </c>
       <c r="R16" t="n">
-        <v>28174</v>
+        <v>28179</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:52</t>
+          <t>2026-06-09 19:06:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.625</v>
+        <v>4.64516</v>
       </c>
       <c r="G2" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:54</t>
+          <t>2026-06-09 19:06:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81738</v>
+        <v>4.81719</v>
       </c>
       <c r="G3" t="n">
-        <v>12540</v>
+        <v>12549</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>11662</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:57</t>
+          <t>2026-06-09 19:06:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:00</t>
+          <t>2026-06-09 19:06:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52948</v>
+        <v>2.52986</v>
       </c>
       <c r="G5" t="n">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -805,7 +805,7 @@
         <v>98</v>
       </c>
       <c r="R5" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:02</t>
+          <t>2026-06-09 19:06:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:05</t>
+          <t>2026-06-09 19:06:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:08</t>
+          <t>2026-06-09 19:06:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -982,7 +982,7 @@
         <v>4.74526</v>
       </c>
       <c r="G8" t="n">
-        <v>13304</v>
+        <v>13308</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>532</v>
       </c>
       <c r="R8" t="n">
-        <v>11841</v>
+        <v>11844</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:10</t>
+          <t>2026-06-09 19:06:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:13</t>
+          <t>2026-06-09 19:06:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:15</t>
+          <t>2026-06-09 19:06:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:18</t>
+          <t>2026-06-09 19:06:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74627</v>
+        <v>4.74646</v>
       </c>
       <c r="G12" t="n">
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2575</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:20</t>
+          <t>2026-06-09 19:06:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:22</t>
+          <t>2026-06-09 19:06:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:25</t>
+          <t>2026-06-09 19:06:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-08 19:13:28</t>
+          <t>2026-06-09 19:06:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7504</v>
+        <v>4.75032</v>
       </c>
       <c r="G16" t="n">
-        <v>31310</v>
+        <v>31316</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="O16" t="n">
         <v>313</v>
@@ -1594,10 +1594,10 @@
         <v>626</v>
       </c>
       <c r="Q16" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="R16" t="n">
-        <v>28179</v>
+        <v>28184</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:23</t>
+          <t>2026-06-10 19:28:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.64516</v>
+        <v>4.66258</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:26</t>
+          <t>2026-06-10 19:28:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81719</v>
+        <v>4.81722</v>
       </c>
       <c r="G3" t="n">
-        <v>12549</v>
+        <v>12556</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="n">
         <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>11671</v>
+        <v>11677</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:28</t>
+          <t>2026-06-10 19:28:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:31</t>
+          <t>2026-06-10 19:29:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52986</v>
+        <v>2.53189</v>
       </c>
       <c r="G5" t="n">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -805,7 +805,7 @@
         <v>98</v>
       </c>
       <c r="R5" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:33</t>
+          <t>2026-06-10 19:29:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.21212</v>
+        <v>3.21805</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>9</v>
@@ -874,10 +874,10 @@
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:36</t>
+          <t>2026-06-10 19:29:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0206</v>
+        <v>4.02088</v>
       </c>
       <c r="G7" t="n">
-        <v>3639</v>
+        <v>3640</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>2329</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:38</t>
+          <t>2026-06-10 19:29:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74526</v>
+        <v>4.74532</v>
       </c>
       <c r="G8" t="n">
-        <v>13308</v>
+        <v>13315</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O8" t="n">
         <v>133</v>
@@ -1018,10 +1018,10 @@
         <v>266</v>
       </c>
       <c r="Q8" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R8" t="n">
-        <v>11844</v>
+        <v>11850</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:41</t>
+          <t>2026-06-10 19:29:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:43</t>
+          <t>2026-06-10 19:29:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:45</t>
+          <t>2026-06-10 19:29:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 05, 2026</t>
+          <t>June 10, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:47</t>
+          <t>2026-06-10 19:29:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:50</t>
+          <t>2026-06-10 19:29:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:52</t>
+          <t>2026-06-10 19:29:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:54</t>
+          <t>2026-06-10 19:29:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:57</t>
+          <t>2026-06-10 19:29:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75032</v>
+        <v>4.75023</v>
       </c>
       <c r="G16" t="n">
-        <v>31316</v>
+        <v>31329</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>313</v>
       </c>
       <c r="P16" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Q16" t="n">
         <v>1253</v>
       </c>
       <c r="R16" t="n">
-        <v>28184</v>
+        <v>28196</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:54</t>
+          <t>2026-06-11 19:28:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.66258</v>
+        <v>4.66866</v>
       </c>
       <c r="G2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:56</t>
+          <t>2026-06-11 19:28:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81722</v>
+        <v>4.81673</v>
       </c>
       <c r="G3" t="n">
-        <v>12556</v>
+        <v>12561</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>11677</v>
+        <v>11682</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:58</t>
+          <t>2026-06-11 19:28:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88117</v>
+        <v>3.88141</v>
       </c>
       <c r="G4" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:01</t>
+          <t>2026-06-11 19:29:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53189</v>
+        <v>2.53208</v>
       </c>
       <c r="G5" t="n">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:03</t>
+          <t>2026-06-11 19:29:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:05</t>
+          <t>2026-06-11 19:29:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02088</v>
+        <v>4.02114</v>
       </c>
       <c r="G7" t="n">
-        <v>3640</v>
+        <v>3641</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O7" t="n">
         <v>146</v>
@@ -946,7 +946,7 @@
         <v>182</v>
       </c>
       <c r="Q7" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R7" t="n">
         <v>2330</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:08</t>
+          <t>2026-06-11 19:29:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74532</v>
+        <v>4.74486</v>
       </c>
       <c r="G8" t="n">
-        <v>13315</v>
+        <v>13322</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>533</v>
       </c>
       <c r="R8" t="n">
-        <v>11850</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:10</t>
+          <t>2026-06-11 19:29:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:12</t>
+          <t>2026-06-11 19:29:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:15</t>
+          <t>2026-06-11 19:29:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:17</t>
+          <t>2026-06-11 19:29:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74646</v>
+        <v>4.74662</v>
       </c>
       <c r="G12" t="n">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2577</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:19</t>
+          <t>2026-06-11 19:29:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:21</t>
+          <t>2026-06-11 19:29:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:24</t>
+          <t>2026-06-11 19:29:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-10 19:29:26</t>
+          <t>2026-06-11 19:29:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75023</v>
+        <v>4.7503</v>
       </c>
       <c r="G16" t="n">
-        <v>31329</v>
+        <v>31341</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="O16" t="n">
         <v>313</v>
@@ -1594,10 +1594,10 @@
         <v>627</v>
       </c>
       <c r="Q16" t="n">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="R16" t="n">
-        <v>28196</v>
+        <v>28207</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:53</t>
+          <t>2026-06-12 18:56:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:55</t>
+          <t>2026-06-12 18:56:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81673</v>
+        <v>4.81698</v>
       </c>
       <c r="G3" t="n">
-        <v>12561</v>
+        <v>12578</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>126</v>
       </c>
       <c r="Q3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>11682</v>
+        <v>11698</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:58</t>
+          <t>2026-06-12 18:56:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88141</v>
+        <v>3.88164</v>
       </c>
       <c r="G4" t="n">
-        <v>4781</v>
+        <v>4799</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="O4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q4" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="R4" t="n">
-        <v>2964</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:00</t>
+          <t>2026-06-12 18:56:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53208</v>
+        <v>2.53184</v>
       </c>
       <c r="G5" t="n">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -805,7 +805,7 @@
         <v>98</v>
       </c>
       <c r="R5" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:02</t>
+          <t>2026-06-12 18:56:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:04</t>
+          <t>2026-06-12 18:56:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02114</v>
+        <v>4.02005</v>
       </c>
       <c r="G7" t="n">
         <v>3641</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:06</t>
+          <t>2026-06-12 18:56:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74486</v>
+        <v>4.74516</v>
       </c>
       <c r="G8" t="n">
-        <v>13322</v>
+        <v>13334</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>133</v>
       </c>
       <c r="P8" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q8" t="n">
         <v>533</v>
       </c>
       <c r="R8" t="n">
-        <v>11857</v>
+        <v>11867</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:09</t>
+          <t>2026-06-12 18:56:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:11</t>
+          <t>2026-06-12 18:56:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.85868</v>
+        <v>3.8598</v>
       </c>
       <c r="G10" t="n">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.25</t>
+          <t>2.1.26</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>May 24, 2026</t>
+          <t>June 12, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1165,7 +1165,7 @@
         <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:13</t>
+          <t>2026-06-12 18:56:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.74194</v>
+        <v>2.82353</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 10, 2026</t>
+          <t>June 11, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:15</t>
+          <t>2026-06-12 18:56:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74662</v>
+        <v>4.74552</v>
       </c>
       <c r="G12" t="n">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2578</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:18</t>
+          <t>2026-06-12 18:56:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:20</t>
+          <t>2026-06-12 18:56:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:22</t>
+          <t>2026-06-12 18:56:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-11 19:29:24</t>
+          <t>2026-06-12 18:56:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7503</v>
+        <v>4.75018</v>
       </c>
       <c r="G16" t="n">
-        <v>31341</v>
+        <v>31354</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1254</v>
       </c>
       <c r="O16" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P16" t="n">
         <v>627</v>
@@ -1597,7 +1597,7 @@
         <v>1254</v>
       </c>
       <c r="R16" t="n">
-        <v>28207</v>
+        <v>27905</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:21</t>
+          <t>2026-06-13 18:02:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:23</t>
+          <t>2026-06-13 18:02:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81698</v>
+        <v>4.81705</v>
       </c>
       <c r="G3" t="n">
-        <v>12578</v>
+        <v>12583</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>11698</v>
+        <v>11702</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:26</t>
+          <t>2026-06-13 18:02:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88164</v>
+        <v>3.88211</v>
       </c>
       <c r="G4" t="n">
-        <v>4799</v>
+        <v>4801</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>384</v>
       </c>
       <c r="R4" t="n">
-        <v>2975</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:28</t>
+          <t>2026-06-13 18:02:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53184</v>
+        <v>2.53532</v>
       </c>
       <c r="G5" t="n">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:31</t>
+          <t>2026-06-13 18:02:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:33</t>
+          <t>2026-06-13 18:02:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02005</v>
+        <v>4.01949</v>
       </c>
       <c r="G7" t="n">
-        <v>3641</v>
+        <v>3643</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:36</t>
+          <t>2026-06-13 18:02:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74516</v>
+        <v>4.74471</v>
       </c>
       <c r="G8" t="n">
-        <v>13334</v>
+        <v>13338</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O8" t="n">
         <v>133</v>
@@ -1018,10 +1018,10 @@
         <v>267</v>
       </c>
       <c r="Q8" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="R8" t="n">
-        <v>11867</v>
+        <v>11871</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:38</t>
+          <t>2026-06-13 18:02:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:40</t>
+          <t>2026-06-13 18:02:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8598</v>
+        <v>3.86078</v>
       </c>
       <c r="G10" t="n">
         <v>1020</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:43</t>
+          <t>2026-06-13 18:02:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82353</v>
+        <v>2.77143</v>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:45</t>
+          <t>2026-06-13 18:02:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74552</v>
+        <v>4.74569</v>
       </c>
       <c r="G12" t="n">
-        <v>2900</v>
+        <v>2902</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:47</t>
+          <t>2026-06-13 18:03:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:50</t>
+          <t>2026-06-13 18:03:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:52</t>
+          <t>2026-06-13 18:03:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:54</t>
+          <t>2026-06-13 18:03:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75018</v>
+        <v>4.75037</v>
       </c>
       <c r="G16" t="n">
-        <v>31354</v>
+        <v>31359</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1254</v>
       </c>
       <c r="R16" t="n">
-        <v>27905</v>
+        <v>28223</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:32</t>
+          <t>2026-06-14 18:06:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:34</t>
+          <t>2026-06-14 18:06:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81705</v>
+        <v>4.81703</v>
       </c>
       <c r="G3" t="n">
-        <v>12583</v>
+        <v>12592</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O3" t="n">
         <v>126</v>
@@ -661,7 +661,7 @@
         <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>11702</v>
+        <v>11711</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:37</t>
+          <t>2026-06-14 18:06:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88211</v>
+        <v>3.88179</v>
       </c>
       <c r="G4" t="n">
-        <v>4801</v>
+        <v>4805</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="O4" t="n">
         <v>240</v>
@@ -733,7 +733,7 @@
         <v>384</v>
       </c>
       <c r="R4" t="n">
-        <v>2977</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:39</t>
+          <t>2026-06-14 18:06:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53532</v>
+        <v>2.53469</v>
       </c>
       <c r="G5" t="n">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:42</t>
+          <t>2026-06-14 18:06:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:44</t>
+          <t>2026-06-14 18:06:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01949</v>
+        <v>4.01922</v>
       </c>
       <c r="G7" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>2332</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:47</t>
+          <t>2026-06-14 18:06:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74471</v>
+        <v>4.74484</v>
       </c>
       <c r="G8" t="n">
-        <v>13338</v>
+        <v>13349</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>534</v>
       </c>
       <c r="R8" t="n">
-        <v>11871</v>
+        <v>11881</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:50</t>
+          <t>2026-06-14 18:07:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:52</t>
+          <t>2026-06-14 18:07:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.86078</v>
+        <v>3.8686</v>
       </c>
       <c r="G10" t="n">
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O10" t="n">
         <v>41</v>
@@ -1162,10 +1162,10 @@
         <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>653</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:55</t>
+          <t>2026-06-14 18:07:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:57</t>
+          <t>2026-06-14 18:07:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74569</v>
+        <v>4.74604</v>
       </c>
       <c r="G12" t="n">
         <v>2902</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-13 18:03:00</t>
+          <t>2026-06-14 18:07:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-13 18:03:02</t>
+          <t>2026-06-14 18:07:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-13 18:03:04</t>
+          <t>2026-06-14 18:07:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-13 18:03:07</t>
+          <t>2026-06-14 18:07:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75037</v>
+        <v>4.75049</v>
       </c>
       <c r="G16" t="n">
-        <v>31359</v>
+        <v>31370</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="O16" t="n">
         <v>314</v>
@@ -1594,10 +1594,10 @@
         <v>627</v>
       </c>
       <c r="Q16" t="n">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="R16" t="n">
-        <v>28223</v>
+        <v>28233</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:43</t>
+          <t>2026-06-15 20:19:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:45</t>
+          <t>2026-06-15 20:19:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81703</v>
+        <v>4.81683</v>
       </c>
       <c r="G3" t="n">
-        <v>12592</v>
+        <v>12600</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.43.0</t>
+          <t>4.44.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>June 07, 2026</t>
+          <t>June 15, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>11711</v>
+        <v>11718</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:48</t>
+          <t>2026-06-15 20:19:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88179</v>
+        <v>3.88202</v>
       </c>
       <c r="G4" t="n">
-        <v>4805</v>
+        <v>4806</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>384</v>
       </c>
       <c r="R4" t="n">
-        <v>2979</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:51</t>
+          <t>2026-06-15 20:19:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53469</v>
+        <v>2.55973</v>
       </c>
       <c r="G5" t="n">
-        <v>2450</v>
+        <v>2478</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1323</v>
+        <v>1338</v>
       </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R5" t="n">
-        <v>784</v>
+        <v>818</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:53</t>
+          <t>2026-06-15 20:19:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.21805</v>
+        <v>3.20455</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
         <v>9</v>
@@ -877,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:56</t>
+          <t>2026-06-15 20:19:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01922</v>
+        <v>4.01976</v>
       </c>
       <c r="G7" t="n">
-        <v>3642</v>
+        <v>3644</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>2331</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:58</t>
+          <t>2026-06-15 20:19:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74484</v>
+        <v>4.74448</v>
       </c>
       <c r="G8" t="n">
-        <v>13349</v>
+        <v>13365</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P8" t="n">
         <v>267</v>
       </c>
       <c r="Q8" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R8" t="n">
-        <v>11881</v>
+        <v>11895</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:01</t>
+          <t>2026-06-15 20:19:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:03</t>
+          <t>2026-06-15 20:20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8686</v>
+        <v>3.87078</v>
       </c>
       <c r="G10" t="n">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:06</t>
+          <t>2026-06-15 20:20:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.77143</v>
+        <v>2.83333</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:09</t>
+          <t>2026-06-15 20:20:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74604</v>
+        <v>4.74467</v>
       </c>
       <c r="G12" t="n">
-        <v>2902</v>
+        <v>2906</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="O12" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>145</v>
       </c>
       <c r="R12" t="n">
-        <v>2583</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:11</t>
+          <t>2026-06-15 20:20:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:14</t>
+          <t>2026-06-15 20:20:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:16</t>
+          <t>2026-06-15 20:20:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-14 18:07:19</t>
+          <t>2026-06-15 20:20:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75049</v>
+        <v>4.75037</v>
       </c>
       <c r="G16" t="n">
-        <v>31370</v>
+        <v>31379</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>June 07, 2026</t>
+          <t>June 14, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1591,13 +1591,13 @@
         <v>314</v>
       </c>
       <c r="P16" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Q16" t="n">
         <v>1255</v>
       </c>
       <c r="R16" t="n">
-        <v>28233</v>
+        <v>28241</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:41</t>
+          <t>2026-06-17 20:05:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:43</t>
+          <t>2026-06-17 20:05:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81683</v>
+        <v>4.81676</v>
       </c>
       <c r="G3" t="n">
-        <v>12600</v>
+        <v>12623</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O3" t="n">
         <v>126</v>
@@ -661,7 +661,7 @@
         <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>11718</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:46</t>
+          <t>2026-06-17 20:05:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88202</v>
+        <v>3.88152</v>
       </c>
       <c r="G4" t="n">
-        <v>4806</v>
+        <v>4811</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="O4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>2980</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:48</t>
+          <t>2026-06-17 20:05:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.55973</v>
+        <v>2.59825</v>
       </c>
       <c r="G5" t="n">
-        <v>2478</v>
+        <v>2529</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.4</t>
+          <t>10.6.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,23 +789,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>June 17, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R5" t="n">
-        <v>818</v>
+        <v>860</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:51</t>
+          <t>2026-06-17 20:05:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.20455</v>
+        <v>3.20301</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>9</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:53</t>
+          <t>2026-06-17 20:05:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01976</v>
+        <v>4.02031</v>
       </c>
       <c r="G7" t="n">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>May 07, 2026</t>
+          <t>June 17, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:56</t>
+          <t>2026-06-17 20:05:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74448</v>
+        <v>4.74313</v>
       </c>
       <c r="G8" t="n">
-        <v>13365</v>
+        <v>13396</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O8" t="n">
         <v>134</v>
       </c>
       <c r="P8" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q8" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R8" t="n">
-        <v>11895</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:58</t>
+          <t>2026-06-17 20:05:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61991</v>
+        <v>4.62045</v>
       </c>
       <c r="G9" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:00</t>
+          <t>2026-06-17 20:05:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87078</v>
+        <v>3.87187</v>
       </c>
       <c r="G10" t="n">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>228</v>
       </c>
       <c r="O10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
         <v>62</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:03</t>
+          <t>2026-06-17 20:05:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 11, 2026</t>
+          <t>June 17, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:05</t>
+          <t>2026-06-17 20:05:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74467</v>
+        <v>4.7451</v>
       </c>
       <c r="G12" t="n">
-        <v>2906</v>
+        <v>2911</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2586</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:07</t>
+          <t>2026-06-17 20:05:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:10</t>
+          <t>2026-06-17 20:05:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:12</t>
+          <t>2026-06-17 20:05:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-15 20:20:14</t>
+          <t>2026-06-17 20:05:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75037</v>
+        <v>4.75007</v>
       </c>
       <c r="G16" t="n">
-        <v>31379</v>
+        <v>31397</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="O16" t="n">
         <v>314</v>
@@ -1594,10 +1594,10 @@
         <v>628</v>
       </c>
       <c r="Q16" t="n">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="R16" t="n">
-        <v>28241</v>
+        <v>28257</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:14</t>
+          <t>2026-06-18 19:17:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.66866</v>
+        <v>4.67066</v>
       </c>
       <c r="G2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:17</t>
+          <t>2026-06-18 19:17:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81676</v>
+        <v>4.81649</v>
       </c>
       <c r="G3" t="n">
-        <v>12623</v>
+        <v>12626</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:19</t>
+          <t>2026-06-18 19:17:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:21</t>
+          <t>2026-06-18 19:18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.59825</v>
+        <v>2.62544</v>
       </c>
       <c r="G5" t="n">
-        <v>2529</v>
+        <v>2563</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:23</t>
+          <t>2026-06-18 19:18:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:26</t>
+          <t>2026-06-18 19:18:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02031</v>
+        <v>4.02058</v>
       </c>
       <c r="G7" t="n">
-        <v>3643</v>
+        <v>3644</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:28</t>
+          <t>2026-06-18 19:18:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74313</v>
+        <v>4.74388</v>
       </c>
       <c r="G8" t="n">
-        <v>13396</v>
+        <v>13408</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>536</v>
       </c>
       <c r="R8" t="n">
-        <v>11922</v>
+        <v>11933</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:30</t>
+          <t>2026-06-18 19:18:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:32</t>
+          <t>2026-06-18 19:18:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:34</t>
+          <t>2026-06-18 19:18:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:37</t>
+          <t>2026-06-18 19:18:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7451</v>
+        <v>4.74519</v>
       </c>
       <c r="G12" t="n">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:39</t>
+          <t>2026-06-18 19:18:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01919</v>
+        <v>4.02111</v>
       </c>
       <c r="G13" t="n">
         <v>521</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:41</t>
+          <t>2026-06-18 19:18:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:43</t>
+          <t>2026-06-18 19:18:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:45</t>
+          <t>2026-06-18 19:18:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75007</v>
+        <v>4.74998</v>
       </c>
       <c r="G16" t="n">
-        <v>31397</v>
+        <v>31402</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1256</v>
       </c>
       <c r="R16" t="n">
-        <v>28257</v>
+        <v>28262</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:54</t>
+          <t>2026-06-19 18:27:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.67066</v>
+        <v>4.66866</v>
       </c>
       <c r="G2" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:56</t>
+          <t>2026-06-19 18:27:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11742</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:58</t>
+          <t>2026-06-19 18:27:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:00</t>
+          <t>2026-06-19 18:27:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1307</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:02</t>
+          <t>2026-06-19 18:27:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:04</t>
+          <t>2026-06-19 18:27:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02058</v>
+        <v>4.02085</v>
       </c>
       <c r="G7" t="n">
-        <v>3644</v>
+        <v>3645</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:06</t>
+          <t>2026-06-19 18:27:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:08</t>
+          <t>2026-06-19 18:28:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:10</t>
+          <t>2026-06-19 18:28:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:12</t>
+          <t>2026-06-19 18:28:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:14</t>
+          <t>2026-06-19 18:28:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="O12" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2592</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:17</t>
+          <t>2026-06-19 18:28:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:19</t>
+          <t>2026-06-19 18:28:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:21</t>
+          <t>2026-06-19 18:28:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-18 19:18:23</t>
+          <t>2026-06-19 18:28:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74998</v>
+        <v>4.7497</v>
       </c>
       <c r="G16" t="n">
-        <v>31402</v>
+        <v>31418</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="O16" t="n">
         <v>314</v>
@@ -1594,10 +1594,10 @@
         <v>628</v>
       </c>
       <c r="Q16" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="R16" t="n">
-        <v>28262</v>
+        <v>27962</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:44</t>
+          <t>2026-06-20 18:04:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.66866</v>
+        <v>4.67066</v>
       </c>
       <c r="G2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:46</t>
+          <t>2026-06-20 18:04:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81649</v>
+        <v>4.8167</v>
       </c>
       <c r="G3" t="n">
-        <v>12626</v>
+        <v>12641</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.0</t>
+          <t>4.44.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>June 15, 2026</t>
+          <t>June 19, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>253</v>
       </c>
       <c r="R3" t="n">
-        <v>11742</v>
+        <v>11756</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:49</t>
+          <t>2026-06-20 18:04:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:51</t>
+          <t>2026-06-20 18:04:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.62544</v>
+        <v>2.65836</v>
       </c>
       <c r="G5" t="n">
-        <v>2563</v>
+        <v>2608</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1307</v>
+        <v>1330</v>
       </c>
       <c r="O5" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P5" t="n">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="Q5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R5" t="n">
-        <v>897</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:53</t>
+          <t>2026-06-20 18:04:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:55</t>
+          <t>2026-06-20 18:04:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02085</v>
+        <v>4.02029</v>
       </c>
       <c r="G7" t="n">
-        <v>3645</v>
+        <v>3648</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O7" t="n">
         <v>146</v>
@@ -949,7 +949,7 @@
         <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:58</t>
+          <t>2026-06-20 18:04:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74388</v>
+        <v>4.74423</v>
       </c>
       <c r="G8" t="n">
-        <v>13408</v>
+        <v>13426</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O8" t="n">
         <v>134</v>
       </c>
       <c r="P8" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q8" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="R8" t="n">
-        <v>11933</v>
+        <v>11949</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:00</t>
+          <t>2026-06-20 18:04:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:02</t>
+          <t>2026-06-20 18:04:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:05</t>
+          <t>2026-06-20 18:04:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.83333</v>
+        <v>2.84211</v>
       </c>
       <c r="G11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 17, 2026</t>
+          <t>June 20, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:07</t>
+          <t>2026-06-20 18:04:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74519</v>
+        <v>4.74408</v>
       </c>
       <c r="G12" t="n">
-        <v>2912</v>
+        <v>2915</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2563</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:09</t>
+          <t>2026-06-20 18:04:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:11</t>
+          <t>2026-06-20 18:04:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:13</t>
+          <t>2026-06-20 18:04:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-19 18:28:16</t>
+          <t>2026-06-20 18:04:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7497</v>
+        <v>4.74964</v>
       </c>
       <c r="G16" t="n">
-        <v>31418</v>
+        <v>31423</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1257</v>
       </c>
       <c r="R16" t="n">
-        <v>27962</v>
+        <v>27966</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:19</t>
+          <t>2026-06-21 18:14:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:21</t>
+          <t>2026-06-21 18:14:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8167</v>
+        <v>4.81616</v>
       </c>
       <c r="G3" t="n">
-        <v>12641</v>
+        <v>12647</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:24</t>
+          <t>2026-06-21 18:14:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:26</t>
+          <t>2026-06-21 18:14:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.65836</v>
+        <v>2.65952</v>
       </c>
       <c r="G5" t="n">
-        <v>2608</v>
+        <v>2611</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:28</t>
+          <t>2026-06-21 18:14:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:30</t>
+          <t>2026-06-21 18:14:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02029</v>
+        <v>4.02055</v>
       </c>
       <c r="G7" t="n">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:33</t>
+          <t>2026-06-21 18:14:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74423</v>
+        <v>4.74418</v>
       </c>
       <c r="G8" t="n">
-        <v>13426</v>
+        <v>13436</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:35</t>
+          <t>2026-06-21 18:14:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:37</t>
+          <t>2026-06-21 18:14:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:40</t>
+          <t>2026-06-21 18:14:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:42</t>
+          <t>2026-06-21 18:14:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74408</v>
+        <v>4.74186</v>
       </c>
       <c r="G12" t="n">
-        <v>2915</v>
+        <v>2917</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:44</t>
+          <t>2026-06-21 18:14:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:46</t>
+          <t>2026-06-21 18:14:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:48</t>
+          <t>2026-06-21 18:14:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:51</t>
+          <t>2026-06-21 18:14:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74964</v>
+        <v>4.74962</v>
       </c>
       <c r="G16" t="n">
-        <v>31423</v>
+        <v>31428</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>27966</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:31</t>
+          <t>2026-06-22 19:59:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:33</t>
+          <t>2026-06-22 19:59:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81616</v>
+        <v>4.81583</v>
       </c>
       <c r="G3" t="n">
-        <v>12647</v>
+        <v>12652</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11766</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:35</t>
+          <t>2026-06-22 19:59:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88152</v>
+        <v>3.88111</v>
       </c>
       <c r="G4" t="n">
         <v>4811</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:36</t>
+          <t>2026-06-22 19:59:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.65952</v>
+        <v>2.68318</v>
       </c>
       <c r="G5" t="n">
-        <v>2611</v>
+        <v>2645</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1349</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:38</t>
+          <t>2026-06-22 19:59:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:40</t>
+          <t>2026-06-22 19:59:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02055</v>
+        <v>4.02029</v>
       </c>
       <c r="G7" t="n">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:42</t>
+          <t>2026-06-22 19:59:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74418</v>
+        <v>4.74407</v>
       </c>
       <c r="G8" t="n">
-        <v>13436</v>
+        <v>13445</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>11966</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:44</t>
+          <t>2026-06-22 19:59:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:46</t>
+          <t>2026-06-22 19:59:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87187</v>
+        <v>3.87404</v>
       </c>
       <c r="G10" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:47</t>
+          <t>2026-06-22 20:00:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:49</t>
+          <t>2026-06-22 20:00:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74186</v>
+        <v>4.74314</v>
       </c>
       <c r="G12" t="n">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:51</t>
+          <t>2026-06-22 20:00:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:53</t>
+          <t>2026-06-22 20:00:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:55</t>
+          <t>2026-06-22 20:00:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:56</t>
+          <t>2026-06-22 20:00:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74962</v>
+        <v>4.74966</v>
       </c>
       <c r="G16" t="n">
-        <v>31428</v>
+        <v>31433</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>27975</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:40</t>
+          <t>2026-06-23 18:59:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:42</t>
+          <t>2026-06-23 18:59:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:45</t>
+          <t>2026-06-23 18:59:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:47</t>
+          <t>2026-06-23 18:59:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1349</v>
+        <v>1322</v>
       </c>
       <c r="O5" t="n">
         <v>159</v>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="n">
         <v>106</v>
       </c>
       <c r="R5" t="n">
-        <v>952</v>
+        <v>979</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:49</t>
+          <t>2026-06-23 18:59:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:51</t>
+          <t>2026-06-23 18:59:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:54</t>
+          <t>2026-06-23 18:59:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:57</t>
+          <t>2026-06-23 18:59:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:59</t>
+          <t>2026-06-23 18:59:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:01</t>
+          <t>2026-06-23 18:59:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:04</t>
+          <t>2026-06-23 18:59:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="O12" t="n">
         <v>29</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:06</t>
+          <t>2026-06-23 18:59:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:08</t>
+          <t>2026-06-23 18:59:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:10</t>
+          <t>2026-06-23 18:59:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-22 20:00:13</t>
+          <t>2026-06-23 18:59:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:26</t>
+          <t>2026-06-24 18:26:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:28</t>
+          <t>2026-06-24 18:26:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81583</v>
+        <v>4.81497</v>
       </c>
       <c r="G3" t="n">
-        <v>12652</v>
+        <v>12668</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>253</v>
       </c>
       <c r="R3" t="n">
-        <v>11766</v>
+        <v>11781</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:31</t>
+          <t>2026-06-24 18:26:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88111</v>
+        <v>3.88097</v>
       </c>
       <c r="G4" t="n">
-        <v>4811</v>
+        <v>4814</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="O4" t="n">
         <v>241</v>
@@ -733,7 +733,7 @@
         <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>2983</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:33</t>
+          <t>2026-06-24 18:26:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.68318</v>
+        <v>2.72872</v>
       </c>
       <c r="G5" t="n">
-        <v>2645</v>
+        <v>2702</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1322</v>
+        <v>1351</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="P5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q5" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R5" t="n">
-        <v>979</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:35</t>
+          <t>2026-06-24 18:26:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.20301</v>
+        <v>3.20149</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
         <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:37</t>
+          <t>2026-06-24 18:26:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02029</v>
+        <v>4.01998</v>
       </c>
       <c r="G7" t="n">
-        <v>3647</v>
+        <v>3653</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>146</v>
       </c>
       <c r="P7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q7" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R7" t="n">
-        <v>2334</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:39</t>
+          <t>2026-06-24 18:26:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74407</v>
+        <v>4.74427</v>
       </c>
       <c r="G8" t="n">
-        <v>13445</v>
+        <v>13471</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>11966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:41</t>
+          <t>2026-06-24 18:26:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:44</t>
+          <t>2026-06-24 18:26:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:46</t>
+          <t>2026-06-24 18:26:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:48</t>
+          <t>2026-06-24 18:26:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74314</v>
+        <v>4.73937</v>
       </c>
       <c r="G12" t="n">
-        <v>2916</v>
+        <v>2920</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:50</t>
+          <t>2026-06-24 18:26:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:53</t>
+          <t>2026-06-24 18:26:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:55</t>
+          <t>2026-06-24 18:26:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:57</t>
+          <t>2026-06-24 18:26:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74966</v>
+        <v>4.74891</v>
       </c>
       <c r="G16" t="n">
-        <v>31433</v>
+        <v>31471</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>27975</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:23</t>
+          <t>2026-06-25 19:00:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:26</t>
+          <t>2026-06-25 19:00:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81497</v>
+        <v>4.81493</v>
       </c>
       <c r="G3" t="n">
-        <v>12668</v>
+        <v>12676</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>127</v>
       </c>
       <c r="Q3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>11781</v>
+        <v>11789</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:28</t>
+          <t>2026-06-25 19:00:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:30</t>
+          <t>2026-06-25 19:00:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.72872</v>
+        <v>2.74817</v>
       </c>
       <c r="G5" t="n">
-        <v>2702</v>
+        <v>2728</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="O5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R5" t="n">
-        <v>1000</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:33</t>
+          <t>2026-06-25 19:00:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.20149</v>
+        <v>3.18519</v>
       </c>
       <c r="G6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>9</v>
@@ -874,10 +874,10 @@
         <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:35</t>
+          <t>2026-06-25 19:00:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01998</v>
+        <v>4.0186</v>
       </c>
       <c r="G7" t="n">
-        <v>3653</v>
+        <v>3655</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O7" t="n">
         <v>146</v>
@@ -949,7 +949,7 @@
         <v>402</v>
       </c>
       <c r="R7" t="n">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:37</t>
+          <t>2026-06-25 19:00:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74427</v>
+        <v>4.74247</v>
       </c>
       <c r="G8" t="n">
-        <v>13471</v>
+        <v>13486</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:39</t>
+          <t>2026-06-25 19:00:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:41</t>
+          <t>2026-06-25 19:00:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:43</t>
+          <t>2026-06-25 19:00:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:45</t>
+          <t>2026-06-25 19:00:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73937</v>
+        <v>4.73812</v>
       </c>
       <c r="G12" t="n">
-        <v>2920</v>
+        <v>2925</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:47</t>
+          <t>2026-06-25 19:00:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:49</t>
+          <t>2026-06-25 19:00:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:51</t>
+          <t>2026-06-25 19:00:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:53</t>
+          <t>2026-06-25 19:00:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74891</v>
+        <v>4.74898</v>
       </c>
       <c r="G16" t="n">
-        <v>31471</v>
+        <v>31492</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>28028</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:16</t>
+          <t>2026-06-26 18:20:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:18</t>
+          <t>2026-06-26 18:20:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81493</v>
+        <v>4.81496</v>
       </c>
       <c r="G3" t="n">
-        <v>12676</v>
+        <v>12689</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O3" t="n">
         <v>127</v>
@@ -661,7 +661,7 @@
         <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>11789</v>
+        <v>11801</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:21</t>
+          <t>2026-06-26 18:20:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88097</v>
+        <v>3.88037</v>
       </c>
       <c r="G4" t="n">
-        <v>4814</v>
+        <v>4815</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:23</t>
+          <t>2026-06-26 18:20:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.74817</v>
+        <v>2.7744</v>
       </c>
       <c r="G5" t="n">
-        <v>2728</v>
+        <v>2766</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1337</v>
+        <v>1355</v>
       </c>
       <c r="O5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R5" t="n">
-        <v>1037</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:25</t>
+          <t>2026-06-26 18:20:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:27</t>
+          <t>2026-06-26 18:20:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:29</t>
+          <t>2026-06-26 18:20:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74247</v>
+        <v>4.74218</v>
       </c>
       <c r="G8" t="n">
-        <v>13486</v>
+        <v>13498</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O8" t="n">
         <v>135</v>
@@ -1018,10 +1018,10 @@
         <v>270</v>
       </c>
       <c r="Q8" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R8" t="n">
-        <v>12003</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:32</t>
+          <t>2026-06-26 18:20:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:34</t>
+          <t>2026-06-26 18:20:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87404</v>
+        <v>3.87512</v>
       </c>
       <c r="G10" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:36</t>
+          <t>2026-06-26 18:20:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84211</v>
+        <v>2.79487</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:38</t>
+          <t>2026-06-26 18:20:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73812</v>
+        <v>4.7382</v>
       </c>
       <c r="G12" t="n">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1303,13 +1303,13 @@
         <v>29</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q12" t="n">
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2574</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:41</t>
+          <t>2026-06-26 18:20:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:43</t>
+          <t>2026-06-26 18:20:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.50413</v>
+        <v>3.51029</v>
       </c>
       <c r="G14" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:45</t>
+          <t>2026-06-26 18:20:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:47</t>
+          <t>2026-06-26 18:20:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74898</v>
+        <v>4.7489</v>
       </c>
       <c r="G16" t="n">
-        <v>31492</v>
+        <v>31509</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1260</v>
       </c>
       <c r="R16" t="n">
-        <v>28028</v>
+        <v>28043</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:16</t>
+          <t>2026-06-27 17:53:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:18</t>
+          <t>2026-06-27 17:53:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81496</v>
+        <v>4.81506</v>
       </c>
       <c r="G3" t="n">
-        <v>12689</v>
+        <v>12696</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>11801</v>
+        <v>11807</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:21</t>
+          <t>2026-06-27 17:53:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:23</t>
+          <t>2026-06-27 17:53:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7744</v>
+        <v>2.7736</v>
       </c>
       <c r="G5" t="n">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:25</t>
+          <t>2026-06-27 17:53:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:27</t>
+          <t>2026-06-27 17:53:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0186</v>
+        <v>4.0194</v>
       </c>
       <c r="G7" t="n">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>402</v>
       </c>
       <c r="R7" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:29</t>
+          <t>2026-06-27 17:53:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74218</v>
+        <v>4.74252</v>
       </c>
       <c r="G8" t="n">
-        <v>13498</v>
+        <v>13504</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>540</v>
       </c>
       <c r="R8" t="n">
-        <v>12013</v>
+        <v>12019</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:32</t>
+          <t>2026-06-27 17:53:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:34</t>
+          <t>2026-06-27 17:53:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:36</t>
+          <t>2026-06-27 17:53:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.79487</v>
+        <v>2.84211</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:38</t>
+          <t>2026-06-27 17:53:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7382</v>
+        <v>4.73726</v>
       </c>
       <c r="G12" t="n">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2575</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:40</t>
+          <t>2026-06-27 17:53:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:43</t>
+          <t>2026-06-27 17:53:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:45</t>
+          <t>2026-06-27 17:54:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:47</t>
+          <t>2026-06-27 17:54:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7489</v>
+        <v>4.7484</v>
       </c>
       <c r="G16" t="n">
-        <v>31509</v>
+        <v>31518</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="O16" t="n">
         <v>315</v>
@@ -1594,10 +1594,10 @@
         <v>630</v>
       </c>
       <c r="Q16" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="R16" t="n">
-        <v>28043</v>
+        <v>28051</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:31</t>
+          <t>2026-06-28 17:56:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:33</t>
+          <t>2026-06-28 17:56:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81506</v>
+        <v>4.81485</v>
       </c>
       <c r="G3" t="n">
-        <v>12696</v>
+        <v>12703</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>11807</v>
+        <v>11814</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:36</t>
+          <t>2026-06-28 17:56:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88037</v>
+        <v>3.88097</v>
       </c>
       <c r="G4" t="n">
-        <v>4815</v>
+        <v>4814</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:38</t>
+          <t>2026-06-28 17:56:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7736</v>
+        <v>2.77473</v>
       </c>
       <c r="G5" t="n">
-        <v>2765</v>
+        <v>2770</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="O5" t="n">
         <v>166</v>
@@ -805,7 +805,7 @@
         <v>111</v>
       </c>
       <c r="R5" t="n">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:40</t>
+          <t>2026-06-28 17:56:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:43</t>
+          <t>2026-06-28 17:57:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>4.0194</v>
       </c>
       <c r="G7" t="n">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>402</v>
       </c>
       <c r="R7" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:45</t>
+          <t>2026-06-28 17:57:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74252</v>
+        <v>4.74273</v>
       </c>
       <c r="G8" t="n">
-        <v>13504</v>
+        <v>13511</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>540</v>
       </c>
       <c r="R8" t="n">
-        <v>12019</v>
+        <v>12025</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:47</t>
+          <t>2026-06-28 17:57:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:49</t>
+          <t>2026-06-28 17:57:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87512</v>
+        <v>3.8762</v>
       </c>
       <c r="G10" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
         <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:52</t>
+          <t>2026-06-28 17:57:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:54</t>
+          <t>2026-06-28 17:57:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73726</v>
+        <v>4.73736</v>
       </c>
       <c r="G12" t="n">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>146</v>
       </c>
       <c r="R12" t="n">
-        <v>2576</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:56</t>
+          <t>2026-06-28 17:57:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:58</t>
+          <t>2026-06-28 17:57:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 17:54:01</t>
+          <t>2026-06-28 17:57:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 17:54:03</t>
+          <t>2026-06-28 17:57:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7484</v>
+        <v>4.74833</v>
       </c>
       <c r="G16" t="n">
-        <v>31518</v>
+        <v>31526</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>315</v>
       </c>
       <c r="P16" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Q16" t="n">
         <v>1261</v>
       </c>
       <c r="R16" t="n">
-        <v>28051</v>
+        <v>28058</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:49</t>
+          <t>2026-06-29 18:56:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:51</t>
+          <t>2026-06-29 18:56:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81485</v>
+        <v>4.81493</v>
       </c>
       <c r="G3" t="n">
-        <v>12703</v>
+        <v>12714</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.1</t>
+          <t>4.44.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>June 19, 2026</t>
+          <t>June 29, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>254</v>
       </c>
       <c r="R3" t="n">
-        <v>11814</v>
+        <v>11824</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:54</t>
+          <t>2026-06-29 18:56:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88097</v>
+        <v>3.88037</v>
       </c>
       <c r="G4" t="n">
-        <v>4814</v>
+        <v>4815</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:56</t>
+          <t>2026-06-29 18:56:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.77473</v>
+        <v>2.79886</v>
       </c>
       <c r="G5" t="n">
-        <v>2770</v>
+        <v>2804</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1357</v>
+        <v>1346</v>
       </c>
       <c r="O5" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="P5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R5" t="n">
-        <v>1053</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:59</t>
+          <t>2026-06-29 18:56:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:01</t>
+          <t>2026-06-29 18:56:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0194</v>
+        <v>4.01994</v>
       </c>
       <c r="G7" t="n">
-        <v>3658</v>
+        <v>3660</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O7" t="n">
         <v>146</v>
@@ -946,10 +946,10 @@
         <v>183</v>
       </c>
       <c r="Q7" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="R7" t="n">
-        <v>2341</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:03</t>
+          <t>2026-06-29 18:56:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74273</v>
+        <v>4.74235</v>
       </c>
       <c r="G8" t="n">
-        <v>13511</v>
+        <v>13526</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O8" t="n">
         <v>135</v>
       </c>
       <c r="P8" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q8" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="R8" t="n">
-        <v>12025</v>
+        <v>12038</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:05</t>
+          <t>2026-06-29 18:56:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:08</t>
+          <t>2026-06-29 18:56:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:10</t>
+          <t>2026-06-29 18:56:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:13</t>
+          <t>2026-06-29 18:56:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73736</v>
+        <v>4.7379</v>
       </c>
       <c r="G12" t="n">
-        <v>2928</v>
+        <v>2934</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>59</v>
       </c>
       <c r="Q12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2577</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:15</t>
+          <t>2026-06-29 18:56:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:17</t>
+          <t>2026-06-29 18:56:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:19</t>
+          <t>2026-06-29 18:56:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-28 17:57:22</t>
+          <t>2026-06-29 18:56:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74833</v>
+        <v>4.74802</v>
       </c>
       <c r="G16" t="n">
-        <v>31526</v>
+        <v>31546</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="O16" t="n">
         <v>315</v>
@@ -1594,10 +1594,10 @@
         <v>631</v>
       </c>
       <c r="Q16" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="R16" t="n">
-        <v>28058</v>
+        <v>28076</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:20</t>
+          <t>2026-06-30 18:27:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:22</t>
+          <t>2026-06-30 18:27:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:25</t>
+          <t>2026-06-30 18:27:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:27</t>
+          <t>2026-06-30 18:27:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.79886</v>
+        <v>2.81363</v>
       </c>
       <c r="G5" t="n">
-        <v>2804</v>
+        <v>2833</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="O5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R5" t="n">
-        <v>1094</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:29</t>
+          <t>2026-06-30 18:27:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:31</t>
+          <t>2026-06-30 18:27:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01994</v>
+        <v>4.01884</v>
       </c>
       <c r="G7" t="n">
-        <v>3660</v>
+        <v>3662</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>403</v>
       </c>
       <c r="R7" t="n">
-        <v>2342</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:34</t>
+          <t>2026-06-30 18:27:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:36</t>
+          <t>2026-06-30 18:27:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:38</t>
+          <t>2026-06-30 18:27:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:40</t>
+          <t>2026-06-30 18:27:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:43</t>
+          <t>2026-06-30 18:27:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7379</v>
+        <v>4.73953</v>
       </c>
       <c r="G12" t="n">
-        <v>2934</v>
+        <v>2937</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2582</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:45</t>
+          <t>2026-06-30 18:27:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:48</t>
+          <t>2026-06-30 18:27:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:50</t>
+          <t>2026-06-30 18:27:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:52</t>
+          <t>2026-06-30 18:27:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74802</v>
+        <v>4.74777</v>
       </c>
       <c r="G16" t="n">
-        <v>31546</v>
+        <v>31559</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1262</v>
       </c>
       <c r="O16" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P16" t="n">
         <v>631</v>
@@ -1597,7 +1597,7 @@
         <v>1262</v>
       </c>
       <c r="R16" t="n">
-        <v>28076</v>
+        <v>28088</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:14</t>
+          <t>2026-07-01 18:53:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:17</t>
+          <t>2026-07-01 18:53:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81493</v>
+        <v>4.81487</v>
       </c>
       <c r="G3" t="n">
-        <v>12714</v>
+        <v>12732</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O3" t="n">
         <v>127</v>
@@ -658,10 +658,10 @@
         <v>127</v>
       </c>
       <c r="Q3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R3" t="n">
-        <v>11824</v>
+        <v>11841</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:19</t>
+          <t>2026-07-01 18:53:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:21</t>
+          <t>2026-07-01 18:53:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.81363</v>
+        <v>2.82491</v>
       </c>
       <c r="G5" t="n">
-        <v>2833</v>
+        <v>2850</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="O5" t="n">
         <v>142</v>
       </c>
       <c r="P5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R5" t="n">
-        <v>1105</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:23</t>
+          <t>2026-07-01 18:53:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:26</t>
+          <t>2026-07-01 18:53:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01884</v>
+        <v>4.01855</v>
       </c>
       <c r="G7" t="n">
-        <v>3662</v>
+        <v>3665</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>586</v>
       </c>
       <c r="O7" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P7" t="n">
         <v>183</v>
@@ -949,7 +949,7 @@
         <v>403</v>
       </c>
       <c r="R7" t="n">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:28</t>
+          <t>2026-07-01 18:53:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74235</v>
+        <v>4.74184</v>
       </c>
       <c r="G8" t="n">
-        <v>13526</v>
+        <v>13542</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O8" t="n">
         <v>135</v>
@@ -1018,10 +1018,10 @@
         <v>271</v>
       </c>
       <c r="Q8" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="R8" t="n">
-        <v>12038</v>
+        <v>12052</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:30</t>
+          <t>2026-07-01 18:53:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:32</t>
+          <t>2026-07-01 18:54:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8762</v>
+        <v>3.87452</v>
       </c>
       <c r="G10" t="n">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O10" t="n">
         <v>42</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:34</t>
+          <t>2026-07-01 18:54:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:37</t>
+          <t>2026-07-01 18:54:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73953</v>
+        <v>4.7397</v>
       </c>
       <c r="G12" t="n">
-        <v>2937</v>
+        <v>2939</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O12" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2585</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:39</t>
+          <t>2026-07-01 18:54:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:41</t>
+          <t>2026-07-01 18:54:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:44</t>
+          <t>2026-07-01 18:54:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:46</t>
+          <t>2026-07-01 18:54:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74777</v>
+        <v>4.74674</v>
       </c>
       <c r="G16" t="n">
-        <v>31559</v>
+        <v>31565</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="O16" t="n">
         <v>316</v>
@@ -1594,10 +1594,10 @@
         <v>631</v>
       </c>
       <c r="Q16" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="R16" t="n">
-        <v>28088</v>
+        <v>28093</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:42</t>
+          <t>2026-07-02 18:22:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.67066</v>
+        <v>4.67262</v>
       </c>
       <c r="G2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>May 07, 2026</t>
+          <t>July 02, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:44</t>
+          <t>2026-07-02 18:22:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81487</v>
+        <v>4.81449</v>
       </c>
       <c r="G3" t="n">
-        <v>12732</v>
+        <v>12743</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>255</v>
       </c>
       <c r="R3" t="n">
-        <v>11841</v>
+        <v>11851</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:46</t>
+          <t>2026-07-02 18:22:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:49</t>
+          <t>2026-07-02 18:22:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82491</v>
+        <v>2.84306</v>
       </c>
       <c r="G5" t="n">
-        <v>2850</v>
+        <v>2880</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1368</v>
+        <v>1354</v>
       </c>
       <c r="O5" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P5" t="n">
         <v>86</v>
       </c>
       <c r="Q5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R5" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:51</t>
+          <t>2026-07-02 18:22:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:53</t>
+          <t>2026-07-02 18:22:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01855</v>
+        <v>4.01882</v>
       </c>
       <c r="G7" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O7" t="n">
         <v>147</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:55</t>
+          <t>2026-07-02 18:22:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74184</v>
+        <v>4.74146</v>
       </c>
       <c r="G8" t="n">
-        <v>13542</v>
+        <v>13561</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>542</v>
       </c>
       <c r="O8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P8" t="n">
         <v>271</v>
@@ -1021,7 +1021,7 @@
         <v>542</v>
       </c>
       <c r="R8" t="n">
-        <v>12052</v>
+        <v>12069</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:58</t>
+          <t>2026-07-02 18:22:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:00</t>
+          <t>2026-07-02 18:22:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.26</t>
+          <t>2.1.27</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>June 12, 2026</t>
+          <t>July 02, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:03</t>
+          <t>2026-07-02 18:22:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:05</t>
+          <t>2026-07-02 18:22:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7397</v>
+        <v>4.7398</v>
       </c>
       <c r="G12" t="n">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2586</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:07</t>
+          <t>2026-07-02 18:22:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:10</t>
+          <t>2026-07-02 18:22:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:12</t>
+          <t>2026-07-02 18:22:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-01 18:54:14</t>
+          <t>2026-07-02 18:22:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74674</v>
+        <v>4.7464</v>
       </c>
       <c r="G16" t="n">
-        <v>31565</v>
+        <v>31581</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>316</v>
       </c>
       <c r="P16" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Q16" t="n">
         <v>1263</v>
       </c>
       <c r="R16" t="n">
-        <v>28093</v>
+        <v>28107</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:10</t>
+          <t>2026-07-03 18:06:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:13</t>
+          <t>2026-07-03 18:06:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81449</v>
+        <v>4.81456</v>
       </c>
       <c r="G3" t="n">
-        <v>12743</v>
+        <v>12759</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q3" t="n">
         <v>255</v>
       </c>
       <c r="R3" t="n">
-        <v>11851</v>
+        <v>11866</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:15</t>
+          <t>2026-07-03 18:06:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88037</v>
+        <v>3.88061</v>
       </c>
       <c r="G4" t="n">
-        <v>4815</v>
+        <v>4816</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>2985</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:18</t>
+          <t>2026-07-03 18:06:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84306</v>
+        <v>2.85433</v>
       </c>
       <c r="G5" t="n">
-        <v>2880</v>
+        <v>2897</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="O5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>1152</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:20</t>
+          <t>2026-07-03 18:06:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:23</t>
+          <t>2026-07-03 18:06:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:25</t>
+          <t>2026-07-03 18:06:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74146</v>
+        <v>4.74125</v>
       </c>
       <c r="G8" t="n">
-        <v>13561</v>
+        <v>13569</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>271</v>
       </c>
       <c r="Q8" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R8" t="n">
-        <v>12069</v>
+        <v>12076</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:28</t>
+          <t>2026-07-03 18:06:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:31</t>
+          <t>2026-07-03 18:06:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:33</t>
+          <t>2026-07-03 18:06:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:35</t>
+          <t>2026-07-03 18:06:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7398</v>
+        <v>4.74015</v>
       </c>
       <c r="G12" t="n">
-        <v>2940</v>
+        <v>2944</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2587</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:38</t>
+          <t>2026-07-03 18:07:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:40</t>
+          <t>2026-07-03 18:07:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:43</t>
+          <t>2026-07-03 18:07:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:45</t>
+          <t>2026-07-03 18:07:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>4.7464</v>
       </c>
       <c r="G16" t="n">
-        <v>31581</v>
+        <v>31593</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="O16" t="n">
         <v>316</v>
@@ -1594,10 +1594,10 @@
         <v>632</v>
       </c>
       <c r="Q16" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="R16" t="n">
-        <v>28107</v>
+        <v>28118</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:37</t>
+          <t>2026-07-04 17:53:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:39</t>
+          <t>2026-07-04 17:53:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:42</t>
+          <t>2026-07-04 17:53:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:44</t>
+          <t>2026-07-04 17:53:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:46</t>
+          <t>2026-07-04 17:53:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:48</t>
+          <t>2026-07-04 17:53:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:50</t>
+          <t>2026-07-04 17:53:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:52</t>
+          <t>2026-07-04 17:53:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:55</t>
+          <t>2026-07-04 17:53:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:57</t>
+          <t>2026-07-04 17:53:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:59</t>
+          <t>2026-07-04 17:53:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03 18:07:01</t>
+          <t>2026-07-04 17:53:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 18:07:03</t>
+          <t>2026-07-04 17:53:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03 18:07:06</t>
+          <t>2026-07-04 17:53:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03 18:07:08</t>
+          <t>2026-07-04 17:53:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:22</t>
+          <t>2026-07-05 17:54:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:25</t>
+          <t>2026-07-05 17:54:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81456</v>
+        <v>4.81451</v>
       </c>
       <c r="G3" t="n">
-        <v>12759</v>
+        <v>12777</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>128</v>
       </c>
       <c r="Q3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R3" t="n">
-        <v>11866</v>
+        <v>11883</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:27</t>
+          <t>2026-07-05 17:54:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88061</v>
+        <v>3.88084</v>
       </c>
       <c r="G4" t="n">
-        <v>4816</v>
+        <v>4817</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>2986</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:29</t>
+          <t>2026-07-05 17:54:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85433</v>
+        <v>2.85186</v>
       </c>
       <c r="G5" t="n">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10.6.5</t>
+          <t>10.6.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -789,11 +789,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>June 17, 2026</t>
+          <t>July 05, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="O5" t="n">
         <v>145</v>
@@ -805,7 +805,7 @@
         <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:32</t>
+          <t>2026-07-05 17:54:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.18519</v>
+        <v>3.16912</v>
       </c>
       <c r="G6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
         <v>8</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:34</t>
+          <t>2026-07-05 17:54:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01882</v>
+        <v>4.01827</v>
       </c>
       <c r="G7" t="n">
-        <v>3666</v>
+        <v>3668</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>403</v>
       </c>
       <c r="R7" t="n">
-        <v>2346</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:37</t>
+          <t>2026-07-05 17:54:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74125</v>
+        <v>4.74153</v>
       </c>
       <c r="G8" t="n">
-        <v>13569</v>
+        <v>13580</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q8" t="n">
         <v>543</v>
       </c>
       <c r="R8" t="n">
-        <v>12076</v>
+        <v>12086</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:39</t>
+          <t>2026-07-05 17:54:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.62045</v>
+        <v>4.61958</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:42</t>
+          <t>2026-07-05 17:54:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87452</v>
+        <v>3.8756</v>
       </c>
       <c r="G10" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:44</t>
+          <t>2026-07-05 17:54:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84211</v>
+        <v>2.84615</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:46</t>
+          <t>2026-07-05 17:54:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74015</v>
+        <v>4.74024</v>
       </c>
       <c r="G12" t="n">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:48</t>
+          <t>2026-07-05 17:54:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:50</t>
+          <t>2026-07-05 17:54:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:52</t>
+          <t>2026-07-05 17:54:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:55</t>
+          <t>2026-07-05 17:54:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7464</v>
+        <v>4.74634</v>
       </c>
       <c r="G16" t="n">
-        <v>31593</v>
+        <v>31617</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="O16" t="n">
         <v>316</v>
@@ -1594,10 +1594,10 @@
         <v>632</v>
       </c>
       <c r="Q16" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="R16" t="n">
-        <v>28118</v>
+        <v>28139</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:01</t>
+          <t>2026-07-06 18:50:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:03</t>
+          <t>2026-07-06 18:50:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81451</v>
+        <v>4.81431</v>
       </c>
       <c r="G3" t="n">
-        <v>12777</v>
+        <v>12785</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O3" t="n">
         <v>128</v>
@@ -661,7 +661,7 @@
         <v>256</v>
       </c>
       <c r="R3" t="n">
-        <v>11883</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:05</t>
+          <t>2026-07-06 18:50:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:07</t>
+          <t>2026-07-06 18:50:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85186</v>
+        <v>2.857</v>
       </c>
       <c r="G5" t="n">
-        <v>2896</v>
+        <v>2902</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="O5" t="n">
         <v>145</v>
@@ -805,7 +805,7 @@
         <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>1158</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:10</t>
+          <t>2026-07-06 18:50:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:12</t>
+          <t>2026-07-06 18:50:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01827</v>
+        <v>4.01825</v>
       </c>
       <c r="G7" t="n">
-        <v>3668</v>
+        <v>3671</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>147</v>
       </c>
       <c r="P7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="R7" t="n">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:14</t>
+          <t>2026-07-06 18:50:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74153</v>
+        <v>4.74152</v>
       </c>
       <c r="G8" t="n">
-        <v>13580</v>
+        <v>13591</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>272</v>
       </c>
       <c r="Q8" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R8" t="n">
-        <v>12086</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:16</t>
+          <t>2026-07-06 18:50:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:18</t>
+          <t>2026-07-06 18:50:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8756</v>
+        <v>3.87285</v>
       </c>
       <c r="G10" t="n">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:20</t>
+          <t>2026-07-06 18:50:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:23</t>
+          <t>2026-07-06 18:50:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74024</v>
+        <v>4.73906</v>
       </c>
       <c r="G12" t="n">
-        <v>2945</v>
+        <v>2947</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:25</t>
+          <t>2026-07-06 18:50:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:27</t>
+          <t>2026-07-06 18:51:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:30</t>
+          <t>2026-07-06 18:51:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-05 17:54:32</t>
+          <t>2026-07-06 18:51:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74634</v>
+        <v>4.74629</v>
       </c>
       <c r="G16" t="n">
-        <v>31617</v>
+        <v>31627</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>316</v>
       </c>
       <c r="P16" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q16" t="n">
         <v>1265</v>
       </c>
       <c r="R16" t="n">
-        <v>28139</v>
+        <v>28148</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:32</t>
+          <t>2026-07-07 18:53:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:34</t>
+          <t>2026-07-07 18:53:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81431</v>
+        <v>4.81429</v>
       </c>
       <c r="G3" t="n">
-        <v>12785</v>
+        <v>12794</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>256</v>
       </c>
       <c r="R3" t="n">
-        <v>11890</v>
+        <v>11898</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:37</t>
+          <t>2026-07-07 18:53:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88084</v>
+        <v>3.88061</v>
       </c>
       <c r="G4" t="n">
-        <v>4817</v>
+        <v>4816</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>385</v>
       </c>
       <c r="R4" t="n">
-        <v>2987</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:39</t>
+          <t>2026-07-07 18:53:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.857</v>
+        <v>2.85729</v>
       </c>
       <c r="G5" t="n">
-        <v>2902</v>
+        <v>2908</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="O5" t="n">
         <v>145</v>
@@ -805,7 +805,7 @@
         <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:41</t>
+          <t>2026-07-07 18:53:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:44</t>
+          <t>2026-07-07 18:53:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01825</v>
+        <v>4.01552</v>
       </c>
       <c r="G7" t="n">
-        <v>3671</v>
+        <v>3673</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,11 +933,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>June 17, 2026</t>
+          <t>July 07, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O7" t="n">
         <v>147</v>
@@ -949,7 +949,7 @@
         <v>404</v>
       </c>
       <c r="R7" t="n">
-        <v>2349</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:46</t>
+          <t>2026-07-07 18:53:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74152</v>
+        <v>4.74118</v>
       </c>
       <c r="G8" t="n">
-        <v>13591</v>
+        <v>13600</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>544</v>
       </c>
       <c r="R8" t="n">
-        <v>12096</v>
+        <v>12104</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:49</t>
+          <t>2026-07-07 18:53:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:51</t>
+          <t>2026-07-07 18:53:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:53</t>
+          <t>2026-07-07 18:53:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:56</t>
+          <t>2026-07-07 18:53:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73906</v>
+        <v>4.73932</v>
       </c>
       <c r="G12" t="n">
-        <v>2947</v>
+        <v>2950</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1300,16 +1300,16 @@
         <v>118</v>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
         <v>59</v>
       </c>
       <c r="Q12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:59</t>
+          <t>2026-07-07 18:53:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-06 18:51:01</t>
+          <t>2026-07-07 18:53:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-06 18:51:03</t>
+          <t>2026-07-07 18:53:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-06 18:51:06</t>
+          <t>2026-07-07 18:53:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74629</v>
+        <v>4.74639</v>
       </c>
       <c r="G16" t="n">
-        <v>31627</v>
+        <v>31643</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>633</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28148</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:21</t>
+          <t>2026-07-08 18:12:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.67262</v>
+        <v>4.65089</v>
       </c>
       <c r="G2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:24</t>
+          <t>2026-07-08 18:12:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81429</v>
+        <v>4.81453</v>
       </c>
       <c r="G3" t="n">
-        <v>12794</v>
+        <v>12811</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>256</v>
       </c>
       <c r="R3" t="n">
-        <v>11898</v>
+        <v>11914</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:26</t>
+          <t>2026-07-08 18:12:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88061</v>
+        <v>3.87946</v>
       </c>
       <c r="G4" t="n">
-        <v>4816</v>
+        <v>4820</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="O4" t="n">
         <v>241</v>
@@ -730,10 +730,10 @@
         <v>241</v>
       </c>
       <c r="Q4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2986</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:28</t>
+          <t>2026-07-08 18:12:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85729</v>
+        <v>2.85611</v>
       </c>
       <c r="G5" t="n">
-        <v>2908</v>
+        <v>2912</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="O5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P5" t="n">
         <v>87</v>
@@ -805,7 +805,7 @@
         <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:30</t>
+          <t>2026-07-08 18:12:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:33</t>
+          <t>2026-07-08 18:12:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01552</v>
+        <v>4.01387</v>
       </c>
       <c r="G7" t="n">
-        <v>3673</v>
+        <v>3677</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="O7" t="n">
         <v>147</v>
@@ -949,7 +949,7 @@
         <v>404</v>
       </c>
       <c r="R7" t="n">
-        <v>2314</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:35</t>
+          <t>2026-07-08 18:12:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74118</v>
+        <v>4.74092</v>
       </c>
       <c r="G8" t="n">
-        <v>13600</v>
+        <v>13606</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>544</v>
       </c>
       <c r="R8" t="n">
-        <v>12104</v>
+        <v>12109</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:37</t>
+          <t>2026-07-08 18:12:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:39</t>
+          <t>2026-07-08 18:12:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:42</t>
+          <t>2026-07-08 18:12:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:44</t>
+          <t>2026-07-08 18:12:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73932</v>
+        <v>4.73916</v>
       </c>
       <c r="G12" t="n">
-        <v>2950</v>
+        <v>2952</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2596</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:46</t>
+          <t>2026-07-08 18:12:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:48</t>
+          <t>2026-07-08 18:12:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:50</t>
+          <t>2026-07-08 18:12:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:51</t>
+          <t>2026-07-08 18:12:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74639</v>
+        <v>4.74629</v>
       </c>
       <c r="G16" t="n">
-        <v>31643</v>
+        <v>31658</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>633</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>28176</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:18</t>
+          <t>2026-07-09 18:44:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:21</t>
+          <t>2026-07-09 18:44:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81453</v>
+        <v>4.81432</v>
       </c>
       <c r="G3" t="n">
-        <v>12811</v>
+        <v>12823</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O3" t="n">
         <v>128</v>
@@ -661,7 +661,7 @@
         <v>256</v>
       </c>
       <c r="R3" t="n">
-        <v>11914</v>
+        <v>11925</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:24</t>
+          <t>2026-07-09 18:44:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:26</t>
+          <t>2026-07-09 18:44:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85611</v>
+        <v>2.8567</v>
       </c>
       <c r="G5" t="n">
-        <v>2912</v>
+        <v>2917</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
       </c>
       <c r="P5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R5" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:29</t>
+          <t>2026-07-09 18:44:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.16912</v>
+        <v>3.15328</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:31</t>
+          <t>2026-07-09 18:44:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01387</v>
+        <v>4.01305</v>
       </c>
       <c r="G7" t="n">
         <v>3677</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:34</t>
+          <t>2026-07-09 18:45:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74092</v>
+        <v>4.74094</v>
       </c>
       <c r="G8" t="n">
-        <v>13606</v>
+        <v>13611</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>544</v>
       </c>
       <c r="R8" t="n">
-        <v>12109</v>
+        <v>12114</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:36</t>
+          <t>2026-07-09 18:45:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:39</t>
+          <t>2026-07-09 18:45:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:41</t>
+          <t>2026-07-09 18:45:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>June 20, 2026</t>
+          <t>July 09, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:44</t>
+          <t>2026-07-09 18:45:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:46</t>
+          <t>2026-07-09 18:45:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.02111</v>
+        <v>4.01532</v>
       </c>
       <c r="G13" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:48</t>
+          <t>2026-07-09 18:45:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:51</t>
+          <t>2026-07-09 18:45:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:53</t>
+          <t>2026-07-09 18:45:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74629</v>
+        <v>4.74627</v>
       </c>
       <c r="G16" t="n">
-        <v>31658</v>
+        <v>31664</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="O16" t="n">
         <v>317</v>
@@ -1594,10 +1594,10 @@
         <v>633</v>
       </c>
       <c r="Q16" t="n">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="R16" t="n">
-        <v>28176</v>
+        <v>28181</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:46</t>
+          <t>2026-07-10 18:15:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:49</t>
+          <t>2026-07-10 18:15:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81432</v>
+        <v>4.81405</v>
       </c>
       <c r="G3" t="n">
-        <v>12823</v>
+        <v>12827</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>128</v>
       </c>
       <c r="Q3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11925</v>
+        <v>11929</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:51</t>
+          <t>2026-07-10 18:15:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87946</v>
+        <v>3.8791</v>
       </c>
       <c r="G4" t="n">
-        <v>4820</v>
+        <v>4822</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2988</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:53</t>
+          <t>2026-07-10 18:15:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8567</v>
+        <v>2.85944</v>
       </c>
       <c r="G5" t="n">
-        <v>2917</v>
+        <v>2924</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>117</v>
       </c>
       <c r="R5" t="n">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:56</t>
+          <t>2026-07-10 18:15:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:58</t>
+          <t>2026-07-10 18:15:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01305</v>
+        <v>4.01168</v>
       </c>
       <c r="G7" t="n">
-        <v>3677</v>
+        <v>3680</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O7" t="n">
         <v>147</v>
@@ -946,10 +946,10 @@
         <v>184</v>
       </c>
       <c r="Q7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R7" t="n">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:00</t>
+          <t>2026-07-10 18:15:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74094</v>
+        <v>4.7417</v>
       </c>
       <c r="G8" t="n">
-        <v>13611</v>
+        <v>13616</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>272</v>
       </c>
       <c r="Q8" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12114</v>
+        <v>12118</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:02</t>
+          <t>2026-07-10 18:15:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:05</t>
+          <t>2026-07-10 18:15:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87285</v>
+        <v>3.87393</v>
       </c>
       <c r="G10" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:07</t>
+          <t>2026-07-10 18:15:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:09</t>
+          <t>2026-07-10 18:15:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73916</v>
+        <v>4.7401</v>
       </c>
       <c r="G12" t="n">
-        <v>2952</v>
+        <v>2955</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2598</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:12</t>
+          <t>2026-07-10 18:15:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:14</t>
+          <t>2026-07-10 18:15:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:16</t>
+          <t>2026-07-10 18:15:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-09 18:45:18</t>
+          <t>2026-07-10 18:15:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74627</v>
+        <v>4.74611</v>
       </c>
       <c r="G16" t="n">
-        <v>31664</v>
+        <v>31671</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1267</v>
       </c>
       <c r="R16" t="n">
-        <v>28181</v>
+        <v>28187</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:23</t>
+          <t>2026-07-11 17:44:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:26</t>
+          <t>2026-07-11 17:44:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81405</v>
+        <v>4.81412</v>
       </c>
       <c r="G3" t="n">
-        <v>12827</v>
+        <v>12831</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11929</v>
+        <v>11933</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:28</t>
+          <t>2026-07-11 17:44:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:30</t>
+          <t>2026-07-11 17:44:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85944</v>
+        <v>2.86017</v>
       </c>
       <c r="G5" t="n">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:33</t>
+          <t>2026-07-11 17:44:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:35</t>
+          <t>2026-07-11 17:44:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01168</v>
+        <v>4.01004</v>
       </c>
       <c r="G7" t="n">
-        <v>3680</v>
+        <v>3682</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>405</v>
       </c>
       <c r="R7" t="n">
-        <v>2318</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:37</t>
+          <t>2026-07-11 17:44:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7417</v>
+        <v>4.74163</v>
       </c>
       <c r="G8" t="n">
-        <v>13616</v>
+        <v>13624</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0.45</t>
+          <t>1.1.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>June 05, 2026</t>
+          <t>July 11, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12118</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:41</t>
+          <t>2026-07-11 17:44:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:43</t>
+          <t>2026-07-11 17:44:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87393</v>
+        <v>3.875</v>
       </c>
       <c r="G10" t="n">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O10" t="n">
         <v>42</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>670</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:45</t>
+          <t>2026-07-11 17:44:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:48</t>
+          <t>2026-07-11 17:44:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7401</v>
+        <v>4.73901</v>
       </c>
       <c r="G12" t="n">
-        <v>2955</v>
+        <v>2958</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2600</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:50</t>
+          <t>2026-07-11 17:44:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:52</t>
+          <t>2026-07-11 17:44:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:55</t>
+          <t>2026-07-11 17:44:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:57</t>
+          <t>2026-07-11 17:45:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74611</v>
+        <v>4.74619</v>
       </c>
       <c r="G16" t="n">
-        <v>31671</v>
+        <v>31677</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>317</v>
       </c>
       <c r="P16" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Q16" t="n">
         <v>1267</v>
       </c>
       <c r="R16" t="n">
-        <v>28187</v>
+        <v>28193</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:27</t>
+          <t>2026-07-12 17:46:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:29</t>
+          <t>2026-07-12 17:46:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81412</v>
+        <v>4.81451</v>
       </c>
       <c r="G3" t="n">
-        <v>12831</v>
+        <v>12836</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.2</t>
+          <t>4.44.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>June 29, 2026</t>
+          <t>July 12, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11933</v>
+        <v>11937</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:32</t>
+          <t>2026-07-12 17:46:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8791</v>
+        <v>3.8785</v>
       </c>
       <c r="G4" t="n">
-        <v>4822</v>
+        <v>4823</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="O4" t="n">
         <v>241</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:34</t>
+          <t>2026-07-12 17:46:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86017</v>
+        <v>2.85963</v>
       </c>
       <c r="G5" t="n">
-        <v>2925</v>
+        <v>2928</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="O5" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>117</v>
       </c>
       <c r="R5" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:37</t>
+          <t>2026-07-12 17:46:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:39</t>
+          <t>2026-07-12 17:46:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01004</v>
+        <v>4.00976</v>
       </c>
       <c r="G7" t="n">
-        <v>3682</v>
+        <v>3684</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>405</v>
       </c>
       <c r="R7" t="n">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:41</t>
+          <t>2026-07-12 17:46:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74163</v>
+        <v>4.7424</v>
       </c>
       <c r="G8" t="n">
-        <v>13624</v>
+        <v>13630</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12125</v>
+        <v>12131</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:44</t>
+          <t>2026-07-12 17:46:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:46</t>
+          <t>2026-07-12 17:46:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:49</t>
+          <t>2026-07-12 17:47:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84615</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:51</t>
+          <t>2026-07-12 17:47:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73901</v>
+        <v>4.73945</v>
       </c>
       <c r="G12" t="n">
-        <v>2958</v>
+        <v>2963</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O12" t="n">
         <v>30</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2603</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:54</t>
+          <t>2026-07-12 17:47:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:56</t>
+          <t>2026-07-12 17:47:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:58</t>
+          <t>2026-07-12 17:47:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 17:45:01</t>
+          <t>2026-07-12 17:47:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74619</v>
+        <v>4.74632</v>
       </c>
       <c r="G16" t="n">
-        <v>31677</v>
+        <v>31690</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="O16" t="n">
         <v>317</v>
@@ -1594,10 +1594,10 @@
         <v>634</v>
       </c>
       <c r="Q16" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="R16" t="n">
-        <v>28193</v>
+        <v>28204</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:38</t>
+          <t>2026-07-13 18:24:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.65089</v>
+        <v>4.64881</v>
       </c>
       <c r="G2" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:40</t>
+          <t>2026-07-13 18:24:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81451</v>
+        <v>4.81459</v>
       </c>
       <c r="G3" t="n">
-        <v>12836</v>
+        <v>12842</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11937</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:42</t>
+          <t>2026-07-13 18:24:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:45</t>
+          <t>2026-07-13 18:24:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85963</v>
+        <v>2.86055</v>
       </c>
       <c r="G5" t="n">
-        <v>2928</v>
+        <v>2933</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="O5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
         <v>88</v>
@@ -805,7 +805,7 @@
         <v>117</v>
       </c>
       <c r="R5" t="n">
-        <v>1200</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:48</t>
+          <t>2026-07-13 18:24:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:50</t>
+          <t>2026-07-13 18:24:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00976</v>
+        <v>4.00949</v>
       </c>
       <c r="G7" t="n">
-        <v>3684</v>
+        <v>3689</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O7" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P7" t="n">
         <v>184</v>
       </c>
       <c r="Q7" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R7" t="n">
-        <v>2321</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:53</t>
+          <t>2026-07-13 18:24:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7424</v>
+        <v>4.74206</v>
       </c>
       <c r="G8" t="n">
-        <v>13630</v>
+        <v>13635</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12131</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:55</t>
+          <t>2026-07-13 18:25:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:57</t>
+          <t>2026-07-13 18:25:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:00</t>
+          <t>2026-07-13 18:25:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:02</t>
+          <t>2026-07-13 18:25:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73945</v>
+        <v>4.73963</v>
       </c>
       <c r="G12" t="n">
-        <v>2963</v>
+        <v>2965</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2607</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:05</t>
+          <t>2026-07-13 18:25:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:07</t>
+          <t>2026-07-13 18:25:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:09</t>
+          <t>2026-07-13 18:25:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 17:47:12</t>
+          <t>2026-07-13 18:25:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74632</v>
+        <v>4.74636</v>
       </c>
       <c r="G16" t="n">
-        <v>31690</v>
+        <v>31699</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1268</v>
       </c>
       <c r="R16" t="n">
-        <v>28204</v>
+        <v>28212</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:44</t>
+          <t>2026-07-14 17:54:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.64881</v>
+        <v>4.65089</v>
       </c>
       <c r="G2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:46</t>
+          <t>2026-07-14 17:54:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81459</v>
+        <v>4.81457</v>
       </c>
       <c r="G3" t="n">
-        <v>12842</v>
+        <v>12851</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:48</t>
+          <t>2026-07-14 17:54:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:51</t>
+          <t>2026-07-14 17:55:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86055</v>
+        <v>2.86288</v>
       </c>
       <c r="G5" t="n">
-        <v>2933</v>
+        <v>2939</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1379</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:53</t>
+          <t>2026-07-14 17:55:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:56</t>
+          <t>2026-07-14 17:55:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00949</v>
+        <v>4.00894</v>
       </c>
       <c r="G7" t="n">
-        <v>3689</v>
+        <v>3692</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O7" t="n">
         <v>148</v>
       </c>
       <c r="P7" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q7" t="n">
         <v>406</v>
       </c>
       <c r="R7" t="n">
-        <v>2324</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:58</t>
+          <t>2026-07-14 17:55:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74206</v>
+        <v>4.74214</v>
       </c>
       <c r="G8" t="n">
-        <v>13635</v>
+        <v>13636</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12135</v>
+        <v>12136</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:00</t>
+          <t>2026-07-14 17:55:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:02</t>
+          <t>2026-07-14 17:55:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:05</t>
+          <t>2026-07-14 17:55:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:07</t>
+          <t>2026-07-14 17:55:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73963</v>
+        <v>4.73854</v>
       </c>
       <c r="G12" t="n">
-        <v>2965</v>
+        <v>2968</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>148</v>
       </c>
       <c r="R12" t="n">
-        <v>2609</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:09</t>
+          <t>2026-07-14 17:55:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:12</t>
+          <t>2026-07-14 17:55:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>May 21, 2026</t>
+          <t>July 14, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:14</t>
+          <t>2026-07-14 17:55:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-13 18:25:16</t>
+          <t>2026-07-14 17:55:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74636</v>
+        <v>4.7464</v>
       </c>
       <c r="G16" t="n">
-        <v>31699</v>
+        <v>31711</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1268</v>
       </c>
       <c r="R16" t="n">
-        <v>28212</v>
+        <v>28223</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:54</t>
+          <t>2026-07-15 18:00:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:56</t>
+          <t>2026-07-15 18:00:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81457</v>
+        <v>4.81461</v>
       </c>
       <c r="G3" t="n">
-        <v>12851</v>
+        <v>12854</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11954</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:58</t>
+          <t>2026-07-15 18:01:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:00</t>
+          <t>2026-07-15 18:01:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:02</t>
+          <t>2026-07-15 18:01:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15328</v>
+        <v>3.13768</v>
       </c>
       <c r="G6" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:04</t>
+          <t>2026-07-15 18:01:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00894</v>
+        <v>4.00921</v>
       </c>
       <c r="G7" t="n">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>406</v>
       </c>
       <c r="R7" t="n">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:06</t>
+          <t>2026-07-15 18:01:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:09</t>
+          <t>2026-07-15 18:01:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:11</t>
+          <t>2026-07-15 18:01:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:13</t>
+          <t>2026-07-15 18:01:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:15</t>
+          <t>2026-07-15 18:01:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:17</t>
+          <t>2026-07-15 18:01:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:19</t>
+          <t>2026-07-15 18:01:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:21</t>
+          <t>2026-07-15 18:01:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-14 17:55:24</t>
+          <t>2026-07-15 18:01:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7464</v>
+        <v>4.74662</v>
       </c>
       <c r="G16" t="n">
-        <v>31711</v>
+        <v>31716</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O16" t="n">
         <v>317</v>
@@ -1594,10 +1594,10 @@
         <v>634</v>
       </c>
       <c r="Q16" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="R16" t="n">
-        <v>28223</v>
+        <v>28227</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:56</t>
+          <t>2026-07-16 17:58:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:59</t>
+          <t>2026-07-16 17:58:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81461</v>
+        <v>4.81471</v>
       </c>
       <c r="G3" t="n">
-        <v>12854</v>
+        <v>12861</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11954</v>
+        <v>11961</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:01</t>
+          <t>2026-07-16 17:58:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:04</t>
+          <t>2026-07-16 17:58:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86288</v>
+        <v>2.86766</v>
       </c>
       <c r="G5" t="n">
-        <v>2939</v>
+        <v>2947</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="O5" t="n">
         <v>147</v>
@@ -805,7 +805,7 @@
         <v>118</v>
       </c>
       <c r="R5" t="n">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:06</t>
+          <t>2026-07-16 17:58:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:09</t>
+          <t>2026-07-16 17:59:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00921</v>
+        <v>4.00812</v>
       </c>
       <c r="G7" t="n">
-        <v>3693</v>
+        <v>3696</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>185</v>
       </c>
       <c r="Q7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R7" t="n">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:11</t>
+          <t>2026-07-16 17:59:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:14</t>
+          <t>2026-07-16 17:59:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:16</t>
+          <t>2026-07-16 17:59:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.875</v>
+        <v>3.87321</v>
       </c>
       <c r="G10" t="n">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>681</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:19</t>
+          <t>2026-07-16 17:59:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:21</t>
+          <t>2026-07-16 17:59:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73854</v>
+        <v>4.73479</v>
       </c>
       <c r="G12" t="n">
-        <v>2968</v>
+        <v>2975</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1303,13 +1303,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2612</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:24</t>
+          <t>2026-07-16 17:59:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.7.14</t>
+          <t>1.7.20</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>May 18, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:26</t>
+          <t>2026-07-16 17:59:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:28</t>
+          <t>2026-07-16 17:59:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:31</t>
+          <t>2026-07-16 17:59:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74662</v>
+        <v>4.7463</v>
       </c>
       <c r="G16" t="n">
-        <v>31716</v>
+        <v>31730</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>317</v>
       </c>
       <c r="P16" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q16" t="n">
         <v>1269</v>
       </c>
       <c r="R16" t="n">
-        <v>28227</v>
+        <v>28240</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:48</t>
+          <t>2026-07-17 17:54:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:51</t>
+          <t>2026-07-17 17:54:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81471</v>
+        <v>4.81454</v>
       </c>
       <c r="G3" t="n">
-        <v>12861</v>
+        <v>12871</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11961</v>
+        <v>11970</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:53</t>
+          <t>2026-07-17 17:54:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:56</t>
+          <t>2026-07-17 17:54:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86766</v>
+        <v>2.86929</v>
       </c>
       <c r="G5" t="n">
-        <v>2947</v>
+        <v>2953</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q5" t="n">
         <v>118</v>
       </c>
       <c r="R5" t="n">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:58</t>
+          <t>2026-07-17 17:54:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.13768</v>
+        <v>3.11429</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:01</t>
+          <t>2026-07-17 17:54:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00812</v>
+        <v>4.00622</v>
       </c>
       <c r="G7" t="n">
-        <v>3696</v>
+        <v>3700</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O7" t="n">
         <v>148</v>
@@ -949,7 +949,7 @@
         <v>407</v>
       </c>
       <c r="R7" t="n">
-        <v>2328</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:03</t>
+          <t>2026-07-17 17:55:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74214</v>
+        <v>4.74217</v>
       </c>
       <c r="G8" t="n">
-        <v>13636</v>
+        <v>13637</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12136</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:06</t>
+          <t>2026-07-17 17:55:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:08</t>
+          <t>2026-07-17 17:55:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:11</t>
+          <t>2026-07-17 17:55:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:13</t>
+          <t>2026-07-17 17:55:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73479</v>
+        <v>4.73488</v>
       </c>
       <c r="G12" t="n">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2618</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:15</t>
+          <t>2026-07-17 17:55:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01532</v>
+        <v>4.01708</v>
       </c>
       <c r="G13" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
         <v>21</v>
@@ -1381,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:17</t>
+          <t>2026-07-17 17:55:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:19</t>
+          <t>2026-07-17 17:55:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-16 17:59:22</t>
+          <t>2026-07-17 17:55:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7463</v>
+        <v>4.74627</v>
       </c>
       <c r="G16" t="n">
-        <v>31730</v>
+        <v>31740</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="O16" t="n">
         <v>317</v>
@@ -1594,10 +1594,10 @@
         <v>635</v>
       </c>
       <c r="Q16" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="R16" t="n">
-        <v>28240</v>
+        <v>28249</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:44</t>
+          <t>2026-07-18 17:44:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:47</t>
+          <t>2026-07-18 17:44:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81454</v>
+        <v>4.81456</v>
       </c>
       <c r="G3" t="n">
-        <v>12871</v>
+        <v>12872</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11970</v>
+        <v>11971</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:50</t>
+          <t>2026-07-18 17:44:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:53</t>
+          <t>2026-07-18 17:44:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:56</t>
+          <t>2026-07-18 17:44:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:59</t>
+          <t>2026-07-18 17:45:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:02</t>
+          <t>2026-07-18 17:45:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:05</t>
+          <t>2026-07-18 17:45:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:09</t>
+          <t>2026-07-18 17:45:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:14</t>
+          <t>2026-07-18 17:45:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:19</t>
+          <t>2026-07-18 17:45:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:24</t>
+          <t>2026-07-18 17:45:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1381,7 +1381,7 @@
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:29</t>
+          <t>2026-07-18 17:45:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:35</t>
+          <t>2026-07-18 17:45:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-17 17:55:38</t>
+          <t>2026-07-18 17:45:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74627</v>
+        <v>4.74633</v>
       </c>
       <c r="G16" t="n">
-        <v>31740</v>
+        <v>31742</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1270</v>
       </c>
       <c r="R16" t="n">
-        <v>28249</v>
+        <v>28250</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:48</t>
+          <t>2026-07-19 17:46:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:51</t>
+          <t>2026-07-19 17:46:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81456</v>
+        <v>4.81459</v>
       </c>
       <c r="G3" t="n">
-        <v>12872</v>
+        <v>12874</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>11971</v>
+        <v>11973</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:54</t>
+          <t>2026-07-19 17:46:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:56</t>
+          <t>2026-07-19 17:46:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86929</v>
+        <v>2.86937</v>
       </c>
       <c r="G5" t="n">
-        <v>2953</v>
+        <v>2955</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="O5" t="n">
         <v>148</v>
@@ -805,7 +805,7 @@
         <v>118</v>
       </c>
       <c r="R5" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:59</t>
+          <t>2026-07-19 17:46:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:01</t>
+          <t>2026-07-19 17:46:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00622</v>
+        <v>4.00567</v>
       </c>
       <c r="G7" t="n">
-        <v>3700</v>
+        <v>3702</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>407</v>
       </c>
       <c r="R7" t="n">
-        <v>2331</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:04</t>
+          <t>2026-07-19 17:46:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:07</t>
+          <t>2026-07-19 17:46:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:09</t>
+          <t>2026-07-19 17:46:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87321</v>
+        <v>3.87429</v>
       </c>
       <c r="G10" t="n">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:12</t>
+          <t>2026-07-19 17:46:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:15</t>
+          <t>2026-07-19 17:46:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:17</t>
+          <t>2026-07-19 17:46:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01708</v>
+        <v>4.01879</v>
       </c>
       <c r="G13" t="n">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O13" t="n">
         <v>21</v>
@@ -1378,10 +1378,10 @@
         <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:19</t>
+          <t>2026-07-19 17:46:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:22</t>
+          <t>2026-07-19 17:46:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-18 17:45:24</t>
+          <t>2026-07-19 17:46:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74633</v>
+        <v>4.74634</v>
       </c>
       <c r="G16" t="n">
-        <v>31742</v>
+        <v>31743</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1270</v>
       </c>
       <c r="R16" t="n">
-        <v>28250</v>
+        <v>28251</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:13</t>
+          <t>2026-07-20 18:47:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:16</t>
+          <t>2026-07-20 18:47:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81459</v>
+        <v>4.81468</v>
       </c>
       <c r="G3" t="n">
-        <v>12874</v>
+        <v>12886</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O3" t="n">
         <v>129</v>
@@ -658,10 +658,10 @@
         <v>129</v>
       </c>
       <c r="Q3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>11973</v>
+        <v>11984</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:18</t>
+          <t>2026-07-20 18:47:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:20</t>
+          <t>2026-07-20 18:47:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86937</v>
+        <v>2.86374</v>
       </c>
       <c r="G5" t="n">
-        <v>2955</v>
+        <v>2965</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="O5" t="n">
         <v>148</v>
@@ -802,10 +802,10 @@
         <v>89</v>
       </c>
       <c r="Q5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:23</t>
+          <t>2026-07-20 18:47:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.11429</v>
+        <v>3.14085</v>
       </c>
       <c r="G6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:25</t>
+          <t>2026-07-20 18:47:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00567</v>
+        <v>4.0027</v>
       </c>
       <c r="G7" t="n">
-        <v>3702</v>
+        <v>3707</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O7" t="n">
         <v>148</v>
@@ -946,10 +946,10 @@
         <v>185</v>
       </c>
       <c r="Q7" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>2332</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:28</t>
+          <t>2026-07-20 18:47:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74217</v>
+        <v>4.74206</v>
       </c>
       <c r="G8" t="n">
-        <v>13637</v>
+        <v>13639</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R8" t="n">
-        <v>12137</v>
+        <v>12139</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:30</t>
+          <t>2026-07-20 18:47:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:33</t>
+          <t>2026-07-20 18:47:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87429</v>
+        <v>3.87321</v>
       </c>
       <c r="G10" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:35</t>
+          <t>2026-07-20 18:47:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:37</t>
+          <t>2026-07-20 18:47:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73488</v>
+        <v>4.73522</v>
       </c>
       <c r="G12" t="n">
-        <v>2976</v>
+        <v>2980</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2619</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:40</t>
+          <t>2026-07-20 18:47:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01879</v>
+        <v>4.01876</v>
       </c>
       <c r="G13" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:42</t>
+          <t>2026-07-20 18:47:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:45</t>
+          <t>2026-07-20 18:47:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:47</t>
+          <t>2026-07-20 18:47:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74634</v>
+        <v>4.74637</v>
       </c>
       <c r="G16" t="n">
-        <v>31743</v>
+        <v>31767</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="O16" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P16" t="n">
         <v>635</v>
       </c>
       <c r="Q16" t="n">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="R16" t="n">
-        <v>28251</v>
+        <v>28273</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:26</t>
+          <t>2026-07-21 18:05:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:29</t>
+          <t>2026-07-21 18:06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81468</v>
+        <v>4.8148</v>
       </c>
       <c r="G3" t="n">
-        <v>12886</v>
+        <v>12894</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:31</t>
+          <t>2026-07-21 18:06:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:33</t>
+          <t>2026-07-21 18:06:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86374</v>
+        <v>2.86584</v>
       </c>
       <c r="G5" t="n">
-        <v>2965</v>
+        <v>2974</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="O5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>89</v>
@@ -805,7 +805,7 @@
         <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>1216</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:35</t>
+          <t>2026-07-21 18:06:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:38</t>
+          <t>2026-07-21 18:06:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>4.0027</v>
       </c>
       <c r="G7" t="n">
-        <v>3707</v>
+        <v>3709</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O7" t="n">
         <v>148</v>
@@ -949,7 +949,7 @@
         <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>2335</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:40</t>
+          <t>2026-07-21 18:06:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74206</v>
+        <v>4.74207</v>
       </c>
       <c r="G8" t="n">
-        <v>13639</v>
+        <v>13640</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>546</v>
       </c>
       <c r="R8" t="n">
-        <v>12139</v>
+        <v>12140</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:42</t>
+          <t>2026-07-21 18:06:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:44</t>
+          <t>2026-07-21 18:06:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:46</t>
+          <t>2026-07-21 18:06:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:48</t>
+          <t>2026-07-21 18:06:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73522</v>
+        <v>4.73532</v>
       </c>
       <c r="G12" t="n">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2622</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:51</t>
+          <t>2026-07-21 18:06:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:53</t>
+          <t>2026-07-21 18:06:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:55</t>
+          <t>2026-07-21 18:06:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:57</t>
+          <t>2026-07-21 18:06:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74637</v>
+        <v>4.74624</v>
       </c>
       <c r="G16" t="n">
-        <v>31767</v>
+        <v>31778</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>318</v>
       </c>
       <c r="P16" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Q16" t="n">
         <v>1271</v>
       </c>
       <c r="R16" t="n">
-        <v>28273</v>
+        <v>28282</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:58</t>
+          <t>2026-07-22 17:59:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:00</t>
+          <t>2026-07-22 17:59:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8148</v>
+        <v>4.81443</v>
       </c>
       <c r="G3" t="n">
-        <v>12894</v>
+        <v>12901</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11998</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:02</t>
+          <t>2026-07-22 17:59:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:05</t>
+          <t>2026-07-22 17:59:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86584</v>
+        <v>2.86492</v>
       </c>
       <c r="G5" t="n">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="O5" t="n">
         <v>149</v>
@@ -805,7 +805,7 @@
         <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:08</t>
+          <t>2026-07-22 17:59:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:10</t>
+          <t>2026-07-22 17:59:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0027</v>
+        <v>4.00108</v>
       </c>
       <c r="G7" t="n">
-        <v>3709</v>
+        <v>3711</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>148</v>
       </c>
       <c r="P7" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q7" t="n">
         <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:13</t>
+          <t>2026-07-22 17:59:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:15</t>
+          <t>2026-07-22 17:59:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:18</t>
+          <t>2026-07-22 17:59:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:20</t>
+          <t>2026-07-22 17:59:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:23</t>
+          <t>2026-07-22 17:59:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73532</v>
+        <v>4.73416</v>
       </c>
       <c r="G12" t="n">
-        <v>2981</v>
+        <v>2983</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2623</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:25</t>
+          <t>2026-07-22 17:59:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:27</t>
+          <t>2026-07-22 18:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:30</t>
+          <t>2026-07-22 18:00:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-21 18:06:33</t>
+          <t>2026-07-22 18:00:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74624</v>
+        <v>4.74606</v>
       </c>
       <c r="G16" t="n">
-        <v>31778</v>
+        <v>31796</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="O16" t="n">
         <v>318</v>
@@ -1594,10 +1594,10 @@
         <v>636</v>
       </c>
       <c r="Q16" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>28282</v>
+        <v>28298</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:32</t>
+          <t>2026-07-23 18:05:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>July 02, 2026</t>
+          <t>July 23, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:34</t>
+          <t>2026-07-23 18:05:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81443</v>
+        <v>4.81453</v>
       </c>
       <c r="G3" t="n">
-        <v>12901</v>
+        <v>12908</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>11998</v>
+        <v>12004</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:36</t>
+          <t>2026-07-23 18:05:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:39</t>
+          <t>2026-07-23 18:05:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86492</v>
+        <v>2.86188</v>
       </c>
       <c r="G5" t="n">
-        <v>2976</v>
+        <v>2983</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="O5" t="n">
         <v>149</v>
@@ -805,7 +805,7 @@
         <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:41</t>
+          <t>2026-07-23 18:05:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:44</t>
+          <t>2026-07-23 18:05:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.00108</v>
+        <v>3.99731</v>
       </c>
       <c r="G7" t="n">
-        <v>3711</v>
+        <v>3715</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O7" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
         <v>186</v>
       </c>
       <c r="Q7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R7" t="n">
-        <v>2338</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:46</t>
+          <t>2026-07-23 18:05:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74207</v>
+        <v>4.74216</v>
       </c>
       <c r="G8" t="n">
         <v>13640</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:49</t>
+          <t>2026-07-23 18:05:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61958</v>
+        <v>4.61904</v>
       </c>
       <c r="G9" t="n">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:51</t>
+          <t>2026-07-23 18:05:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87321</v>
+        <v>3.87429</v>
       </c>
       <c r="G10" t="n">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:53</t>
+          <t>2026-07-23 18:05:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:56</t>
+          <t>2026-07-23 18:05:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:58</t>
+          <t>2026-07-23 18:05:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01876</v>
+        <v>4.0206</v>
       </c>
       <c r="G13" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-22 18:00:00</t>
+          <t>2026-07-23 18:05:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-22 18:00:03</t>
+          <t>2026-07-23 18:05:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-22 18:00:05</t>
+          <t>2026-07-23 18:05:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74606</v>
+        <v>4.74636</v>
       </c>
       <c r="G16" t="n">
-        <v>31796</v>
+        <v>31817</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>3.1.4</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>June 14, 2026</t>
+          <t>July 23, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="O16" t="n">
         <v>318</v>
@@ -1594,10 +1594,10 @@
         <v>636</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="R16" t="n">
-        <v>28298</v>
+        <v>28317</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:00</t>
+          <t>2026-07-24 18:09:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:03</t>
+          <t>2026-07-24 18:09:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81453</v>
+        <v>4.81414</v>
       </c>
       <c r="G3" t="n">
-        <v>12908</v>
+        <v>12913</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>12004</v>
+        <v>12009</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:05</t>
+          <t>2026-07-24 18:09:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8785</v>
+        <v>3.87912</v>
       </c>
       <c r="G4" t="n">
         <v>4823</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:07</t>
+          <t>2026-07-24 18:09:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86188</v>
+        <v>2.86441</v>
       </c>
       <c r="G5" t="n">
-        <v>2983</v>
+        <v>2987</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="O5" t="n">
         <v>149</v>
       </c>
       <c r="P5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="n">
         <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:09</t>
+          <t>2026-07-24 18:09:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:12</t>
+          <t>2026-07-24 18:09:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.99731</v>
+        <v>3.99543</v>
       </c>
       <c r="G7" t="n">
-        <v>3715</v>
+        <v>3719</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>409</v>
       </c>
       <c r="R7" t="n">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:14</t>
+          <t>2026-07-24 18:09:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:16</t>
+          <t>2026-07-24 18:09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61904</v>
+        <v>4.61958</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:18</t>
+          <t>2026-07-24 18:09:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:21</t>
+          <t>2026-07-24 18:09:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:23</t>
+          <t>2026-07-24 18:09:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73416</v>
+        <v>4.73309</v>
       </c>
       <c r="G12" t="n">
-        <v>2983</v>
+        <v>2986</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2625</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:25</t>
+          <t>2026-07-24 18:09:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:27</t>
+          <t>2026-07-24 18:09:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:29</t>
+          <t>2026-07-24 18:09:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-23 18:05:32</t>
+          <t>2026-07-24 18:09:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74636</v>
+        <v>4.74633</v>
       </c>
       <c r="G16" t="n">
-        <v>31817</v>
+        <v>31833</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>318</v>
       </c>
       <c r="P16" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Q16" t="n">
         <v>1273</v>
       </c>
       <c r="R16" t="n">
-        <v>28317</v>
+        <v>28331</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:14</t>
+          <t>2026-07-25 17:46:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:16</t>
+          <t>2026-07-25 17:46:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81414</v>
+        <v>4.81416</v>
       </c>
       <c r="G3" t="n">
-        <v>12913</v>
+        <v>12914</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>12009</v>
+        <v>12010</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:18</t>
+          <t>2026-07-25 17:46:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:21</t>
+          <t>2026-07-25 17:46:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86441</v>
+        <v>2.8645</v>
       </c>
       <c r="G5" t="n">
-        <v>2987</v>
+        <v>2989</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="O5" t="n">
         <v>149</v>
@@ -802,7 +802,7 @@
         <v>90</v>
       </c>
       <c r="Q5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R5" t="n">
         <v>1225</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:23</t>
+          <t>2026-07-25 17:46:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:25</t>
+          <t>2026-07-25 17:46:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.99543</v>
+        <v>3.99248</v>
       </c>
       <c r="G7" t="n">
-        <v>3719</v>
+        <v>3724</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O7" t="n">
         <v>149</v>
@@ -946,10 +946,10 @@
         <v>186</v>
       </c>
       <c r="Q7" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="R7" t="n">
-        <v>2343</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:28</t>
+          <t>2026-07-25 17:46:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74216</v>
+        <v>4.74214</v>
       </c>
       <c r="G8" t="n">
-        <v>13640</v>
+        <v>13639</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>546</v>
       </c>
       <c r="R8" t="n">
-        <v>12140</v>
+        <v>12139</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:30</t>
+          <t>2026-07-25 17:46:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:32</t>
+          <t>2026-07-25 17:46:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:35</t>
+          <t>2026-07-25 17:46:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:37</t>
+          <t>2026-07-25 17:46:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73309</v>
+        <v>4.73336</v>
       </c>
       <c r="G12" t="n">
-        <v>2986</v>
+        <v>2989</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O12" t="n">
         <v>30</v>
@@ -1309,7 +1309,7 @@
         <v>149</v>
       </c>
       <c r="R12" t="n">
-        <v>2628</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:40</t>
+          <t>2026-07-25 17:46:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.0206</v>
+        <v>4.01495</v>
       </c>
       <c r="G13" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O13" t="n">
         <v>21</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:42</t>
+          <t>2026-07-25 17:46:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:44</t>
+          <t>2026-07-25 17:46:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:46</t>
+          <t>2026-07-25 17:46:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74633</v>
+        <v>4.74626</v>
       </c>
       <c r="G16" t="n">
-        <v>31833</v>
+        <v>31851</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="O16" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P16" t="n">
         <v>637</v>
       </c>
       <c r="Q16" t="n">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="R16" t="n">
-        <v>28331</v>
+        <v>28347</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:17</t>
+          <t>2026-07-26 17:51:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.65089</v>
+        <v>4.64881</v>
       </c>
       <c r="G2" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:20</t>
+          <t>2026-07-26 17:51:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81416</v>
+        <v>4.81393</v>
       </c>
       <c r="G3" t="n">
-        <v>12914</v>
+        <v>12920</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O3" t="n">
         <v>129</v>
@@ -661,7 +661,7 @@
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>12010</v>
+        <v>12016</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:22</t>
+          <t>2026-07-26 17:51:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:24</t>
+          <t>2026-07-26 17:51:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8645</v>
+        <v>2.86388</v>
       </c>
       <c r="G5" t="n">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>1405</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P5" t="n">
         <v>90</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:27</t>
+          <t>2026-07-26 17:51:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:29</t>
+          <t>2026-07-26 17:51:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.99248</v>
+        <v>3.99168</v>
       </c>
       <c r="G7" t="n">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>July 07, 2026</t>
+          <t>July 26, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -949,7 +949,7 @@
         <v>410</v>
       </c>
       <c r="R7" t="n">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:32</t>
+          <t>2026-07-26 17:51:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:34</t>
+          <t>2026-07-26 17:51:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:36</t>
+          <t>2026-07-26 17:51:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:39</t>
+          <t>2026-07-26 17:51:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:41</t>
+          <t>2026-07-26 17:51:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73336</v>
+        <v>4.73637</v>
       </c>
       <c r="G12" t="n">
-        <v>2989</v>
+        <v>2993</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>60</v>
       </c>
       <c r="Q12" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R12" t="n">
-        <v>2630</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:44</t>
+          <t>2026-07-26 17:51:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:46</t>
+          <t>2026-07-26 17:51:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:48</t>
+          <t>2026-07-26 17:51:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:51</t>
+          <t>2026-07-26 17:51:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74626</v>
+        <v>4.74616</v>
       </c>
       <c r="G16" t="n">
-        <v>31851</v>
+        <v>31863</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
@@ -1594,10 +1594,10 @@
         <v>637</v>
       </c>
       <c r="Q16" t="n">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="R16" t="n">
-        <v>28347</v>
+        <v>28358</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:16</t>
+          <t>2026-07-27 18:17:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.64881</v>
+        <v>4.65089</v>
       </c>
       <c r="G2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:18</t>
+          <t>2026-07-27 18:17:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81393</v>
+        <v>4.814</v>
       </c>
       <c r="G3" t="n">
-        <v>12920</v>
+        <v>12925</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>12016</v>
+        <v>12020</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:21</t>
+          <t>2026-07-27 18:17:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87912</v>
+        <v>3.87873</v>
       </c>
       <c r="G4" t="n">
-        <v>4823</v>
+        <v>4824</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2990</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:24</t>
+          <t>2026-07-27 18:17:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86388</v>
+        <v>2.86602</v>
       </c>
       <c r="G5" t="n">
-        <v>2990</v>
+        <v>2993</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="O5" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:26</t>
+          <t>2026-07-27 18:17:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:29</t>
+          <t>2026-07-27 18:17:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.99168</v>
+        <v>3.98928</v>
       </c>
       <c r="G7" t="n">
-        <v>3725</v>
+        <v>3732</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O7" t="n">
         <v>149</v>
       </c>
       <c r="P7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q7" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="R7" t="n">
-        <v>2347</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:31</t>
+          <t>2026-07-27 18:17:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:34</t>
+          <t>2026-07-27 18:17:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:36</t>
+          <t>2026-07-27 18:17:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:39</t>
+          <t>2026-07-27 18:17:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:41</t>
+          <t>2026-07-27 18:17:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73637</v>
+        <v>4.73649</v>
       </c>
       <c r="G12" t="n">
-        <v>2993</v>
+        <v>2998</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>150</v>
       </c>
       <c r="R12" t="n">
-        <v>2634</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:44</t>
+          <t>2026-07-27 18:17:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:46</t>
+          <t>2026-07-27 18:17:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:48</t>
+          <t>2026-07-27 18:17:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:51</t>
+          <t>2026-07-27 18:18:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74616</v>
+        <v>4.74627</v>
       </c>
       <c r="G16" t="n">
-        <v>31863</v>
+        <v>31878</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>319</v>
       </c>
       <c r="P16" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q16" t="n">
         <v>1275</v>
       </c>
       <c r="R16" t="n">
-        <v>28358</v>
+        <v>28371</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:29</t>
+          <t>2026-07-28 18:07:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:31</t>
+          <t>2026-07-28 18:07:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.814</v>
+        <v>4.81382</v>
       </c>
       <c r="G3" t="n">
-        <v>12925</v>
+        <v>12934</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.3</t>
+          <t>4.44.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>July 12, 2026</t>
+          <t>July 28, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -658,10 +658,10 @@
         <v>129</v>
       </c>
       <c r="Q3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R3" t="n">
-        <v>12020</v>
+        <v>12029</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:34</t>
+          <t>2026-07-28 18:07:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:36</t>
+          <t>2026-07-28 18:07:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:38</t>
+          <t>2026-07-28 18:07:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:40</t>
+          <t>2026-07-28 18:07:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98928</v>
+        <v>3.98768</v>
       </c>
       <c r="G7" t="n">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O7" t="n">
         <v>149</v>
@@ -949,7 +949,7 @@
         <v>411</v>
       </c>
       <c r="R7" t="n">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:43</t>
+          <t>2026-07-28 18:07:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:45</t>
+          <t>2026-07-28 18:07:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:47</t>
+          <t>2026-07-28 18:07:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:49</t>
+          <t>2026-07-28 18:07:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:52</t>
+          <t>2026-07-28 18:07:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73649</v>
+        <v>4.73618</v>
       </c>
       <c r="G12" t="n">
-        <v>2998</v>
+        <v>3002</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>150</v>
       </c>
       <c r="R12" t="n">
-        <v>2638</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:54</t>
+          <t>2026-07-28 18:07:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:56</t>
+          <t>2026-07-28 18:07:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:58</t>
+          <t>2026-07-28 18:07:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-27 18:18:01</t>
+          <t>2026-07-28 18:07:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74627</v>
+        <v>4.74634</v>
       </c>
       <c r="G16" t="n">
-        <v>31878</v>
+        <v>31889</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
@@ -1594,10 +1594,10 @@
         <v>638</v>
       </c>
       <c r="Q16" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="R16" t="n">
-        <v>28371</v>
+        <v>28381</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:17</t>
+          <t>2026-07-29 18:01:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:20</t>
+          <t>2026-07-29 18:01:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:22</t>
+          <t>2026-07-29 18:01:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:24</t>
+          <t>2026-07-29 18:01:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:26</t>
+          <t>2026-07-29 18:01:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:29</t>
+          <t>2026-07-29 18:01:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:31</t>
+          <t>2026-07-29 18:01:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:34</t>
+          <t>2026-07-29 18:01:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:36</t>
+          <t>2026-07-29 18:01:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:38</t>
+          <t>2026-07-29 18:01:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:40</t>
+          <t>2026-07-29 18:01:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:43</t>
+          <t>2026-07-29 18:01:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:45</t>
+          <t>2026-07-29 18:01:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:47</t>
+          <t>2026-07-29 18:01:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:49</t>
+          <t>2026-07-29 18:01:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:03</t>
+          <t>2026-07-30 18:08:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:05</t>
+          <t>2026-07-30 18:08:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81382</v>
+        <v>4.81324</v>
       </c>
       <c r="G3" t="n">
-        <v>12934</v>
+        <v>12958</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q3" t="n">
         <v>259</v>
       </c>
       <c r="R3" t="n">
-        <v>12029</v>
+        <v>12051</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:08</t>
+          <t>2026-07-30 18:08:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87873</v>
+        <v>3.87816</v>
       </c>
       <c r="G4" t="n">
-        <v>4824</v>
+        <v>4826</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2991</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:10</t>
+          <t>2026-07-30 18:08:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86602</v>
+        <v>2.87</v>
       </c>
       <c r="G5" t="n">
-        <v>2993</v>
+        <v>3000</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="O5" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:13</t>
+          <t>2026-07-30 18:08:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:15</t>
+          <t>2026-07-30 18:08:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98768</v>
+        <v>3.98772</v>
       </c>
       <c r="G7" t="n">
-        <v>3733</v>
+        <v>3745</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.4.7</t>
+          <t>1.4.9</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,23 +933,23 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>July 26, 2026</t>
+          <t>July 29, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P7" t="n">
         <v>187</v>
       </c>
       <c r="Q7" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="R7" t="n">
-        <v>2352</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:17</t>
+          <t>2026-07-30 18:08:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74214</v>
+        <v>4.7421</v>
       </c>
       <c r="G8" t="n">
-        <v>13639</v>
+        <v>13637</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1005,11 +1005,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>July 11, 2026</t>
+          <t>July 29, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12139</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:20</t>
+          <t>2026-07-30 18:08:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:22</t>
+          <t>2026-07-30 18:08:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:25</t>
+          <t>2026-07-30 18:08:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:27</t>
+          <t>2026-07-30 18:08:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73618</v>
+        <v>4.73471</v>
       </c>
       <c r="G12" t="n">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>May 19, 2026</t>
+          <t>July 29, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>150</v>
       </c>
       <c r="R12" t="n">
-        <v>2642</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:29</t>
+          <t>2026-07-30 18:08:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:32</t>
+          <t>2026-07-30 18:08:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:34</t>
+          <t>2026-07-30 18:08:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:36</t>
+          <t>2026-07-30 18:08:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74634</v>
+        <v>4.74604</v>
       </c>
       <c r="G16" t="n">
-        <v>31889</v>
+        <v>31919</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
@@ -1594,10 +1594,10 @@
         <v>638</v>
       </c>
       <c r="Q16" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="R16" t="n">
-        <v>28381</v>
+        <v>28408</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:09</t>
+          <t>2026-07-31 18:14:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:11</t>
+          <t>2026-07-31 18:14:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81324</v>
+        <v>4.81317</v>
       </c>
       <c r="G3" t="n">
-        <v>12958</v>
+        <v>12969</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>259</v>
       </c>
       <c r="R3" t="n">
-        <v>12051</v>
+        <v>12061</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:13</t>
+          <t>2026-07-31 18:14:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:15</t>
+          <t>2026-07-31 18:14:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.87</v>
+        <v>2.86893</v>
       </c>
       <c r="G5" t="n">
-        <v>3000</v>
+        <v>3006</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="O5" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:17</t>
+          <t>2026-07-31 18:14:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:20</t>
+          <t>2026-07-31 18:15:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98772</v>
+        <v>3.98773</v>
       </c>
       <c r="G7" t="n">
-        <v>3745</v>
+        <v>3749</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>412</v>
       </c>
       <c r="R7" t="n">
-        <v>2359</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:22</t>
+          <t>2026-07-31 18:15:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7421</v>
+        <v>4.74212</v>
       </c>
       <c r="G8" t="n">
-        <v>13637</v>
+        <v>13638</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R8" t="n">
-        <v>12137</v>
+        <v>12138</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:24</t>
+          <t>2026-07-31 18:15:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:26</t>
+          <t>2026-07-31 18:15:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:29</t>
+          <t>2026-07-31 18:15:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.85366</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:31</t>
+          <t>2026-07-31 18:15:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73471</v>
+        <v>4.73431</v>
       </c>
       <c r="G12" t="n">
-        <v>3008</v>
+        <v>3011</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>60</v>
       </c>
       <c r="Q12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2647</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:33</t>
+          <t>2026-07-31 18:15:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:35</t>
+          <t>2026-07-31 18:15:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:37</t>
+          <t>2026-07-31 18:15:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:40</t>
+          <t>2026-07-31 18:15:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74604</v>
+        <v>4.746</v>
       </c>
       <c r="G16" t="n">
-        <v>31919</v>
+        <v>31949</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
       </c>
       <c r="P16" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q16" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="R16" t="n">
-        <v>28408</v>
+        <v>28435</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:50</t>
+          <t>2026-08-01 17:48:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:52</t>
+          <t>2026-08-01 17:48:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81317</v>
+        <v>4.81289</v>
       </c>
       <c r="G3" t="n">
-        <v>12969</v>
+        <v>12976</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R3" t="n">
-        <v>12061</v>
+        <v>12068</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:54</t>
+          <t>2026-08-01 17:48:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87816</v>
+        <v>3.87736</v>
       </c>
       <c r="G4" t="n">
-        <v>4826</v>
+        <v>4827</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2992</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:56</t>
+          <t>2026-08-01 17:48:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86893</v>
+        <v>2.86583</v>
       </c>
       <c r="G5" t="n">
-        <v>3006</v>
+        <v>3011</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="O5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P5" t="n">
         <v>90</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:59</t>
+          <t>2026-08-01 17:48:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:01</t>
+          <t>2026-08-01 17:48:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98773</v>
+        <v>3.9888</v>
       </c>
       <c r="G7" t="n">
         <v>3749</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:03</t>
+          <t>2026-08-01 17:48:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74212</v>
+        <v>4.74234</v>
       </c>
       <c r="G8" t="n">
         <v>13638</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:05</t>
+          <t>2026-08-01 17:48:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:08</t>
+          <t>2026-08-01 17:48:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:10</t>
+          <t>2026-08-01 17:48:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:12</t>
+          <t>2026-08-01 17:48:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73431</v>
+        <v>4.7305</v>
       </c>
       <c r="G12" t="n">
-        <v>3011</v>
+        <v>3013</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O12" t="n">
         <v>30</v>
@@ -1309,7 +1309,7 @@
         <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2650</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:14</t>
+          <t>2026-08-01 17:48:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:17</t>
+          <t>2026-08-01 17:48:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:19</t>
+          <t>2026-08-01 17:48:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31 18:15:21</t>
+          <t>2026-08-01 17:48:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.746</v>
+        <v>4.74573</v>
       </c>
       <c r="G16" t="n">
-        <v>31949</v>
+        <v>31958</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1278</v>
       </c>
       <c r="O16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P16" t="n">
         <v>639</v>
@@ -1597,7 +1597,7 @@
         <v>1278</v>
       </c>
       <c r="R16" t="n">
-        <v>28435</v>
+        <v>28443</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:06</t>
+          <t>2026-08-02 17:49:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:08</t>
+          <t>2026-08-02 17:49:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81289</v>
+        <v>4.81264</v>
       </c>
       <c r="G3" t="n">
-        <v>12976</v>
+        <v>12981</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>12068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:11</t>
+          <t>2026-08-02 17:49:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87736</v>
+        <v>3.87676</v>
       </c>
       <c r="G4" t="n">
-        <v>4827</v>
+        <v>4828</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="O4" t="n">
         <v>241</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:13</t>
+          <t>2026-08-02 17:49:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86583</v>
+        <v>2.86521</v>
       </c>
       <c r="G5" t="n">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="O5" t="n">
         <v>151</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:15</t>
+          <t>2026-08-02 17:49:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:18</t>
+          <t>2026-08-02 17:49:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9888</v>
+        <v>3.988</v>
       </c>
       <c r="G7" t="n">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O7" t="n">
         <v>150</v>
       </c>
       <c r="P7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q7" t="n">
         <v>412</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:20</t>
+          <t>2026-08-02 17:49:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:22</t>
+          <t>2026-08-02 17:49:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:25</t>
+          <t>2026-08-02 17:49:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:27</t>
+          <t>2026-08-02 17:49:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:29</t>
+          <t>2026-08-02 17:49:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7305</v>
+        <v>4.73068</v>
       </c>
       <c r="G12" t="n">
-        <v>3013</v>
+        <v>3015</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2651</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:31</t>
+          <t>2026-08-02 17:49:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01495</v>
+        <v>4.01679</v>
       </c>
       <c r="G13" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:33</t>
+          <t>2026-08-02 17:49:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:35</t>
+          <t>2026-08-02 17:49:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:38</t>
+          <t>2026-08-02 17:49:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74573</v>
+        <v>4.7462</v>
       </c>
       <c r="G16" t="n">
-        <v>31958</v>
+        <v>31975</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="O16" t="n">
         <v>320</v>
       </c>
       <c r="P16" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Q16" t="n">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="R16" t="n">
-        <v>28443</v>
+        <v>28458</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:06</t>
+          <t>2026-08-03 18:30:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:08</t>
+          <t>2026-08-03 18:30:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81264</v>
+        <v>4.81276</v>
       </c>
       <c r="G3" t="n">
-        <v>12981</v>
+        <v>12994</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>12084</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:10</t>
+          <t>2026-08-03 18:30:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87676</v>
+        <v>3.87616</v>
       </c>
       <c r="G4" t="n">
-        <v>4828</v>
+        <v>4829</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2993</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:13</t>
+          <t>2026-08-03 18:30:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86521</v>
+        <v>2.86448</v>
       </c>
       <c r="G5" t="n">
-        <v>3012</v>
+        <v>3018</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="O5" t="n">
         <v>151</v>
       </c>
       <c r="P5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R5" t="n">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:15</t>
+          <t>2026-08-03 18:30:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.14085</v>
+        <v>3.12587</v>
       </c>
       <c r="G6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:17</t>
+          <t>2026-08-03 18:30:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.988</v>
+        <v>3.98747</v>
       </c>
       <c r="G7" t="n">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>188</v>
       </c>
       <c r="Q7" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:19</t>
+          <t>2026-08-03 18:30:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:21</t>
+          <t>2026-08-03 18:30:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61958</v>
+        <v>4.61872</v>
       </c>
       <c r="G9" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:23</t>
+          <t>2026-08-03 18:31:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87429</v>
+        <v>3.87536</v>
       </c>
       <c r="G10" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>672</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:26</t>
+          <t>2026-08-03 18:31:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:28</t>
+          <t>2026-08-03 18:31:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73068</v>
+        <v>4.73027</v>
       </c>
       <c r="G12" t="n">
-        <v>3015</v>
+        <v>3018</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2653</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:30</t>
+          <t>2026-08-03 18:31:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-03 18:31:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:34</t>
+          <t>2026-08-03 18:31:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:36</t>
+          <t>2026-08-03 18:31:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7462</v>
+        <v>4.74594</v>
       </c>
       <c r="G16" t="n">
-        <v>31975</v>
+        <v>31996</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="O16" t="n">
         <v>320</v>
@@ -1594,10 +1594,10 @@
         <v>640</v>
       </c>
       <c r="Q16" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="R16" t="n">
-        <v>28458</v>
+        <v>28476</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:39</t>
+          <t>2026-08-04 18:20:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:42</t>
+          <t>2026-08-04 18:20:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81276</v>
+        <v>4.81277</v>
       </c>
       <c r="G3" t="n">
-        <v>12994</v>
+        <v>13000</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>260</v>
       </c>
       <c r="R3" t="n">
-        <v>12084</v>
+        <v>12090</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:45</t>
+          <t>2026-08-04 18:20:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:47</t>
+          <t>2026-08-04 18:20:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86448</v>
+        <v>2.86519</v>
       </c>
       <c r="G5" t="n">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="O5" t="n">
         <v>151</v>
@@ -805,7 +805,7 @@
         <v>121</v>
       </c>
       <c r="R5" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:50</t>
+          <t>2026-08-04 18:20:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:53</t>
+          <t>2026-08-04 18:20:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:56</t>
+          <t>2026-08-04 18:20:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74234</v>
+        <v>4.74232</v>
       </c>
       <c r="G8" t="n">
-        <v>13638</v>
+        <v>13637</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12138</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:59</t>
+          <t>2026-08-04 18:20:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61872</v>
+        <v>4.61925</v>
       </c>
       <c r="G9" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:01</t>
+          <t>2026-08-04 18:20:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:04</t>
+          <t>2026-08-04 18:20:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:07</t>
+          <t>2026-08-04 18:21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.73027</v>
+        <v>4.72998</v>
       </c>
       <c r="G12" t="n">
-        <v>3018</v>
+        <v>3022</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2656</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:09</t>
+          <t>2026-08-04 18:21:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:12</t>
+          <t>2026-08-04 18:21:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:15</t>
+          <t>2026-08-04 18:21:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-03 18:31:17</t>
+          <t>2026-08-04 18:21:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74594</v>
+        <v>4.7458</v>
       </c>
       <c r="G16" t="n">
-        <v>31996</v>
+        <v>32012</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1280</v>
       </c>
       <c r="R16" t="n">
-        <v>28476</v>
+        <v>28491</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:38</t>
+          <t>2026-08-05 18:14:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:40</t>
+          <t>2026-08-05 18:14:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:42</t>
+          <t>2026-08-05 18:14:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:44</t>
+          <t>2026-08-05 18:14:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:47</t>
+          <t>2026-08-05 18:14:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:49</t>
+          <t>2026-08-05 18:14:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:51</t>
+          <t>2026-08-05 18:14:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:53</t>
+          <t>2026-08-05 18:14:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:56</t>
+          <t>2026-08-05 18:14:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:58</t>
+          <t>2026-08-05 18:14:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04 18:21:00</t>
+          <t>2026-08-05 18:14:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-04 18:21:02</t>
+          <t>2026-08-05 18:14:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-04 18:21:04</t>
+          <t>2026-08-05 18:14:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-04 18:21:07</t>
+          <t>2026-08-05 18:14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-04 18:21:09</t>
+          <t>2026-08-05 18:14:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:02</t>
+          <t>2026-08-07 17:38:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.65089</v>
+        <v>4.65294</v>
       </c>
       <c r="G2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:04</t>
+          <t>2026-08-07 17:38:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81277</v>
+        <v>4.81297</v>
       </c>
       <c r="G3" t="n">
-        <v>13000</v>
+        <v>13036</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O3" t="n">
         <v>130</v>
@@ -658,10 +658,10 @@
         <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R3" t="n">
-        <v>12090</v>
+        <v>12123</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:06</t>
+          <t>2026-08-07 17:38:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87616</v>
+        <v>3.87518</v>
       </c>
       <c r="G4" t="n">
-        <v>4829</v>
+        <v>4831</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -724,16 +724,16 @@
         <v>966</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q4" t="n">
         <v>386</v>
       </c>
       <c r="R4" t="n">
-        <v>2994</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:08</t>
+          <t>2026-08-07 17:38:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86519</v>
+        <v>2.86326</v>
       </c>
       <c r="G5" t="n">
-        <v>3019</v>
+        <v>3035</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="O5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P5" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>121</v>
       </c>
       <c r="R5" t="n">
-        <v>1238</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:11</t>
+          <t>2026-08-07 17:38:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12587</v>
+        <v>3.13889</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:13</t>
+          <t>2026-08-07 17:38:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:15</t>
+          <t>2026-08-07 17:38:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74232</v>
+        <v>4.74206</v>
       </c>
       <c r="G8" t="n">
-        <v>13637</v>
+        <v>13639</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R8" t="n">
-        <v>12137</v>
+        <v>12139</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:17</t>
+          <t>2026-08-07 17:38:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61925</v>
+        <v>4.61872</v>
       </c>
       <c r="G9" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:19</t>
+          <t>2026-08-07 17:38:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:21</t>
+          <t>2026-08-07 17:38:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:24</t>
+          <t>2026-08-07 17:38:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72998</v>
+        <v>4.72862</v>
       </c>
       <c r="G12" t="n">
-        <v>3022</v>
+        <v>3029</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>July 29, 2026</t>
+          <t>August 06, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1303,13 +1303,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
         <v>151</v>
       </c>
       <c r="R12" t="n">
-        <v>2659</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:26</t>
+          <t>2026-08-07 17:38:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:28</t>
+          <t>2026-08-07 17:38:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:30</t>
+          <t>2026-08-07 17:38:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-05 18:14:32</t>
+          <t>2026-08-07 17:38:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7458</v>
+        <v>4.74442</v>
       </c>
       <c r="G16" t="n">
-        <v>32012</v>
+        <v>32053</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="O16" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P16" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q16" t="n">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="R16" t="n">
-        <v>28491</v>
+        <v>28527</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:01</t>
+          <t>2026-08-08 17:19:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:03</t>
+          <t>2026-08-08 17:19:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81297</v>
+        <v>4.81216</v>
       </c>
       <c r="G3" t="n">
-        <v>13036</v>
+        <v>13043</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>261</v>
       </c>
       <c r="R3" t="n">
-        <v>12123</v>
+        <v>12130</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:06</t>
+          <t>2026-08-08 17:19:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87518</v>
+        <v>3.87363</v>
       </c>
       <c r="G4" t="n">
-        <v>4831</v>
+        <v>4835</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="O4" t="n">
         <v>242</v>
@@ -730,10 +730,10 @@
         <v>242</v>
       </c>
       <c r="Q4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R4" t="n">
-        <v>2995</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:08</t>
+          <t>2026-08-08 17:19:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86326</v>
+        <v>2.86203</v>
       </c>
       <c r="G5" t="n">
-        <v>3035</v>
+        <v>3037</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
@@ -805,7 +805,7 @@
         <v>121</v>
       </c>
       <c r="R5" t="n">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:10</t>
+          <t>2026-08-08 17:19:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:13</t>
+          <t>2026-08-08 17:19:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98747</v>
+        <v>3.98614</v>
       </c>
       <c r="G7" t="n">
-        <v>3751</v>
+        <v>3753</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2363</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:15</t>
+          <t>2026-08-08 17:19:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:17</t>
+          <t>2026-08-08 17:19:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:19</t>
+          <t>2026-08-08 17:19:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:22</t>
+          <t>2026-08-08 17:19:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:24</t>
+          <t>2026-08-08 17:19:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72862</v>
+        <v>4.72525</v>
       </c>
       <c r="G12" t="n">
-        <v>3029</v>
+        <v>3032</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2666</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:26</t>
+          <t>2026-08-08 17:19:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:28</t>
+          <t>2026-08-08 17:19:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:31</t>
+          <t>2026-08-08 17:19:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-07 17:38:33</t>
+          <t>2026-08-08 17:19:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74442</v>
+        <v>4.7445</v>
       </c>
       <c r="G16" t="n">
-        <v>32053</v>
+        <v>32062</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1282</v>
       </c>
       <c r="R16" t="n">
-        <v>28527</v>
+        <v>28535</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:09</t>
+          <t>2026-08-09 17:19:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:11</t>
+          <t>2026-08-09 17:19:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81216</v>
+        <v>4.81203</v>
       </c>
       <c r="G3" t="n">
-        <v>13043</v>
+        <v>13055</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q3" t="n">
         <v>261</v>
       </c>
       <c r="R3" t="n">
-        <v>12130</v>
+        <v>12141</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:14</t>
+          <t>2026-08-09 17:20:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:16</t>
+          <t>2026-08-09 17:20:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86203</v>
+        <v>2.85959</v>
       </c>
       <c r="G5" t="n">
-        <v>3037</v>
+        <v>3041</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
@@ -802,10 +802,10 @@
         <v>91</v>
       </c>
       <c r="Q5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:18</t>
+          <t>2026-08-09 17:20:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:21</t>
+          <t>2026-08-09 17:20:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:23</t>
+          <t>2026-08-09 17:20:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74206</v>
+        <v>4.7421</v>
       </c>
       <c r="G8" t="n">
-        <v>13639</v>
+        <v>13637</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
         <v>136</v>
@@ -1018,10 +1018,10 @@
         <v>273</v>
       </c>
       <c r="Q8" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12139</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:25</t>
+          <t>2026-08-09 17:20:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:28</t>
+          <t>2026-08-09 17:20:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:30</t>
+          <t>2026-08-09 17:20:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:32</t>
+          <t>2026-08-09 17:20:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72525</v>
+        <v>4.72535</v>
       </c>
       <c r="G12" t="n">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2668</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:34</t>
+          <t>2026-08-09 17:20:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:37</t>
+          <t>2026-08-09 17:20:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:39</t>
+          <t>2026-08-09 17:20:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:41</t>
+          <t>2026-08-09 17:20:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7445</v>
+        <v>4.74429</v>
       </c>
       <c r="G16" t="n">
-        <v>32062</v>
+        <v>32071</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="O16" t="n">
         <v>321</v>
@@ -1594,10 +1594,10 @@
         <v>641</v>
       </c>
       <c r="Q16" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="R16" t="n">
-        <v>28535</v>
+        <v>28543</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:57</t>
+          <t>2026-08-10 17:41:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:59</t>
+          <t>2026-08-10 17:41:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81203</v>
+        <v>4.81191</v>
       </c>
       <c r="G3" t="n">
-        <v>13055</v>
+        <v>13063</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>261</v>
       </c>
       <c r="R3" t="n">
-        <v>12141</v>
+        <v>12149</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:02</t>
+          <t>2026-08-10 17:41:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:05</t>
+          <t>2026-08-10 17:41:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85959</v>
+        <v>2.86213</v>
       </c>
       <c r="G5" t="n">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:07</t>
+          <t>2026-08-10 17:41:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:10</t>
+          <t>2026-08-10 17:41:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98614</v>
+        <v>3.98694</v>
       </c>
       <c r="G7" t="n">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:12</t>
+          <t>2026-08-10 17:41:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7421</v>
+        <v>4.7422</v>
       </c>
       <c r="G8" t="n">
-        <v>13637</v>
+        <v>13627</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12137</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:15</t>
+          <t>2026-08-10 17:41:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61872</v>
+        <v>4.61367</v>
       </c>
       <c r="G9" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:17</t>
+          <t>2026-08-10 17:41:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:20</t>
+          <t>2026-08-10 17:41:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:23</t>
+          <t>2026-08-10 17:41:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72535</v>
+        <v>4.72625</v>
       </c>
       <c r="G12" t="n">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2669</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:25</t>
+          <t>2026-08-10 17:41:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:27</t>
+          <t>2026-08-10 17:41:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:30</t>
+          <t>2026-08-10 17:42:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-09 17:20:33</t>
+          <t>2026-08-10 17:42:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74429</v>
+        <v>4.74401</v>
       </c>
       <c r="G16" t="n">
-        <v>32071</v>
+        <v>32079</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>321</v>
       </c>
       <c r="P16" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Q16" t="n">
         <v>1283</v>
       </c>
       <c r="R16" t="n">
-        <v>28543</v>
+        <v>28550</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:32</t>
+          <t>2026-08-11 17:45:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.65294</v>
+        <v>4.65089</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:35</t>
+          <t>2026-08-11 17:45:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81191</v>
+        <v>4.81201</v>
       </c>
       <c r="G3" t="n">
-        <v>13063</v>
+        <v>13070</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>261</v>
       </c>
       <c r="R3" t="n">
-        <v>12149</v>
+        <v>12155</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:37</t>
+          <t>2026-08-11 17:45:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:39</t>
+          <t>2026-08-11 17:46:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86213</v>
+        <v>2.86231</v>
       </c>
       <c r="G5" t="n">
-        <v>3039</v>
+        <v>3043</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:41</t>
+          <t>2026-08-11 17:46:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.13889</v>
+        <v>3.12414</v>
       </c>
       <c r="G6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:43</t>
+          <t>2026-08-11 17:46:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:46</t>
+          <t>2026-08-11 17:46:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:48</t>
+          <t>2026-08-11 17:46:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:50</t>
+          <t>2026-08-11 17:46:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:52</t>
+          <t>2026-08-11 17:46:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>July 09, 2026</t>
+          <t>August 11, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:54</t>
+          <t>2026-08-11 17:46:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72625</v>
+        <v>4.7267</v>
       </c>
       <c r="G12" t="n">
-        <v>3032</v>
+        <v>3037</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2668</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:56</t>
+          <t>2026-08-11 17:46:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:59</t>
+          <t>2026-08-11 17:46:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:42:01</t>
+          <t>2026-08-11 17:46:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:42:03</t>
+          <t>2026-08-11 17:46:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74401</v>
+        <v>4.74383</v>
       </c>
       <c r="G16" t="n">
-        <v>32079</v>
+        <v>32100</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O16" t="n">
         <v>321</v>
@@ -1594,10 +1594,10 @@
         <v>642</v>
       </c>
       <c r="Q16" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="R16" t="n">
-        <v>28550</v>
+        <v>28569</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:54</t>
+          <t>2026-08-12 17:47:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.65089</v>
+        <v>4.64706</v>
       </c>
       <c r="G2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:56</t>
+          <t>2026-08-12 17:47:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81201</v>
+        <v>4.81208</v>
       </c>
       <c r="G3" t="n">
-        <v>13070</v>
+        <v>13075</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>131</v>
       </c>
       <c r="Q3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12155</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:58</t>
+          <t>2026-08-12 17:47:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87363</v>
+        <v>3.87446</v>
       </c>
       <c r="G4" t="n">
         <v>4835</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:00</t>
+          <t>2026-08-12 17:47:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86231</v>
+        <v>2.86108</v>
       </c>
       <c r="G5" t="n">
-        <v>3043</v>
+        <v>3045</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:03</t>
+          <t>2026-08-12 17:47:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12414</v>
+        <v>3.10959</v>
       </c>
       <c r="G6" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -871,13 +871,13 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:05</t>
+          <t>2026-08-12 17:47:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98694</v>
+        <v>3.98667</v>
       </c>
       <c r="G7" t="n">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2364</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:07</t>
+          <t>2026-08-12 17:47:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:09</t>
+          <t>2026-08-12 17:47:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:12</t>
+          <t>2026-08-12 17:47:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:14</t>
+          <t>2026-08-12 17:47:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>August 11, 2026</t>
+          <t>August 12, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:16</t>
+          <t>2026-08-12 17:48:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.7267</v>
+        <v>4.72539</v>
       </c>
       <c r="G12" t="n">
         <v>3037</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:18</t>
+          <t>2026-08-12 17:48:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:21</t>
+          <t>2026-08-12 17:48:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:23</t>
+          <t>2026-08-12 17:48:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-11 17:46:25</t>
+          <t>2026-08-12 17:48:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74383</v>
+        <v>4.74404</v>
       </c>
       <c r="G16" t="n">
-        <v>32100</v>
+        <v>32107</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3.1.5</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>August 12, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1597,7 +1597,7 @@
         <v>1284</v>
       </c>
       <c r="R16" t="n">
-        <v>28569</v>
+        <v>28575</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:38</t>
+          <t>2026-08-13 17:46:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:40</t>
+          <t>2026-08-13 17:46:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81208</v>
+        <v>4.81224</v>
       </c>
       <c r="G3" t="n">
-        <v>13075</v>
+        <v>13092</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O3" t="n">
         <v>131</v>
@@ -661,7 +661,7 @@
         <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12160</v>
+        <v>12176</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:42</t>
+          <t>2026-08-13 17:46:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87446</v>
+        <v>3.8741</v>
       </c>
       <c r="G4" t="n">
-        <v>4835</v>
+        <v>4837</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>387</v>
       </c>
       <c r="R4" t="n">
-        <v>2998</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:44</t>
+          <t>2026-08-13 17:46:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86108</v>
+        <v>2.86492</v>
       </c>
       <c r="G5" t="n">
-        <v>3045</v>
+        <v>3050</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="O5" t="n">
         <v>152</v>
       </c>
       <c r="P5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q5" t="n">
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:47</t>
+          <t>2026-08-13 17:46:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:49</t>
+          <t>2026-08-13 17:46:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:51</t>
+          <t>2026-08-13 17:47:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7422</v>
+        <v>4.74218</v>
       </c>
       <c r="G8" t="n">
-        <v>13627</v>
+        <v>13626</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12128</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:54</t>
+          <t>2026-08-13 17:47:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:56</t>
+          <t>2026-08-13 17:47:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:58</t>
+          <t>2026-08-13 17:47:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-12 17:48:01</t>
+          <t>2026-08-13 17:47:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72539</v>
+        <v>4.72524</v>
       </c>
       <c r="G12" t="n">
-        <v>3037</v>
+        <v>3039</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O12" t="n">
         <v>30</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-12 17:48:03</t>
+          <t>2026-08-13 17:47:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-12 17:48:05</t>
+          <t>2026-08-13 17:47:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-12 17:48:07</t>
+          <t>2026-08-13 17:47:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-12 17:48:10</t>
+          <t>2026-08-13 17:47:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74404</v>
+        <v>4.74376</v>
       </c>
       <c r="G16" t="n">
-        <v>32107</v>
+        <v>32124</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28575</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:47</t>
+          <t>2026-08-14 17:42:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:49</t>
+          <t>2026-08-14 17:42:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81224</v>
+        <v>4.81177</v>
       </c>
       <c r="G3" t="n">
-        <v>13092</v>
+        <v>13101</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12176</v>
+        <v>12184</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:52</t>
+          <t>2026-08-14 17:42:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:54</t>
+          <t>2026-08-14 17:42:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86492</v>
+        <v>2.86431</v>
       </c>
       <c r="G5" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>1434</v>
       </c>
       <c r="O5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>92</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:56</t>
+          <t>2026-08-14 17:43:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.10959</v>
+        <v>3.12245</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:59</t>
+          <t>2026-08-14 17:43:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98667</v>
+        <v>3.98694</v>
       </c>
       <c r="G7" t="n">
-        <v>3751</v>
+        <v>3752</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2363</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:01</t>
+          <t>2026-08-14 17:43:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74218</v>
+        <v>4.74217</v>
       </c>
       <c r="G8" t="n">
-        <v>13626</v>
+        <v>13625</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12127</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:03</t>
+          <t>2026-08-14 17:43:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:06</t>
+          <t>2026-08-14 17:43:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:08</t>
+          <t>2026-08-14 17:43:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:10</t>
+          <t>2026-08-14 17:43:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72524</v>
+        <v>4.72542</v>
       </c>
       <c r="G12" t="n">
-        <v>3039</v>
+        <v>3041</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2674</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:13</t>
+          <t>2026-08-14 17:43:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:15</t>
+          <t>2026-08-14 17:43:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:18</t>
+          <t>2026-08-14 17:43:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-13 17:47:20</t>
+          <t>2026-08-14 17:43:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74376</v>
+        <v>4.74383</v>
       </c>
       <c r="G16" t="n">
-        <v>32124</v>
+        <v>32136</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>28601</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:51</t>
+          <t>2026-08-15 17:10:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.64706</v>
+        <v>4.62573</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:53</t>
+          <t>2026-08-15 17:10:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81177</v>
+        <v>4.81186</v>
       </c>
       <c r="G3" t="n">
-        <v>13101</v>
+        <v>13107</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12184</v>
+        <v>12190</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:56</t>
+          <t>2026-08-15 17:10:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:59</t>
+          <t>2026-08-15 17:10:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86431</v>
+        <v>2.86426</v>
       </c>
       <c r="G5" t="n">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>1434</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P5" t="n">
         <v>92</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:01</t>
+          <t>2026-08-15 17:10:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:03</t>
+          <t>2026-08-15 17:10:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>3.98694</v>
       </c>
       <c r="G7" t="n">
-        <v>3752</v>
+        <v>3753</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:06</t>
+          <t>2026-08-15 17:11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74217</v>
+        <v>4.74218</v>
       </c>
       <c r="G8" t="n">
-        <v>13625</v>
+        <v>13626</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12126</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:08</t>
+          <t>2026-08-15 17:11:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:10</t>
+          <t>2026-08-15 17:11:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:12</t>
+          <t>2026-08-15 17:11:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:15</t>
+          <t>2026-08-15 17:11:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72542</v>
+        <v>4.72438</v>
       </c>
       <c r="G12" t="n">
-        <v>3041</v>
+        <v>3044</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2676</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:17</t>
+          <t>2026-08-15 17:11:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01679</v>
+        <v>4.01682</v>
       </c>
       <c r="G13" t="n">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:19</t>
+          <t>2026-08-15 17:11:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:22</t>
+          <t>2026-08-15 17:11:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-14 17:43:24</t>
+          <t>2026-08-15 17:11:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74383</v>
+        <v>4.74376</v>
       </c>
       <c r="G16" t="n">
-        <v>32136</v>
+        <v>32143</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="O16" t="n">
         <v>321</v>
@@ -1594,10 +1594,10 @@
         <v>643</v>
       </c>
       <c r="Q16" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="R16" t="n">
-        <v>28601</v>
+        <v>28607</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:46</t>
+          <t>2026-08-16 17:09:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:48</t>
+          <t>2026-08-16 17:09:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81186</v>
+        <v>4.81161</v>
       </c>
       <c r="G3" t="n">
-        <v>13107</v>
+        <v>13111</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12190</v>
+        <v>12193</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:50</t>
+          <t>2026-08-16 17:09:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:53</t>
+          <t>2026-08-16 17:09:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86426</v>
+        <v>2.86496</v>
       </c>
       <c r="G5" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>1434</v>
       </c>
       <c r="O5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>92</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:55</t>
+          <t>2026-08-16 17:09:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:58</t>
+          <t>2026-08-16 17:10:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98694</v>
+        <v>3.98695</v>
       </c>
       <c r="G7" t="n">
-        <v>3753</v>
+        <v>3755</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2364</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:00</t>
+          <t>2026-08-16 17:10:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:02</t>
+          <t>2026-08-16 17:10:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>May 30, 2026</t>
+          <t>August 16, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:04</t>
+          <t>2026-08-16 17:10:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87536</v>
+        <v>3.87643</v>
       </c>
       <c r="G10" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:07</t>
+          <t>2026-08-16 17:10:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:09</t>
+          <t>2026-08-16 17:10:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72438</v>
+        <v>4.72259</v>
       </c>
       <c r="G12" t="n">
-        <v>3044</v>
+        <v>3046</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2679</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:12</t>
+          <t>2026-08-16 17:10:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01682</v>
+        <v>4.01119</v>
       </c>
       <c r="G13" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:14</t>
+          <t>2026-08-16 17:10:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:16</t>
+          <t>2026-08-16 17:10:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-15 17:11:18</t>
+          <t>2026-08-16 17:10:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74376</v>
+        <v>4.74383</v>
       </c>
       <c r="G16" t="n">
-        <v>32143</v>
+        <v>32152</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1286</v>
       </c>
       <c r="O16" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P16" t="n">
         <v>643</v>
@@ -1597,7 +1597,7 @@
         <v>1286</v>
       </c>
       <c r="R16" t="n">
-        <v>28607</v>
+        <v>28615</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:48</t>
+          <t>2026-08-17 17:15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:50</t>
+          <t>2026-08-17 17:15:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81161</v>
+        <v>4.8118</v>
       </c>
       <c r="G3" t="n">
-        <v>13111</v>
+        <v>13124</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O3" t="n">
         <v>131</v>
@@ -661,7 +661,7 @@
         <v>262</v>
       </c>
       <c r="R3" t="n">
-        <v>12193</v>
+        <v>12205</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:53</t>
+          <t>2026-08-17 17:15:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:55</t>
+          <t>2026-08-17 17:15:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86496</v>
+        <v>2.86444</v>
       </c>
       <c r="G5" t="n">
-        <v>3051</v>
+        <v>3054</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:58</t>
+          <t>2026-08-17 17:15:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:01</t>
+          <t>2026-08-17 17:15:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98695</v>
+        <v>3.98643</v>
       </c>
       <c r="G7" t="n">
-        <v>3755</v>
+        <v>3757</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O7" t="n">
         <v>150</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:03</t>
+          <t>2026-08-17 17:15:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:06</t>
+          <t>2026-08-17 17:15:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:08</t>
+          <t>2026-08-17 17:15:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:11</t>
+          <t>2026-08-17 17:15:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>August 12, 2026</t>
+          <t>August 17, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:14</t>
+          <t>2026-08-17 17:15:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72259</v>
+        <v>4.72137</v>
       </c>
       <c r="G12" t="n">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2680</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:16</t>
+          <t>2026-08-17 17:15:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:19</t>
+          <t>2026-08-17 17:15:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:21</t>
+          <t>2026-08-17 17:16:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-16 17:10:24</t>
+          <t>2026-08-17 17:16:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74383</v>
+        <v>4.74375</v>
       </c>
       <c r="G16" t="n">
-        <v>32152</v>
+        <v>32164</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="O16" t="n">
         <v>322</v>
@@ -1594,10 +1594,10 @@
         <v>643</v>
       </c>
       <c r="Q16" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="R16" t="n">
-        <v>28615</v>
+        <v>28626</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:30</t>
+          <t>2026-08-18 17:24:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:32</t>
+          <t>2026-08-18 17:24:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8118</v>
+        <v>4.81166</v>
       </c>
       <c r="G3" t="n">
-        <v>13124</v>
+        <v>13136</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.5</t>
+          <t>4.45.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>July 28, 2026</t>
+          <t>August 18, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -658,10 +658,10 @@
         <v>131</v>
       </c>
       <c r="Q3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R3" t="n">
-        <v>12205</v>
+        <v>12216</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:35</t>
+          <t>2026-08-18 17:24:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.0</t>
+          <t>2.22.1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>June 08, 2026</t>
+          <t>August 18, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:37</t>
+          <t>2026-08-18 17:24:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86444</v>
+        <v>2.86453</v>
       </c>
       <c r="G5" t="n">
-        <v>3054</v>
+        <v>3056</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:39</t>
+          <t>2026-08-18 17:24:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:42</t>
+          <t>2026-08-18 17:24:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98643</v>
+        <v>3.98563</v>
       </c>
       <c r="G7" t="n">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>413</v>
       </c>
       <c r="R7" t="n">
-        <v>2367</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:44</t>
+          <t>2026-08-18 17:24:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74218</v>
+        <v>4.74217</v>
       </c>
       <c r="G8" t="n">
-        <v>13626</v>
+        <v>13625</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>136</v>
       </c>
       <c r="P8" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q8" t="n">
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12127</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:47</t>
+          <t>2026-08-18 17:24:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:49</t>
+          <t>2026-08-18 17:24:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:51</t>
+          <t>2026-08-18 17:24:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.85366</v>
+        <v>2.83333</v>
       </c>
       <c r="G11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:54</t>
+          <t>2026-08-18 17:24:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72137</v>
+        <v>4.72071</v>
       </c>
       <c r="G12" t="n">
         <v>3047</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:56</t>
+          <t>2026-08-18 17:24:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:59</t>
+          <t>2026-08-18 17:24:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-17 17:16:01</t>
+          <t>2026-08-18 17:24:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-17 17:16:03</t>
+          <t>2026-08-18 17:24:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>4.74375</v>
       </c>
       <c r="G16" t="n">
-        <v>32164</v>
+        <v>32175</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>322</v>
       </c>
       <c r="P16" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Q16" t="n">
         <v>1287</v>
       </c>
       <c r="R16" t="n">
-        <v>28626</v>
+        <v>28636</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:22</t>
+          <t>2026-08-19 17:15:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:24</t>
+          <t>2026-08-19 17:15:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81166</v>
+        <v>4.81123</v>
       </c>
       <c r="G3" t="n">
-        <v>13136</v>
+        <v>13148</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>263</v>
       </c>
       <c r="R3" t="n">
-        <v>12216</v>
+        <v>12228</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:27</t>
+          <t>2026-08-19 17:15:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:29</t>
+          <t>2026-08-19 17:15:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86453</v>
+        <v>2.86462</v>
       </c>
       <c r="G5" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:32</t>
+          <t>2026-08-19 17:15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:35</t>
+          <t>2026-08-19 17:15:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:37</t>
+          <t>2026-08-19 17:15:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74217</v>
+        <v>4.74214</v>
       </c>
       <c r="G8" t="n">
-        <v>13625</v>
+        <v>13624</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12126</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:39</t>
+          <t>2026-08-19 17:15:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61367</v>
+        <v>4.61474</v>
       </c>
       <c r="G9" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:42</t>
+          <t>2026-08-19 17:15:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:44</t>
+          <t>2026-08-19 17:15:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:47</t>
+          <t>2026-08-19 17:16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72071</v>
+        <v>4.71982</v>
       </c>
       <c r="G12" t="n">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2681</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:49</t>
+          <t>2026-08-19 17:16:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:52</t>
+          <t>2026-08-19 17:16:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:54</t>
+          <t>2026-08-19 17:16:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:56</t>
+          <t>2026-08-19 17:16:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74375</v>
+        <v>4.74397</v>
       </c>
       <c r="G16" t="n">
-        <v>32175</v>
+        <v>32189</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="O16" t="n">
         <v>322</v>
@@ -1594,10 +1594,10 @@
         <v>644</v>
       </c>
       <c r="Q16" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="R16" t="n">
-        <v>28636</v>
+        <v>28648</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:34</t>
+          <t>2026-08-20 17:17:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:36</t>
+          <t>2026-08-20 17:17:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81123</v>
+        <v>4.81114</v>
       </c>
       <c r="G3" t="n">
-        <v>13148</v>
+        <v>13164</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q3" t="n">
         <v>263</v>
       </c>
       <c r="R3" t="n">
-        <v>12228</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:39</t>
+          <t>2026-08-20 17:17:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:42</t>
+          <t>2026-08-20 17:17:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86462</v>
+        <v>2.86088</v>
       </c>
       <c r="G5" t="n">
-        <v>3058</v>
+        <v>3062</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="R5" t="n">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:45</t>
+          <t>2026-08-20 17:17:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:47</t>
+          <t>2026-08-20 17:17:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98563</v>
+        <v>3.98617</v>
       </c>
       <c r="G7" t="n">
-        <v>3758</v>
+        <v>3760</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>188</v>
       </c>
       <c r="Q7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:50</t>
+          <t>2026-08-20 17:17:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:52</t>
+          <t>2026-08-20 17:18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:55</t>
+          <t>2026-08-20 17:18:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:57</t>
+          <t>2026-08-20 17:18:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>August 17, 2026</t>
+          <t>August 20, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19 17:16:00</t>
+          <t>2026-08-20 17:18:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71982</v>
+        <v>4.72089</v>
       </c>
       <c r="G12" t="n">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>August 06, 2026</t>
+          <t>August 20, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="n">
-        <v>2682</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-19 17:16:03</t>
+          <t>2026-08-20 17:18:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-19 17:16:05</t>
+          <t>2026-08-20 17:18:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19 17:16:09</t>
+          <t>2026-08-20 17:18:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-19 17:16:11</t>
+          <t>2026-08-20 17:18:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74397</v>
+        <v>4.74399</v>
       </c>
       <c r="G16" t="n">
-        <v>32189</v>
+        <v>32194</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1288</v>
       </c>
       <c r="R16" t="n">
-        <v>28648</v>
+        <v>28653</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:44</t>
+          <t>2026-08-21 17:17:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:46</t>
+          <t>2026-08-21 17:17:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81114</v>
+        <v>4.81128</v>
       </c>
       <c r="G3" t="n">
-        <v>13164</v>
+        <v>13173</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>263</v>
       </c>
       <c r="R3" t="n">
-        <v>12243</v>
+        <v>12251</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:48</t>
+          <t>2026-08-21 17:17:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:51</t>
+          <t>2026-08-21 17:17:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86088</v>
+        <v>2.85975</v>
       </c>
       <c r="G5" t="n">
-        <v>3062</v>
+        <v>3066</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -802,10 +802,10 @@
         <v>92</v>
       </c>
       <c r="Q5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:53</t>
+          <t>2026-08-21 17:17:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:56</t>
+          <t>2026-08-21 17:17:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98617</v>
+        <v>3.98458</v>
       </c>
       <c r="G7" t="n">
-        <v>3760</v>
+        <v>3762</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O7" t="n">
         <v>150</v>
@@ -949,7 +949,7 @@
         <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:58</t>
+          <t>2026-08-21 17:17:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:00</t>
+          <t>2026-08-21 17:17:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61474</v>
+        <v>4.61388</v>
       </c>
       <c r="G9" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:03</t>
+          <t>2026-08-21 17:17:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:05</t>
+          <t>2026-08-21 17:17:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:07</t>
+          <t>2026-08-21 17:17:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.72089</v>
+        <v>4.71924</v>
       </c>
       <c r="G12" t="n">
-        <v>3049</v>
+        <v>3056</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1300,16 +1300,16 @@
         <v>122</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
         <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>2683</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:09</t>
+          <t>2026-08-21 17:18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:12</t>
+          <t>2026-08-21 17:18:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:14</t>
+          <t>2026-08-21 17:18:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-20 17:18:16</t>
+          <t>2026-08-21 17:18:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74399</v>
+        <v>4.74432</v>
       </c>
       <c r="G16" t="n">
-        <v>32194</v>
+        <v>32216</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="O16" t="n">
         <v>322</v>
@@ -1594,10 +1594,10 @@
         <v>644</v>
       </c>
       <c r="Q16" t="n">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="R16" t="n">
-        <v>28653</v>
+        <v>28672</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:32</t>
+          <t>2026-08-22 17:10:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:34</t>
+          <t>2026-08-22 17:10:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81128</v>
+        <v>4.81134</v>
       </c>
       <c r="G3" t="n">
-        <v>13173</v>
+        <v>13177</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>132</v>
       </c>
       <c r="Q3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R3" t="n">
-        <v>12251</v>
+        <v>12255</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:37</t>
+          <t>2026-08-22 17:10:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:40</t>
+          <t>2026-08-22 17:10:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85975</v>
+        <v>2.86036</v>
       </c>
       <c r="G5" t="n">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:42</t>
+          <t>2026-08-22 17:10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12245</v>
+        <v>3.11486</v>
       </c>
       <c r="G6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:45</t>
+          <t>2026-08-22 17:10:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:47</t>
+          <t>2026-08-22 17:10:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:50</t>
+          <t>2026-08-22 17:10:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:52</t>
+          <t>2026-08-22 17:10:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:55</t>
+          <t>2026-08-22 17:10:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.83333</v>
+        <v>2.7907</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:57</t>
+          <t>2026-08-22 17:10:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71924</v>
+        <v>4.71826</v>
       </c>
       <c r="G12" t="n">
         <v>3056</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 17:18:00</t>
+          <t>2026-08-22 17:10:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 17:18:02</t>
+          <t>2026-08-22 17:10:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 17:18:05</t>
+          <t>2026-08-22 17:10:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 17:18:07</t>
+          <t>2026-08-22 17:10:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74432</v>
+        <v>4.74423</v>
       </c>
       <c r="G16" t="n">
-        <v>32216</v>
+        <v>32220</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1289</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1289</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28672</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:22</t>
+          <t>2026-08-23 17:10:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:24</t>
+          <t>2026-08-23 17:10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81134</v>
+        <v>4.81148</v>
       </c>
       <c r="G3" t="n">
-        <v>13177</v>
+        <v>13187</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O3" t="n">
         <v>132</v>
@@ -661,7 +661,7 @@
         <v>264</v>
       </c>
       <c r="R3" t="n">
-        <v>12255</v>
+        <v>12264</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:26</t>
+          <t>2026-08-23 17:10:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:28</t>
+          <t>2026-08-23 17:10:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86036</v>
+        <v>2.86045</v>
       </c>
       <c r="G5" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:30</t>
+          <t>2026-08-23 17:10:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:33</t>
+          <t>2026-08-23 17:10:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98458</v>
+        <v>3.98379</v>
       </c>
       <c r="G7" t="n">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>640</v>
       </c>
       <c r="O7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>188</v>
@@ -949,7 +949,7 @@
         <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:35</t>
+          <t>2026-08-23 17:10:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:37</t>
+          <t>2026-08-23 17:10:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:39</t>
+          <t>2026-08-23 17:10:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87643</v>
+        <v>3.87369</v>
       </c>
       <c r="G10" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:41</t>
+          <t>2026-08-23 17:10:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7907</v>
+        <v>2.75</v>
       </c>
       <c r="G11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:43</t>
+          <t>2026-08-23 17:10:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71826</v>
+        <v>4.71854</v>
       </c>
       <c r="G12" t="n">
-        <v>3056</v>
+        <v>3059</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:45</t>
+          <t>2026-08-23 17:10:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01119</v>
+        <v>4.01304</v>
       </c>
       <c r="G13" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:46</t>
+          <t>2026-08-23 17:10:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:48</t>
+          <t>2026-08-23 17:10:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:50</t>
+          <t>2026-08-23 17:11:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74423</v>
+        <v>4.74443</v>
       </c>
       <c r="G16" t="n">
-        <v>32220</v>
+        <v>32242</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>28695</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:27</t>
+          <t>2026-08-24 17:20:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:30</t>
+          <t>2026-08-24 17:20:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81148</v>
+        <v>4.81156</v>
       </c>
       <c r="G3" t="n">
-        <v>13187</v>
+        <v>13198</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>264</v>
       </c>
       <c r="R3" t="n">
-        <v>12264</v>
+        <v>12274</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:32</t>
+          <t>2026-08-24 17:20:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:35</t>
+          <t>2026-08-24 17:20:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86045</v>
+        <v>2.86054</v>
       </c>
       <c r="G5" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="O5" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:37</t>
+          <t>2026-08-24 17:20:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.11486</v>
+        <v>3.12752</v>
       </c>
       <c r="G6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
         <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:39</t>
+          <t>2026-08-24 17:20:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98379</v>
+        <v>3.98406</v>
       </c>
       <c r="G7" t="n">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:41</t>
+          <t>2026-08-24 17:20:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:44</t>
+          <t>2026-08-24 17:20:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:46</t>
+          <t>2026-08-24 17:20:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:49</t>
+          <t>2026-08-24 17:20:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.75</v>
+        <v>2.72727</v>
       </c>
       <c r="G11" t="n">
         <v>44</v>
@@ -1228,10 +1228,10 @@
         <v>23</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:51</t>
+          <t>2026-08-24 17:20:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71854</v>
+        <v>4.71638</v>
       </c>
       <c r="G12" t="n">
-        <v>3059</v>
+        <v>3064</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O12" t="n">
         <v>31</v>
@@ -1309,7 +1309,7 @@
         <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>2692</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:54</t>
+          <t>2026-08-24 17:20:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:56</t>
+          <t>2026-08-24 17:20:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:58</t>
+          <t>2026-08-24 17:20:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-23 17:11:01</t>
+          <t>2026-08-24 17:20:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74443</v>
+        <v>4.74427</v>
       </c>
       <c r="G16" t="n">
-        <v>32242</v>
+        <v>32261</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1290</v>
       </c>
       <c r="O16" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P16" t="n">
         <v>645</v>
@@ -1597,7 +1597,7 @@
         <v>1290</v>
       </c>
       <c r="R16" t="n">
-        <v>28695</v>
+        <v>28712</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:16</t>
+          <t>2026-08-25 17:21:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:18</t>
+          <t>2026-08-25 17:21:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81156</v>
+        <v>4.81171</v>
       </c>
       <c r="G3" t="n">
-        <v>13198</v>
+        <v>13208</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>264</v>
       </c>
       <c r="R3" t="n">
-        <v>12274</v>
+        <v>12283</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:20</t>
+          <t>2026-08-25 17:21:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:23</t>
+          <t>2026-08-25 17:21:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86054</v>
+        <v>2.85882</v>
       </c>
       <c r="G5" t="n">
-        <v>3069</v>
+        <v>3074</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P5" t="n">
         <v>92</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:25</t>
+          <t>2026-08-25 17:21:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:28</t>
+          <t>2026-08-25 17:21:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98406</v>
+        <v>3.98407</v>
       </c>
       <c r="G7" t="n">
-        <v>3764</v>
+        <v>3766</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2371</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:30</t>
+          <t>2026-08-25 17:21:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74214</v>
+        <v>4.74217</v>
       </c>
       <c r="G8" t="n">
-        <v>13624</v>
+        <v>13625</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12125</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:32</t>
+          <t>2026-08-25 17:21:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:35</t>
+          <t>2026-08-25 17:21:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:37</t>
+          <t>2026-08-25 17:21:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72727</v>
+        <v>2.65217</v>
       </c>
       <c r="G11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>August 20, 2026</t>
+          <t>August 25, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:39</t>
+          <t>2026-08-25 17:21:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:41</t>
+          <t>2026-08-25 17:21:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:44</t>
+          <t>2026-08-25 17:21:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:46</t>
+          <t>2026-08-25 17:21:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:48</t>
+          <t>2026-08-25 17:21:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74427</v>
+        <v>4.74362</v>
       </c>
       <c r="G16" t="n">
-        <v>32261</v>
+        <v>32282</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="O16" t="n">
         <v>323</v>
       </c>
       <c r="P16" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q16" t="n">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="R16" t="n">
-        <v>28712</v>
+        <v>28731</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:01</t>
+          <t>2026-08-26 18:32:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:04</t>
+          <t>2026-08-26 18:32:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81171</v>
+        <v>4.81196</v>
       </c>
       <c r="G3" t="n">
-        <v>13208</v>
+        <v>13226</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O3" t="n">
         <v>132</v>
@@ -658,10 +658,10 @@
         <v>132</v>
       </c>
       <c r="Q3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R3" t="n">
-        <v>12283</v>
+        <v>12300</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:06</t>
+          <t>2026-08-26 18:32:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:09</t>
+          <t>2026-08-26 18:32:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85882</v>
+        <v>2.8596</v>
       </c>
       <c r="G5" t="n">
-        <v>3074</v>
+        <v>3077</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="O5" t="n">
         <v>154</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:11</t>
+          <t>2026-08-26 18:32:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:14</t>
+          <t>2026-08-26 18:32:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:16</t>
+          <t>2026-08-26 18:32:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:18</t>
+          <t>2026-08-26 18:32:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:21</t>
+          <t>2026-08-26 18:32:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:23</t>
+          <t>2026-08-26 18:32:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:25</t>
+          <t>2026-08-26 18:32:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71638</v>
+        <v>4.71713</v>
       </c>
       <c r="G12" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>2696</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:28</t>
+          <t>2026-08-26 18:32:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:31</t>
+          <t>2026-08-26 18:32:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:33</t>
+          <t>2026-08-26 18:32:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:21:35</t>
+          <t>2026-08-26 18:32:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74362</v>
+        <v>4.74386</v>
       </c>
       <c r="G16" t="n">
-        <v>32282</v>
+        <v>32306</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="O16" t="n">
         <v>323</v>
@@ -1594,10 +1594,10 @@
         <v>646</v>
       </c>
       <c r="Q16" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="R16" t="n">
-        <v>28731</v>
+        <v>28752</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:05</t>
+          <t>2026-08-28 01:13:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:07</t>
+          <t>2026-08-28 01:13:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81196</v>
+        <v>4.81207</v>
       </c>
       <c r="G3" t="n">
-        <v>13226</v>
+        <v>13234</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>265</v>
       </c>
       <c r="R3" t="n">
-        <v>12300</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:09</t>
+          <t>2026-08-28 01:13:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:12</t>
+          <t>2026-08-28 01:13:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:14</t>
+          <t>2026-08-28 01:13:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:16</t>
+          <t>2026-08-28 01:13:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:19</t>
+          <t>2026-08-28 01:13:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74217</v>
+        <v>4.74214</v>
       </c>
       <c r="G8" t="n">
-        <v>13625</v>
+        <v>13624</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12126</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:21</t>
+          <t>2026-08-28 01:13:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61388</v>
+        <v>4.61334</v>
       </c>
       <c r="G9" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:23</t>
+          <t>2026-08-28 01:13:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:26</t>
+          <t>2026-08-28 01:13:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:28</t>
+          <t>2026-08-28 01:13:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71713</v>
+        <v>4.71689</v>
       </c>
       <c r="G12" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>2697</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:30</t>
+          <t>2026-08-28 01:13:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:33</t>
+          <t>2026-08-28 01:13:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:35</t>
+          <t>2026-08-28 01:13:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:37</t>
+          <t>2026-08-28 01:13:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74386</v>
+        <v>4.74341</v>
       </c>
       <c r="G16" t="n">
-        <v>32306</v>
+        <v>32316</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="O16" t="n">
         <v>323</v>
@@ -1594,10 +1594,10 @@
         <v>646</v>
       </c>
       <c r="Q16" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="R16" t="n">
-        <v>28752</v>
+        <v>28761</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:02</t>
+          <t>2026-08-29 00:47:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:07</t>
+          <t>2026-08-29 00:47:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81207</v>
+        <v>4.81234</v>
       </c>
       <c r="G3" t="n">
-        <v>13234</v>
+        <v>13258</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q3" t="n">
         <v>265</v>
       </c>
       <c r="R3" t="n">
-        <v>12308</v>
+        <v>12330</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:10</t>
+          <t>2026-08-29 00:47:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8741</v>
+        <v>3.87479</v>
       </c>
       <c r="G4" t="n">
-        <v>4837</v>
+        <v>4840</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="O4" t="n">
         <v>242</v>
@@ -733,7 +733,7 @@
         <v>387</v>
       </c>
       <c r="R4" t="n">
-        <v>2999</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:13</t>
+          <t>2026-08-29 00:47:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8596</v>
+        <v>2.85877</v>
       </c>
       <c r="G5" t="n">
-        <v>3077</v>
+        <v>3080</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="O5" t="n">
         <v>154</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:15</t>
+          <t>2026-08-29 00:47:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12752</v>
+        <v>3.12583</v>
       </c>
       <c r="G6" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -868,13 +868,13 @@
         <v>54</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
         <v>63</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:17</t>
+          <t>2026-08-29 00:47:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:20</t>
+          <t>2026-08-29 00:47:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74214</v>
+        <v>4.74217</v>
       </c>
       <c r="G8" t="n">
-        <v>13624</v>
+        <v>13625</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>12125</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:22</t>
+          <t>2026-08-29 00:47:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.61334</v>
+        <v>4.61388</v>
       </c>
       <c r="G9" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:24</t>
+          <t>2026-08-29 00:47:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:27</t>
+          <t>2026-08-29 00:47:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:29</t>
+          <t>2026-08-29 00:47:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71689</v>
+        <v>4.71469</v>
       </c>
       <c r="G12" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>153</v>
       </c>
       <c r="R12" t="n">
-        <v>2698</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:31</t>
+          <t>2026-08-29 00:47:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:33</t>
+          <t>2026-08-29 00:47:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:35</t>
+          <t>2026-08-29 00:47:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 01:13:37</t>
+          <t>2026-08-29 00:47:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74341</v>
+        <v>4.74289</v>
       </c>
       <c r="G16" t="n">
-        <v>32316</v>
+        <v>32342</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="O16" t="n">
         <v>323</v>
       </c>
       <c r="P16" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Q16" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="R16" t="n">
-        <v>28761</v>
+        <v>28784</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:06</t>
+          <t>2026-08-29 19:33:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:08</t>
+          <t>2026-08-29 19:33:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81234</v>
+        <v>4.81238</v>
       </c>
       <c r="G3" t="n">
-        <v>13258</v>
+        <v>13261</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>265</v>
       </c>
       <c r="R3" t="n">
-        <v>12330</v>
+        <v>12333</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:11</t>
+          <t>2026-08-29 19:33:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87479</v>
+        <v>3.87443</v>
       </c>
       <c r="G4" t="n">
-        <v>4840</v>
+        <v>4842</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>387</v>
       </c>
       <c r="R4" t="n">
-        <v>3001</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:13</t>
+          <t>2026-08-29 19:33:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85877</v>
+        <v>2.85756</v>
       </c>
       <c r="G5" t="n">
-        <v>3080</v>
+        <v>3082</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="O5" t="n">
         <v>154</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:16</t>
+          <t>2026-08-29 19:33:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:18</t>
+          <t>2026-08-29 19:33:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98407</v>
+        <v>3.9838</v>
       </c>
       <c r="G7" t="n">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:20</t>
+          <t>2026-08-29 19:33:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:23</t>
+          <t>2026-08-29 19:33:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:25</t>
+          <t>2026-08-29 19:33:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:27</t>
+          <t>2026-08-29 19:33:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:30</t>
+          <t>2026-08-29 19:33:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:32</t>
+          <t>2026-08-29 19:34:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.01304</v>
+        <v>4.00743</v>
       </c>
       <c r="G13" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>102</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P13" t="n">
         <v>16</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:34</t>
+          <t>2026-08-29 19:34:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:37</t>
+          <t>2026-08-29 19:34:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:39</t>
+          <t>2026-08-29 19:34:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74289</v>
+        <v>4.74273</v>
       </c>
       <c r="G16" t="n">
-        <v>32342</v>
+        <v>32347</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>1294</v>
       </c>
       <c r="R16" t="n">
-        <v>28784</v>
+        <v>28789</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:35</t>
+          <t>2026-08-30 19:32:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:37</t>
+          <t>2026-08-30 19:32:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81238</v>
+        <v>4.81192</v>
       </c>
       <c r="G3" t="n">
-        <v>13261</v>
+        <v>13271</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.45.0</t>
+          <t>4.45.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>August 18, 2026</t>
+          <t>August 29, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -661,7 +661,7 @@
         <v>265</v>
       </c>
       <c r="R3" t="n">
-        <v>12333</v>
+        <v>12342</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:40</t>
+          <t>2026-08-30 19:32:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87443</v>
+        <v>3.8749</v>
       </c>
       <c r="G4" t="n">
-        <v>4842</v>
+        <v>4844</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="O4" t="n">
         <v>242</v>
@@ -730,10 +730,10 @@
         <v>242</v>
       </c>
       <c r="Q4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:42</t>
+          <t>2026-08-30 19:32:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85756</v>
+        <v>2.85765</v>
       </c>
       <c r="G5" t="n">
-        <v>3082</v>
+        <v>3084</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>154</v>
       </c>
       <c r="P5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q5" t="n">
         <v>123</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:45</t>
+          <t>2026-08-30 19:32:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:47</t>
+          <t>2026-08-30 19:32:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9838</v>
+        <v>3.98567</v>
       </c>
       <c r="G7" t="n">
-        <v>3765</v>
+        <v>3768</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O7" t="n">
         <v>151</v>
@@ -949,7 +949,7 @@
         <v>414</v>
       </c>
       <c r="R7" t="n">
-        <v>2372</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:49</t>
+          <t>2026-08-30 19:32:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:51</t>
+          <t>2026-08-30 19:32:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:53</t>
+          <t>2026-08-30 19:32:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.27</t>
+          <t>2.1.28</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,23 +1149,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>July 02, 2026</t>
+          <t>August 30, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:56</t>
+          <t>2026-08-30 19:33:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:58</t>
+          <t>2026-08-30 19:33:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71469</v>
+        <v>4.71149</v>
       </c>
       <c r="G12" t="n">
-        <v>3067</v>
+        <v>3071</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-29 19:34:02</t>
+          <t>2026-08-30 19:33:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.7.20</t>
+          <t>1.8.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>July 16, 2026</t>
+          <t>August 30, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-29 19:34:06</t>
+          <t>2026-08-30 19:33:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-29 19:34:14</t>
+          <t>2026-08-30 19:33:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-29 19:34:17</t>
+          <t>2026-08-30 19:33:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74273</v>
+        <v>4.74295</v>
       </c>
       <c r="G16" t="n">
-        <v>32347</v>
+        <v>32359</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1294</v>
       </c>
       <c r="O16" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P16" t="n">
         <v>647</v>
@@ -1597,7 +1597,7 @@
         <v>1294</v>
       </c>
       <c r="R16" t="n">
-        <v>28789</v>
+        <v>28800</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:38</t>
+          <t>2026-08-31 21:41:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:41</t>
+          <t>2026-08-31 21:41:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81192</v>
+        <v>4.81206</v>
       </c>
       <c r="G3" t="n">
-        <v>13271</v>
+        <v>13281</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>133</v>
       </c>
       <c r="Q3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R3" t="n">
-        <v>12342</v>
+        <v>12351</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:43</t>
+          <t>2026-08-31 21:41:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8749</v>
+        <v>3.87492</v>
       </c>
       <c r="G4" t="n">
-        <v>4844</v>
+        <v>4845</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3003</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:46</t>
+          <t>2026-08-31 21:41:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85765</v>
+        <v>2.85774</v>
       </c>
       <c r="G5" t="n">
-        <v>3084</v>
+        <v>3086</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="O5" t="n">
         <v>154</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:48</t>
+          <t>2026-08-31 21:41:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:51</t>
+          <t>2026-08-31 21:41:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98567</v>
+        <v>3.98515</v>
       </c>
       <c r="G7" t="n">
-        <v>3768</v>
+        <v>3770</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>188</v>
       </c>
       <c r="Q7" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R7" t="n">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:53</t>
+          <t>2026-08-31 21:41:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:56</t>
+          <t>2026-08-31 21:41:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:58</t>
+          <t>2026-08-31 21:41:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87369</v>
+        <v>3.88219</v>
       </c>
       <c r="G10" t="n">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O10" t="n">
         <v>42</v>
@@ -1162,10 +1162,10 @@
         <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>674</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:01</t>
+          <t>2026-08-31 21:41:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:03</t>
+          <t>2026-08-31 21:41:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71149</v>
+        <v>4.71145</v>
       </c>
       <c r="G12" t="n">
-        <v>3071</v>
+        <v>3074</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:06</t>
+          <t>2026-08-31 21:41:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00743</v>
+        <v>4.0073</v>
       </c>
       <c r="G13" t="n">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:09</t>
+          <t>2026-08-31 21:41:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:11</t>
+          <t>2026-08-31 21:41:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-30 19:33:14</t>
+          <t>2026-08-31 21:41:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74295</v>
+        <v>4.74272</v>
       </c>
       <c r="G16" t="n">
-        <v>32359</v>
+        <v>32373</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1294</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1294</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28800</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:15</t>
+          <t>2026-09-01 19:40:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:17</t>
+          <t>2026-09-01 19:40:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:20</t>
+          <t>2026-09-01 19:40:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87492</v>
+        <v>3.87518</v>
       </c>
       <c r="G4" t="n">
-        <v>4845</v>
+        <v>4847</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:22</t>
+          <t>2026-09-01 19:40:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85774</v>
+        <v>2.85677</v>
       </c>
       <c r="G5" t="n">
         <v>3086</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:24</t>
+          <t>2026-09-01 19:40:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:27</t>
+          <t>2026-09-01 19:40:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:29</t>
+          <t>2026-09-01 19:41:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>July 29, 2026</t>
+          <t>September 01, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:31</t>
+          <t>2026-09-01 19:41:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:34</t>
+          <t>2026-09-01 19:41:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:35</t>
+          <t>2026-09-01 19:41:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:37</t>
+          <t>2026-09-01 19:41:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71145</v>
+        <v>4.71154</v>
       </c>
       <c r="G12" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:39</t>
+          <t>2026-09-01 19:41:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.0073</v>
+        <v>4.00721</v>
       </c>
       <c r="G13" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.8.0</t>
+          <t>1.8.1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1365,23 +1365,23 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>August 30, 2026</t>
+          <t>September 01, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:41</t>
+          <t>2026-09-01 19:41:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.51029</v>
+        <v>3.50413</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:43</t>
+          <t>2026-09-01 19:41:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:44</t>
+          <t>2026-09-01 19:41:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1295</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1295</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>28812</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:48</t>
+          <t>2026-09-02 19:32:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:50</t>
+          <t>2026-09-02 19:32:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81206</v>
+        <v>4.81216</v>
       </c>
       <c r="G3" t="n">
-        <v>13281</v>
+        <v>13288</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O3" t="n">
         <v>133</v>
@@ -661,7 +661,7 @@
         <v>266</v>
       </c>
       <c r="R3" t="n">
-        <v>12351</v>
+        <v>12358</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:52</t>
+          <t>2026-09-02 19:32:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:54</t>
+          <t>2026-09-02 19:32:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:56</t>
+          <t>2026-09-02 19:32:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:58</t>
+          <t>2026-09-02 19:32:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98515</v>
+        <v>3.9841</v>
       </c>
       <c r="G7" t="n">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>151</v>
       </c>
       <c r="P7" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7" t="n">
         <v>415</v>
       </c>
       <c r="R7" t="n">
-        <v>2375</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:00</t>
+          <t>2026-09-02 19:33:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:03</t>
+          <t>2026-09-02 19:33:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:05</t>
+          <t>2026-09-02 19:33:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:07</t>
+          <t>2026-09-02 19:33:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:09</t>
+          <t>2026-09-02 19:33:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:11</t>
+          <t>2026-09-02 19:33:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:14</t>
+          <t>2026-09-02 19:33:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:16</t>
+          <t>2026-09-02 19:33:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:41:18</t>
+          <t>2026-09-02 19:33:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74272</v>
+        <v>4.74311</v>
       </c>
       <c r="G16" t="n">
-        <v>32373</v>
+        <v>32387</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>324</v>
       </c>
       <c r="P16" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Q16" t="n">
         <v>1295</v>
       </c>
       <c r="R16" t="n">
-        <v>28812</v>
+        <v>28824</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:47</t>
+          <t>2026-09-03 19:29:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:50</t>
+          <t>2026-09-03 19:30:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81216</v>
+        <v>4.81236</v>
       </c>
       <c r="G3" t="n">
-        <v>13288</v>
+        <v>13303</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>266</v>
       </c>
       <c r="R3" t="n">
-        <v>12358</v>
+        <v>12372</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:52</t>
+          <t>2026-09-03 19:30:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87518</v>
+        <v>3.87629</v>
       </c>
       <c r="G4" t="n">
-        <v>4847</v>
+        <v>4850</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="O4" t="n">
         <v>242</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3005</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:55</t>
+          <t>2026-09-03 19:30:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85677</v>
+        <v>2.85645</v>
       </c>
       <c r="G5" t="n">
-        <v>3086</v>
+        <v>3093</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="O5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>93</v>
       </c>
       <c r="Q5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1265</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:57</t>
+          <t>2026-09-03 19:30:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.12583</v>
+        <v>3.13816</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O6" t="n">
         <v>11</v>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:59</t>
+          <t>2026-09-03 19:30:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9841</v>
+        <v>3.98331</v>
       </c>
       <c r="G7" t="n">
-        <v>3773</v>
+        <v>3775</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.4.9</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -933,11 +933,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>July 29, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O7" t="n">
         <v>151</v>
@@ -949,7 +949,7 @@
         <v>415</v>
       </c>
       <c r="R7" t="n">
-        <v>2377</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:01</t>
+          <t>2026-09-03 19:30:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:04</t>
+          <t>2026-09-03 19:30:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:06</t>
+          <t>2026-09-03 19:30:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.88219</v>
+        <v>3.88324</v>
       </c>
       <c r="G10" t="n">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.28</t>
+          <t>2.1.29</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>August 30, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O10" t="n">
         <v>42</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:08</t>
+          <t>2026-09-03 19:30:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>August 25, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:10</t>
+          <t>2026-09-03 19:30:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71154</v>
+        <v>4.71192</v>
       </c>
       <c r="G12" t="n">
-        <v>3075</v>
+        <v>3079</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>August 20, 2026</t>
+          <t>September 02, 2026</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2706</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:13</t>
+          <t>2026-09-03 19:30:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00721</v>
+        <v>4.00873</v>
       </c>
       <c r="G13" t="n">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P13" t="n">
         <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:15</t>
+          <t>2026-09-03 19:30:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.50413</v>
+        <v>3.51029</v>
       </c>
       <c r="G14" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:17</t>
+          <t>2026-09-03 19:30:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:33:19</t>
+          <t>2026-09-03 19:30:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74311</v>
+        <v>4.7424</v>
       </c>
       <c r="G16" t="n">
-        <v>32387</v>
+        <v>32420</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="O16" t="n">
         <v>324</v>
@@ -1594,10 +1594,10 @@
         <v>648</v>
       </c>
       <c r="Q16" t="n">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="R16" t="n">
-        <v>28824</v>
+        <v>28854</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:58</t>
+          <t>2026-09-04 19:39:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.62573</v>
+        <v>4.61628</v>
       </c>
       <c r="G2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -583,13 +583,13 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:00</t>
+          <t>2026-09-04 19:39:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81236</v>
+        <v>4.81257</v>
       </c>
       <c r="G3" t="n">
-        <v>13303</v>
+        <v>13318</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O3" t="n">
         <v>133</v>
@@ -661,7 +661,7 @@
         <v>266</v>
       </c>
       <c r="R3" t="n">
-        <v>12372</v>
+        <v>12386</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:03</t>
+          <t>2026-09-04 19:39:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87629</v>
+        <v>3.87552</v>
       </c>
       <c r="G4" t="n">
-        <v>4850</v>
+        <v>4852</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -724,16 +724,16 @@
         <v>970</v>
       </c>
       <c r="O4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q4" t="n">
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3007</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:05</t>
+          <t>2026-09-04 19:39:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85645</v>
+        <v>2.85557</v>
       </c>
       <c r="G5" t="n">
-        <v>3093</v>
+        <v>3095</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="O5" t="n">
         <v>155</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="R5" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:08</t>
+          <t>2026-09-04 19:39:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.13816</v>
+        <v>3.13725</v>
       </c>
       <c r="G6" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
         <v>14</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:10</t>
+          <t>2026-09-04 19:39:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:13</t>
+          <t>2026-09-04 19:39:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:15</t>
+          <t>2026-09-04 19:39:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:18</t>
+          <t>2026-09-04 19:39:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:20</t>
+          <t>2026-09-04 19:39:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:23</t>
+          <t>2026-09-04 19:39:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71192</v>
+        <v>4.71089</v>
       </c>
       <c r="G12" t="n">
-        <v>3079</v>
+        <v>3082</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2710</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:25</t>
+          <t>2026-09-04 19:39:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.00873</v>
+        <v>4.00521</v>
       </c>
       <c r="G13" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:28</t>
+          <t>2026-09-04 19:39:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:30</t>
+          <t>2026-09-04 19:39:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 19:30:32</t>
+          <t>2026-09-04 19:39:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7424</v>
+        <v>4.74207</v>
       </c>
       <c r="G16" t="n">
-        <v>32420</v>
+        <v>32437</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>324</v>
       </c>
       <c r="P16" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q16" t="n">
         <v>1297</v>
       </c>
       <c r="R16" t="n">
-        <v>28854</v>
+        <v>28869</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:21</t>
+          <t>2026-09-05 18:38:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:24</t>
+          <t>2026-09-05 18:38:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81257</v>
+        <v>4.81273</v>
       </c>
       <c r="G3" t="n">
-        <v>13318</v>
+        <v>13328</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>133</v>
       </c>
       <c r="Q3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12386</v>
+        <v>12395</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:26</t>
+          <t>2026-09-05 18:38:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87552</v>
+        <v>3.87575</v>
       </c>
       <c r="G4" t="n">
-        <v>4852</v>
+        <v>4853</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O4" t="n">
         <v>243</v>
@@ -733,7 +733,7 @@
         <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>3008</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:28</t>
+          <t>2026-09-05 18:38:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85557</v>
+        <v>2.85497</v>
       </c>
       <c r="G5" t="n">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:30</t>
+          <t>2026-09-05 18:38:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:32</t>
+          <t>2026-09-05 18:38:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.98331</v>
+        <v>3.98439</v>
       </c>
       <c r="G7" t="n">
-        <v>3775</v>
+        <v>3779</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>189</v>
       </c>
       <c r="Q7" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2378</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:34</t>
+          <t>2026-09-05 18:38:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:36</t>
+          <t>2026-09-05 18:38:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:38</t>
+          <t>2026-09-05 18:38:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:40</t>
+          <t>2026-09-05 18:38:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:42</t>
+          <t>2026-09-05 18:38:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.71089</v>
+        <v>4.70913</v>
       </c>
       <c r="G12" t="n">
-        <v>3082</v>
+        <v>3084</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2712</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:45</t>
+          <t>2026-09-05 18:38:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:47</t>
+          <t>2026-09-05 18:38:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:49</t>
+          <t>2026-09-05 18:38:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:51</t>
+          <t>2026-09-05 18:39:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74207</v>
+        <v>4.74181</v>
       </c>
       <c r="G16" t="n">
-        <v>32437</v>
+        <v>32450</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="O16" t="n">
         <v>324</v>
@@ -1594,10 +1594,10 @@
         <v>649</v>
       </c>
       <c r="Q16" t="n">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="R16" t="n">
-        <v>28869</v>
+        <v>28880</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:27</t>
+          <t>2026-09-06 18:41:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:30</t>
+          <t>2026-09-06 18:41:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81273</v>
+        <v>4.81278</v>
       </c>
       <c r="G3" t="n">
-        <v>13328</v>
+        <v>13332</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>267</v>
       </c>
       <c r="R3" t="n">
-        <v>12395</v>
+        <v>12399</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:32</t>
+          <t>2026-09-06 18:41:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.87575</v>
+        <v>3.87598</v>
       </c>
       <c r="G4" t="n">
-        <v>4853</v>
+        <v>4854</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:34</t>
+          <t>2026-09-06 18:41:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.85497</v>
+        <v>2.85428</v>
       </c>
       <c r="G5" t="n">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:37</t>
+          <t>2026-09-06 18:41:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:39</t>
+          <t>2026-09-06 18:41:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:42</t>
+          <t>2026-09-06 18:42:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:44</t>
+          <t>2026-09-06 18:42:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:46</t>
+          <t>2026-09-06 18:42:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:49</t>
+          <t>2026-09-06 18:42:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:51</t>
+          <t>2026-09-06 18:42:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.70913</v>
+        <v>4.70901</v>
       </c>
       <c r="G12" t="n">
-        <v>3084</v>
+        <v>3086</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>154</v>
       </c>
       <c r="R12" t="n">
-        <v>2714</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:53</t>
+          <t>2026-09-06 18:42:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1342,7 +1342,7 @@
         <v>4.00521</v>
       </c>
       <c r="G13" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:56</t>
+          <t>2026-09-06 18:42:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:58</t>
+          <t>2026-09-06 18:42:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-05 18:39:00</t>
+          <t>2026-09-06 18:42:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74181</v>
+        <v>4.74164</v>
       </c>
       <c r="G16" t="n">
-        <v>32450</v>
+        <v>32462</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>1298</v>
       </c>
       <c r="O16" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P16" t="n">
         <v>649</v>
@@ -1597,7 +1597,7 @@
         <v>1298</v>
       </c>
       <c r="R16" t="n">
-        <v>28880</v>
+        <v>28891</v>
       </c>
     </row>
   </sheetData>
